--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_13_1.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_13_1.xlsx
@@ -6465,7 +6465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA125"/>
+  <dimension ref="A1:AA124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8.75" customWidth="1" style="50" min="1" max="1"/>
@@ -10960,7 +10960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="30.9140625" defaultRowHeight="14"/>
   <cols>
     <col width="35.83203125" customWidth="1" style="50" min="6" max="6"/>
@@ -10972,32 +10972,6 @@
           <t>BSI.IT.6.C7.3: DR Data Integrity Validation, Testing of attributes (Scope, Email approval and all attributes)</t>
         </is>
       </c>
-      <c r="B1" s="97" t="n"/>
-      <c r="C1" s="97" t="n"/>
-      <c r="D1" s="97" t="n"/>
-      <c r="E1" s="97" t="n"/>
-      <c r="F1" s="97" t="n"/>
-      <c r="G1" s="98" t="n"/>
-      <c r="H1" s="68" t="n"/>
-      <c r="I1" s="68" t="n"/>
-      <c r="J1" s="68" t="n"/>
-      <c r="K1" s="68" t="n"/>
-      <c r="L1" s="68" t="n"/>
-      <c r="M1" s="68" t="n"/>
-      <c r="N1" s="68" t="n"/>
-      <c r="O1" s="68" t="n"/>
-      <c r="P1" s="68" t="n"/>
-      <c r="Q1" s="68" t="n"/>
-      <c r="R1" s="68" t="n"/>
-      <c r="S1" s="68" t="n"/>
-      <c r="T1" s="68" t="n"/>
-      <c r="U1" s="68" t="n"/>
-      <c r="V1" s="68" t="n"/>
-      <c r="W1" s="85" t="n"/>
-      <c r="X1" s="85" t="n"/>
-      <c r="Y1" s="85" t="n"/>
-      <c r="Z1" s="85" t="n"/>
-      <c r="AA1" s="85" t="n"/>
       <c r="AB1" s="85" t="n"/>
       <c r="AC1" s="85" t="n"/>
       <c r="AD1" s="85" t="n"/>
@@ -11023,34 +10997,13 @@
       <c r="AX1" s="85" t="n"/>
       <c r="AY1" s="85" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" s="50">
       <c r="A2" s="74" t="n"/>
       <c r="B2" s="74" t="n"/>
       <c r="C2" s="74" t="n"/>
       <c r="D2" s="74" t="n"/>
       <c r="E2" s="74" t="n"/>
       <c r="F2" s="74" t="n"/>
-      <c r="G2" s="65" t="n"/>
-      <c r="H2" s="68" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="68" t="n"/>
-      <c r="K2" s="68" t="n"/>
-      <c r="L2" s="68" t="n"/>
-      <c r="M2" s="68" t="n"/>
-      <c r="N2" s="68" t="n"/>
-      <c r="O2" s="68" t="n"/>
-      <c r="P2" s="68" t="n"/>
-      <c r="Q2" s="68" t="n"/>
-      <c r="R2" s="68" t="n"/>
-      <c r="S2" s="68" t="n"/>
-      <c r="T2" s="68" t="n"/>
-      <c r="U2" s="68" t="n"/>
-      <c r="V2" s="68" t="n"/>
-      <c r="W2" s="85" t="n"/>
-      <c r="X2" s="85" t="n"/>
-      <c r="Y2" s="85" t="n"/>
-      <c r="Z2" s="85" t="n"/>
-      <c r="AA2" s="85" t="n"/>
       <c r="AB2" s="85" t="n"/>
       <c r="AC2" s="85" t="n"/>
       <c r="AD2" s="85" t="n"/>
@@ -11077,9 +11030,9 @@
       <c r="AY2" s="85" t="n"/>
     </row>
     <row r="3" ht="41" customHeight="1" s="50">
-      <c r="A3" s="71" t="inlineStr">
-        <is>
-          <t>1. Application Name (column D): review of evidence files and results</t>
+      <c r="A3" s="101" t="inlineStr">
+        <is>
+          <t>1. Application Name (column B): review of evidence files and results</t>
         </is>
       </c>
       <c r="B3" s="97" t="n"/>
@@ -11088,26 +11041,6 @@
       <c r="E3" s="97" t="n"/>
       <c r="F3" s="97" t="n"/>
       <c r="G3" s="98" t="n"/>
-      <c r="H3" s="68" t="n"/>
-      <c r="I3" s="68" t="n"/>
-      <c r="J3" s="68" t="n"/>
-      <c r="K3" s="68" t="n"/>
-      <c r="L3" s="68" t="n"/>
-      <c r="M3" s="68" t="n"/>
-      <c r="N3" s="68" t="n"/>
-      <c r="O3" s="68" t="n"/>
-      <c r="P3" s="68" t="n"/>
-      <c r="Q3" s="68" t="n"/>
-      <c r="R3" s="68" t="n"/>
-      <c r="S3" s="68" t="n"/>
-      <c r="T3" s="68" t="n"/>
-      <c r="U3" s="68" t="n"/>
-      <c r="V3" s="68" t="n"/>
-      <c r="W3" s="85" t="n"/>
-      <c r="X3" s="85" t="n"/>
-      <c r="Y3" s="85" t="n"/>
-      <c r="Z3" s="85" t="n"/>
-      <c r="AA3" s="85" t="n"/>
       <c r="AB3" s="85" t="n"/>
       <c r="AC3" s="85" t="n"/>
       <c r="AD3" s="85" t="n"/>
@@ -11170,20 +11103,6 @@
         </is>
       </c>
       <c r="H4" s="67" t="n"/>
-      <c r="N4" s="68" t="n"/>
-      <c r="O4" s="68" t="n"/>
-      <c r="P4" s="68" t="n"/>
-      <c r="Q4" s="68" t="n"/>
-      <c r="R4" s="68" t="n"/>
-      <c r="S4" s="68" t="n"/>
-      <c r="T4" s="68" t="n"/>
-      <c r="U4" s="68" t="n"/>
-      <c r="V4" s="68" t="n"/>
-      <c r="W4" s="85" t="n"/>
-      <c r="X4" s="85" t="n"/>
-      <c r="Y4" s="85" t="n"/>
-      <c r="Z4" s="85" t="n"/>
-      <c r="AA4" s="85" t="n"/>
       <c r="AB4" s="85" t="n"/>
       <c r="AC4" s="85" t="n"/>
       <c r="AD4" s="85" t="n"/>
@@ -11256,7 +11175,7 @@
       </c>
       <c r="F5" s="76" t="inlineStr">
         <is>
-          <t>Supports Application Name (column D), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>Supports Application Name (column B), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="G5" s="77" t="inlineStr">
@@ -11270,20 +11189,6 @@
       <c r="K5" s="70" t="n"/>
       <c r="L5" s="70" t="n"/>
       <c r="M5" s="70" t="n"/>
-      <c r="N5" s="68" t="n"/>
-      <c r="O5" s="68" t="n"/>
-      <c r="P5" s="68" t="n"/>
-      <c r="Q5" s="68" t="n"/>
-      <c r="R5" s="68" t="n"/>
-      <c r="S5" s="68" t="n"/>
-      <c r="T5" s="68" t="n"/>
-      <c r="U5" s="68" t="n"/>
-      <c r="V5" s="68" t="n"/>
-      <c r="W5" s="85" t="n"/>
-      <c r="X5" s="85" t="n"/>
-      <c r="Y5" s="85" t="n"/>
-      <c r="Z5" s="85" t="n"/>
-      <c r="AA5" s="85" t="n"/>
       <c r="AB5" s="85" t="n"/>
       <c r="AC5" s="85" t="n"/>
       <c r="AD5" s="85" t="n"/>
@@ -11309,7 +11214,7 @@
       <c r="AX5" s="85" t="n"/>
       <c r="AY5" s="85" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" s="50">
       <c r="A6" s="74" t="n"/>
       <c r="B6" s="74" t="n"/>
       <c r="C6" s="74" t="n"/>
@@ -11317,26 +11222,26 @@
       <c r="E6" s="74" t="n"/>
       <c r="F6" s="74" t="n"/>
       <c r="G6" s="74" t="n"/>
-      <c r="H6" s="68" t="n"/>
-      <c r="I6" s="68" t="n"/>
-      <c r="J6" s="68" t="n"/>
-      <c r="K6" s="68" t="n"/>
-      <c r="L6" s="68" t="n"/>
-      <c r="M6" s="68" t="n"/>
-      <c r="N6" s="68" t="n"/>
-      <c r="O6" s="68" t="n"/>
-      <c r="P6" s="68" t="n"/>
-      <c r="Q6" s="68" t="n"/>
-      <c r="R6" s="68" t="n"/>
-      <c r="S6" s="68" t="n"/>
-      <c r="T6" s="68" t="n"/>
-      <c r="U6" s="68" t="n"/>
-      <c r="V6" s="68" t="n"/>
-      <c r="W6" s="85" t="n"/>
-      <c r="X6" s="85" t="n"/>
-      <c r="Y6" s="85" t="n"/>
-      <c r="Z6" s="85" t="n"/>
-      <c r="AA6" s="85" t="n"/>
+      <c r="H6" s="74" t="n"/>
+      <c r="I6" s="74" t="n"/>
+      <c r="J6" s="74" t="n"/>
+      <c r="K6" s="74" t="n"/>
+      <c r="L6" s="74" t="n"/>
+      <c r="M6" s="74" t="n"/>
+      <c r="N6" s="74" t="n"/>
+      <c r="O6" s="74" t="n"/>
+      <c r="P6" s="74" t="n"/>
+      <c r="Q6" s="74" t="n"/>
+      <c r="R6" s="74" t="n"/>
+      <c r="S6" s="74" t="n"/>
+      <c r="T6" s="74" t="n"/>
+      <c r="U6" s="74" t="n"/>
+      <c r="V6" s="74" t="n"/>
+      <c r="W6" s="74" t="n"/>
+      <c r="X6" s="74" t="n"/>
+      <c r="Y6" s="74" t="n"/>
+      <c r="Z6" s="74" t="n"/>
+      <c r="AA6" s="74" t="n"/>
       <c r="AB6" s="85" t="n"/>
       <c r="AC6" s="85" t="n"/>
       <c r="AD6" s="85" t="n"/>
@@ -11363,9 +11268,9 @@
       <c r="AY6" s="85" t="n"/>
     </row>
     <row r="7" ht="15.5" customHeight="1" s="50">
-      <c r="A7" s="71" t="inlineStr">
-        <is>
-          <t>2. IT DR exercise name (column B): review of evidence files and results</t>
+      <c r="A7" s="101" t="inlineStr">
+        <is>
+          <t>2. Applications in Scope Identified (column C): review of evidence files and results</t>
         </is>
       </c>
       <c r="B7" s="97" t="n"/>
@@ -11374,26 +11279,6 @@
       <c r="E7" s="97" t="n"/>
       <c r="F7" s="97" t="n"/>
       <c r="G7" s="98" t="n"/>
-      <c r="H7" s="68" t="n"/>
-      <c r="I7" s="68" t="n"/>
-      <c r="J7" s="68" t="n"/>
-      <c r="K7" s="68" t="n"/>
-      <c r="L7" s="68" t="n"/>
-      <c r="M7" s="68" t="n"/>
-      <c r="N7" s="68" t="n"/>
-      <c r="O7" s="68" t="n"/>
-      <c r="P7" s="68" t="n"/>
-      <c r="Q7" s="68" t="n"/>
-      <c r="R7" s="68" t="n"/>
-      <c r="S7" s="68" t="n"/>
-      <c r="T7" s="68" t="n"/>
-      <c r="U7" s="68" t="n"/>
-      <c r="V7" s="68" t="n"/>
-      <c r="W7" s="85" t="n"/>
-      <c r="X7" s="85" t="n"/>
-      <c r="Y7" s="85" t="n"/>
-      <c r="Z7" s="85" t="n"/>
-      <c r="AA7" s="85" t="n"/>
       <c r="AB7" s="85" t="n"/>
       <c r="AC7" s="85" t="n"/>
       <c r="AD7" s="85" t="n"/>
@@ -11456,17 +11341,6 @@
         </is>
       </c>
       <c r="H8" s="67" t="n"/>
-      <c r="Q8" s="68" t="n"/>
-      <c r="R8" s="68" t="n"/>
-      <c r="S8" s="68" t="n"/>
-      <c r="T8" s="68" t="n"/>
-      <c r="U8" s="68" t="n"/>
-      <c r="V8" s="68" t="n"/>
-      <c r="W8" s="85" t="n"/>
-      <c r="X8" s="85" t="n"/>
-      <c r="Y8" s="85" t="n"/>
-      <c r="Z8" s="85" t="n"/>
-      <c r="AA8" s="85" t="n"/>
       <c r="AB8" s="85" t="n"/>
       <c r="AC8" s="85" t="n"/>
       <c r="AD8" s="85" t="n"/>
@@ -11492,46 +11366,54 @@
       <c r="AX8" s="85" t="n"/>
       <c r="AY8" s="85" t="n"/>
     </row>
-    <row r="9" ht="126" customHeight="1" s="50">
+    <row r="9" ht="409" customHeight="1" s="50">
       <c r="A9" s="78" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>MA01</t>
         </is>
       </c>
       <c r="B9" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
         <v/>
       </c>
       <c r="C9" s="76" t="inlineStr">
         <is>
-          <t>BCiC: Applications In Scope for DR Test BSI</t>
+          <t>09/23/2026, Cesar Vidal (BCiC walkthrough)</t>
         </is>
       </c>
       <c r="D9" s="76" t="inlineStr">
         <is>
-          <t>1822 ACH Express (E01 row 3)
-1867 FedExport - BSI (E01 row 19)
-1868 FedImport - BSI (E01 row 20)
-3299 Imaging101 (E01 row 24)
-4052 Interface Monitor (E01 row 25)
-3301 MQ Payment Monitor (E01 row 31)
-1903 OFAC - BSI (E01 row 34)
-1917 ReconXpert (E01 row 36)
-1936 Swift Interface - BSI (E01 row 42)
-1937 T24 (E01 row 43)</t>
+          <t>1822 ACH Express
+1867 FedExport - BSI
+1868 FedImport - BSI
+3299 Imaging101
+4052 Interface Monitor
+3301 MQ Payment Monitor
+1903 OFAC - BSI
+1917 ReconXpert
+1936 Swift Interface - BSI
+1937 T24</t>
         </is>
       </c>
       <c r="E9" s="76" t="inlineStr">
         <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.
-Checked for IT DR exercise name:
-Exercise Date 12/11/25, 2025 DR Test Scope = True
-Exercise Date 11/15/25, 2025 DR Test Scope = True</t>
+          <t>BC in the Cloud 'Applications In Scope for DR Test BSI' view (filter Scope Entity = BSI; 43 items). The 10 tested applications are selected (1822, 1867, 1868, 1903, 1917, 1937, 1936, 3301, 3299, 4052) and each shows 2025 DR Test Scope = True, 2025 Backup/Restore Test Scope = True and 2025 Backup/Restore DIV Scope = True.
+Checked for Applications in Scope Identified:
+BSI In-Scope Applications-2026: App ID 1822 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 1867 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 1868 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 3299 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 4052 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 3301 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 1903 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 1917 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 1936 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+BSI In-Scope Applications-2026: App ID 1937 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True</t>
         </is>
       </c>
       <c r="F9" s="76" t="inlineStr">
         <is>
-          <t>Supports IT DR exercise name (column B), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>Supports Applications in Scope Identified (column C), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="G9" s="77" t="inlineStr">
@@ -11540,25 +11422,11 @@
         </is>
       </c>
       <c r="H9" s="70" t="n"/>
-      <c r="I9" s="70" t="n"/>
+      <c r="I9" s="69" t="n"/>
       <c r="J9" s="70" t="n"/>
       <c r="K9" s="70" t="n"/>
       <c r="L9" s="70" t="n"/>
       <c r="M9" s="70" t="n"/>
-      <c r="N9" s="69" t="n"/>
-      <c r="O9" s="70" t="n"/>
-      <c r="P9" s="70" t="n"/>
-      <c r="Q9" s="68" t="n"/>
-      <c r="R9" s="68" t="n"/>
-      <c r="S9" s="68" t="n"/>
-      <c r="T9" s="68" t="n"/>
-      <c r="U9" s="68" t="n"/>
-      <c r="V9" s="68" t="n"/>
-      <c r="W9" s="85" t="n"/>
-      <c r="X9" s="85" t="n"/>
-      <c r="Y9" s="85" t="n"/>
-      <c r="Z9" s="85" t="n"/>
-      <c r="AA9" s="85" t="n"/>
       <c r="AB9" s="85" t="n"/>
       <c r="AC9" s="85" t="n"/>
       <c r="AD9" s="85" t="n"/>
@@ -11584,7 +11452,7 @@
       <c r="AX9" s="85" t="n"/>
       <c r="AY9" s="85" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" s="50">
       <c r="A10" s="74" t="n"/>
       <c r="B10" s="74" t="n"/>
       <c r="C10" s="74" t="n"/>
@@ -11592,26 +11460,26 @@
       <c r="E10" s="74" t="n"/>
       <c r="F10" s="74" t="n"/>
       <c r="G10" s="74" t="n"/>
-      <c r="H10" s="68" t="n"/>
-      <c r="I10" s="68" t="n"/>
-      <c r="J10" s="68" t="n"/>
-      <c r="K10" s="68" t="n"/>
-      <c r="L10" s="68" t="n"/>
-      <c r="M10" s="68" t="n"/>
-      <c r="N10" s="68" t="n"/>
-      <c r="O10" s="68" t="n"/>
-      <c r="P10" s="68" t="n"/>
-      <c r="Q10" s="68" t="n"/>
-      <c r="R10" s="68" t="n"/>
-      <c r="S10" s="68" t="n"/>
-      <c r="T10" s="68" t="n"/>
-      <c r="U10" s="68" t="n"/>
-      <c r="V10" s="68" t="n"/>
-      <c r="W10" s="85" t="n"/>
-      <c r="X10" s="85" t="n"/>
-      <c r="Y10" s="85" t="n"/>
-      <c r="Z10" s="85" t="n"/>
-      <c r="AA10" s="85" t="n"/>
+      <c r="H10" s="74" t="n"/>
+      <c r="I10" s="74" t="n"/>
+      <c r="J10" s="74" t="n"/>
+      <c r="K10" s="74" t="n"/>
+      <c r="L10" s="74" t="n"/>
+      <c r="M10" s="74" t="n"/>
+      <c r="N10" s="74" t="n"/>
+      <c r="O10" s="74" t="n"/>
+      <c r="P10" s="74" t="n"/>
+      <c r="Q10" s="74" t="n"/>
+      <c r="R10" s="74" t="n"/>
+      <c r="S10" s="74" t="n"/>
+      <c r="T10" s="74" t="n"/>
+      <c r="U10" s="74" t="n"/>
+      <c r="V10" s="74" t="n"/>
+      <c r="W10" s="74" t="n"/>
+      <c r="X10" s="74" t="n"/>
+      <c r="Y10" s="74" t="n"/>
+      <c r="Z10" s="74" t="n"/>
+      <c r="AA10" s="74" t="n"/>
       <c r="AB10" s="85" t="n"/>
       <c r="AC10" s="85" t="n"/>
       <c r="AD10" s="85" t="n"/>
@@ -11637,34 +11505,18 @@
       <c r="AX10" s="85" t="n"/>
       <c r="AY10" s="85" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="74" t="n"/>
-      <c r="B11" s="74" t="n"/>
-      <c r="C11" s="74" t="n"/>
-      <c r="D11" s="74" t="n"/>
-      <c r="E11" s="74" t="n"/>
-      <c r="F11" s="74" t="n"/>
-      <c r="G11" s="74" t="n"/>
-      <c r="H11" s="68" t="n"/>
-      <c r="I11" s="68" t="n"/>
-      <c r="J11" s="68" t="n"/>
-      <c r="K11" s="68" t="n"/>
-      <c r="L11" s="68" t="n"/>
-      <c r="M11" s="68" t="n"/>
-      <c r="N11" s="68" t="n"/>
-      <c r="O11" s="68" t="n"/>
-      <c r="P11" s="68" t="n"/>
-      <c r="Q11" s="68" t="n"/>
-      <c r="R11" s="68" t="n"/>
-      <c r="S11" s="68" t="n"/>
-      <c r="T11" s="68" t="n"/>
-      <c r="U11" s="68" t="n"/>
-      <c r="V11" s="68" t="n"/>
-      <c r="W11" s="85" t="n"/>
-      <c r="X11" s="85" t="n"/>
-      <c r="Y11" s="85" t="n"/>
-      <c r="Z11" s="85" t="n"/>
-      <c r="AA11" s="85" t="n"/>
+    <row r="11" ht="15.5" customHeight="1" s="50">
+      <c r="A11" s="101" t="inlineStr">
+        <is>
+          <t>3. IT DR exercise name (column D): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B11" s="97" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="97" t="n"/>
+      <c r="E11" s="97" t="n"/>
+      <c r="F11" s="97" t="n"/>
+      <c r="G11" s="98" t="n"/>
       <c r="AB11" s="85" t="n"/>
       <c r="AC11" s="85" t="n"/>
       <c r="AD11" s="85" t="n"/>
@@ -11690,38 +11542,43 @@
       <c r="AX11" s="85" t="n"/>
       <c r="AY11" s="85" t="n"/>
     </row>
-    <row r="12" ht="15.5" customHeight="1" s="50">
-      <c r="A12" s="71" t="inlineStr">
-        <is>
-          <t>4. Business Tester (column E): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B12" s="97" t="n"/>
-      <c r="C12" s="97" t="n"/>
-      <c r="D12" s="97" t="n"/>
-      <c r="E12" s="97" t="n"/>
-      <c r="F12" s="97" t="n"/>
-      <c r="G12" s="98" t="n"/>
-      <c r="H12" s="68" t="n"/>
-      <c r="I12" s="68" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="68" t="n"/>
-      <c r="L12" s="68" t="n"/>
-      <c r="M12" s="68" t="n"/>
-      <c r="N12" s="68" t="n"/>
-      <c r="O12" s="68" t="n"/>
-      <c r="P12" s="68" t="n"/>
-      <c r="Q12" s="68" t="n"/>
-      <c r="R12" s="68" t="n"/>
-      <c r="S12" s="68" t="n"/>
-      <c r="T12" s="68" t="n"/>
-      <c r="U12" s="68" t="n"/>
-      <c r="V12" s="68" t="n"/>
-      <c r="W12" s="85" t="n"/>
-      <c r="X12" s="85" t="n"/>
-      <c r="Y12" s="85" t="n"/>
-      <c r="Z12" s="85" t="n"/>
-      <c r="AA12" s="85" t="n"/>
+    <row r="12" ht="26" customHeight="1" s="50">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B12" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C12" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D12" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E12" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F12" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G12" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H12" s="67" t="n"/>
       <c r="AB12" s="85" t="n"/>
       <c r="AC12" s="85" t="n"/>
       <c r="AD12" s="85" t="n"/>
@@ -11747,54 +11604,62 @@
       <c r="AX12" s="85" t="n"/>
       <c r="AY12" s="85" t="n"/>
     </row>
-    <row r="13" ht="26" customHeight="1" s="50">
-      <c r="A13" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B13" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C13" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D13" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E13" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F13" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G13" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H13" s="67" t="n"/>
-      <c r="Q13" s="68" t="n"/>
-      <c r="R13" s="68" t="n"/>
-      <c r="S13" s="68" t="n"/>
-      <c r="T13" s="68" t="n"/>
-      <c r="U13" s="68" t="n"/>
-      <c r="V13" s="68" t="n"/>
-      <c r="W13" s="85" t="n"/>
-      <c r="X13" s="85" t="n"/>
-      <c r="Y13" s="85" t="n"/>
-      <c r="Z13" s="85" t="n"/>
-      <c r="AA13" s="85" t="n"/>
+    <row r="13" ht="126" customHeight="1" s="50">
+      <c r="A13" s="78" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B13" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <v/>
+      </c>
+      <c r="C13" s="76" t="inlineStr">
+        <is>
+          <t>BCiC: Applications In Scope for DR Test BSI</t>
+        </is>
+      </c>
+      <c r="D13" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express (E01 row 3)
+1867 FedExport - BSI (E01 row 19)
+1868 FedImport - BSI (E01 row 20)
+3299 Imaging101 (E01 row 24)
+4052 Interface Monitor (E01 row 25)
+3301 MQ Payment Monitor (E01 row 31)
+1903 OFAC - BSI (E01 row 34)
+1917 ReconXpert (E01 row 36)
+1936 Swift Interface - BSI (E01 row 42)
+1937 T24 (E01 row 43)</t>
+        </is>
+      </c>
+      <c r="E13" s="76" t="inlineStr">
+        <is>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.
+Checked for IT DR exercise name:
+Exercise Date 12/11/25, 2025 DR Test Scope = True
+Exercise Date 11/15/25, 2025 DR Test Scope = True</t>
+        </is>
+      </c>
+      <c r="F13" s="76" t="inlineStr">
+        <is>
+          <t>Supports IT DR exercise name (column D), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G13" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H13" s="70" t="n"/>
+      <c r="I13" s="70" t="n"/>
+      <c r="J13" s="70" t="n"/>
+      <c r="K13" s="70" t="n"/>
+      <c r="L13" s="70" t="n"/>
+      <c r="M13" s="70" t="n"/>
+      <c r="N13" s="69" t="n"/>
+      <c r="O13" s="70" t="n"/>
+      <c r="P13" s="70" t="n"/>
       <c r="AB13" s="85" t="n"/>
       <c r="AC13" s="85" t="n"/>
       <c r="AD13" s="85" t="n"/>
@@ -11820,72 +11685,34 @@
       <c r="AX13" s="85" t="n"/>
       <c r="AY13" s="85" t="n"/>
     </row>
-    <row r="14" ht="174" customHeight="1" s="50">
-      <c r="A14" s="78" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B14" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
-      </c>
-      <c r="C14" s="76" t="inlineStr">
-        <is>
-          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
-        </is>
-      </c>
-      <c r="D14" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express (E03 row 47)
-1867 FedExport - BSI (E03 row 9)
-1868 FedImport - BSI (E03 row 10)
-3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
-4052 Interface Monitor (E03 row 61)
-3301 MQ Payment Monitor (E03 row 25, 29)
-1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
-1917 ReconXpert (E03 row 17)
-1936 Swift Interface - BSI (E03 row 7, 60)
-1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
-        </is>
-      </c>
-      <c r="E14" s="76" t="inlineStr">
-        <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
-Checked for Business Tester:
-'Business Tester(s)' column</t>
-        </is>
-      </c>
-      <c r="F14" s="76" t="inlineStr">
-        <is>
-          <t>Supports Business Tester (column E), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G14" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H14" s="70" t="n"/>
-      <c r="I14" s="70" t="n"/>
-      <c r="J14" s="70" t="n"/>
-      <c r="K14" s="70" t="n"/>
-      <c r="L14" s="70" t="n"/>
-      <c r="M14" s="69" t="n"/>
-      <c r="N14" s="70" t="n"/>
-      <c r="O14" s="70" t="n"/>
-      <c r="P14" s="70" t="n"/>
-      <c r="Q14" s="68" t="n"/>
-      <c r="R14" s="68" t="n"/>
-      <c r="S14" s="68" t="n"/>
-      <c r="T14" s="68" t="n"/>
-      <c r="U14" s="68" t="n"/>
-      <c r="V14" s="68" t="n"/>
-      <c r="W14" s="85" t="n"/>
-      <c r="X14" s="85" t="n"/>
-      <c r="Y14" s="85" t="n"/>
-      <c r="Z14" s="85" t="n"/>
-      <c r="AA14" s="85" t="n"/>
+    <row r="14" s="50">
+      <c r="A14" s="74" t="n"/>
+      <c r="B14" s="74" t="n"/>
+      <c r="C14" s="74" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="74" t="n"/>
+      <c r="G14" s="74" t="n"/>
+      <c r="H14" s="74" t="n"/>
+      <c r="I14" s="74" t="n"/>
+      <c r="J14" s="74" t="n"/>
+      <c r="K14" s="74" t="n"/>
+      <c r="L14" s="74" t="n"/>
+      <c r="M14" s="74" t="n"/>
+      <c r="N14" s="74" t="n"/>
+      <c r="O14" s="74" t="n"/>
+      <c r="P14" s="74" t="n"/>
+      <c r="Q14" s="74" t="n"/>
+      <c r="R14" s="74" t="n"/>
+      <c r="S14" s="74" t="n"/>
+      <c r="T14" s="74" t="n"/>
+      <c r="U14" s="74" t="n"/>
+      <c r="V14" s="74" t="n"/>
+      <c r="W14" s="74" t="n"/>
+      <c r="X14" s="74" t="n"/>
+      <c r="Y14" s="74" t="n"/>
+      <c r="Z14" s="74" t="n"/>
+      <c r="AA14" s="74" t="n"/>
       <c r="AB14" s="85" t="n"/>
       <c r="AC14" s="85" t="n"/>
       <c r="AD14" s="85" t="n"/>
@@ -11911,34 +11738,18 @@
       <c r="AX14" s="85" t="n"/>
       <c r="AY14" s="85" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="74" t="n"/>
-      <c r="B15" s="74" t="n"/>
-      <c r="C15" s="74" t="n"/>
-      <c r="D15" s="74" t="n"/>
-      <c r="E15" s="74" t="n"/>
-      <c r="F15" s="74" t="n"/>
-      <c r="G15" s="74" t="n"/>
-      <c r="H15" s="68" t="n"/>
-      <c r="I15" s="68" t="n"/>
-      <c r="J15" s="68" t="n"/>
-      <c r="K15" s="68" t="n"/>
-      <c r="L15" s="68" t="n"/>
-      <c r="M15" s="68" t="n"/>
-      <c r="N15" s="68" t="n"/>
-      <c r="O15" s="68" t="n"/>
-      <c r="P15" s="68" t="n"/>
-      <c r="Q15" s="68" t="n"/>
-      <c r="R15" s="68" t="n"/>
-      <c r="S15" s="68" t="n"/>
-      <c r="T15" s="68" t="n"/>
-      <c r="U15" s="68" t="n"/>
-      <c r="V15" s="68" t="n"/>
-      <c r="W15" s="85" t="n"/>
-      <c r="X15" s="85" t="n"/>
-      <c r="Y15" s="85" t="n"/>
-      <c r="Z15" s="85" t="n"/>
-      <c r="AA15" s="85" t="n"/>
+    <row r="15" ht="41" customHeight="1" s="50">
+      <c r="A15" s="101" t="inlineStr">
+        <is>
+          <t>4. IT DR exercise name, was the exercise annually executed? (column E): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B15" s="97" t="n"/>
+      <c r="C15" s="97" t="n"/>
+      <c r="D15" s="97" t="n"/>
+      <c r="E15" s="97" t="n"/>
+      <c r="F15" s="97" t="n"/>
+      <c r="G15" s="98" t="n"/>
       <c r="AB15" s="85" t="n"/>
       <c r="AC15" s="85" t="n"/>
       <c r="AD15" s="85" t="n"/>
@@ -11964,38 +11775,43 @@
       <c r="AX15" s="85" t="n"/>
       <c r="AY15" s="85" t="n"/>
     </row>
-    <row r="16" ht="15.5" customHeight="1" s="50">
-      <c r="A16" s="71" t="inlineStr">
-        <is>
-          <t>5. Business Data validation (column F): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B16" s="97" t="n"/>
-      <c r="C16" s="97" t="n"/>
-      <c r="D16" s="97" t="n"/>
-      <c r="E16" s="97" t="n"/>
-      <c r="F16" s="97" t="n"/>
-      <c r="G16" s="98" t="n"/>
-      <c r="H16" s="68" t="n"/>
-      <c r="I16" s="68" t="n"/>
-      <c r="J16" s="68" t="n"/>
-      <c r="K16" s="68" t="n"/>
-      <c r="L16" s="68" t="n"/>
-      <c r="M16" s="68" t="n"/>
-      <c r="N16" s="68" t="n"/>
-      <c r="O16" s="68" t="n"/>
-      <c r="P16" s="68" t="n"/>
-      <c r="Q16" s="68" t="n"/>
-      <c r="R16" s="68" t="n"/>
-      <c r="S16" s="68" t="n"/>
-      <c r="T16" s="68" t="n"/>
-      <c r="U16" s="68" t="n"/>
-      <c r="V16" s="68" t="n"/>
-      <c r="W16" s="85" t="n"/>
-      <c r="X16" s="85" t="n"/>
-      <c r="Y16" s="85" t="n"/>
-      <c r="Z16" s="85" t="n"/>
-      <c r="AA16" s="85" t="n"/>
+    <row r="16" ht="26" customHeight="1" s="50">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C16" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D16" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E16" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F16" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G16" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H16" s="67" t="n"/>
       <c r="AB16" s="85" t="n"/>
       <c r="AC16" s="85" t="n"/>
       <c r="AD16" s="85" t="n"/>
@@ -12021,53 +11837,64 @@
       <c r="AX16" s="85" t="n"/>
       <c r="AY16" s="85" t="n"/>
     </row>
-    <row r="17" ht="26" customHeight="1" s="50">
-      <c r="A17" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B17" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C17" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D17" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E17" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F17" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G17" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H17" s="67" t="n"/>
-      <c r="R17" s="68" t="n"/>
-      <c r="S17" s="68" t="n"/>
-      <c r="T17" s="68" t="n"/>
-      <c r="U17" s="68" t="n"/>
-      <c r="V17" s="68" t="n"/>
-      <c r="W17" s="85" t="n"/>
-      <c r="X17" s="85" t="n"/>
-      <c r="Y17" s="85" t="n"/>
-      <c r="Z17" s="85" t="n"/>
-      <c r="AA17" s="85" t="n"/>
+    <row r="17" ht="126" customHeight="1" s="50">
+      <c r="A17" s="78" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B17" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <v/>
+      </c>
+      <c r="C17" s="76" t="inlineStr">
+        <is>
+          <t>BCiC: Applications In Scope for DR Test BSI</t>
+        </is>
+      </c>
+      <c r="D17" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express (E01 row 3)
+1867 FedExport - BSI (E01 row 19)
+1868 FedImport - BSI (E01 row 20)
+3299 Imaging101 (E01 row 24)
+4052 Interface Monitor (E01 row 25)
+3301 MQ Payment Monitor (E01 row 31)
+1903 OFAC - BSI (E01 row 34)
+1917 ReconXpert (E01 row 36)
+1936 Swift Interface - BSI (E01 row 42)
+1937 T24 (E01 row 43)</t>
+        </is>
+      </c>
+      <c r="E17" s="76" t="inlineStr">
+        <is>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.
+Checked for IT DR exercise name, was the exercise annually executed?
+Exercise Date 12/11/2025 / 2025 DR Test Scope = True
+Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+2025 cycle: BSI IT DR Exercise 11/15/2025 (within the review period 08/01/2025 to 06/01/2026).
+2024 cycle: 2024 Full 2024 DR Test (Virginia) 10/19/2024, see tab 'DR 2024 Testing Results'.
+Interval 10/19/2024 to 11/15/2025 = 392 days; one DR / DIV exercise in each annual cycle.</t>
+        </is>
+      </c>
+      <c r="F17" s="76" t="inlineStr">
+        <is>
+          <t>Supports IT DR exercise name, was the exercise annually executed? (column E), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G17" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H17" s="70" t="n"/>
+      <c r="I17" s="70" t="n"/>
+      <c r="J17" s="70" t="n"/>
+      <c r="K17" s="70" t="n"/>
+      <c r="L17" s="70" t="n"/>
+      <c r="M17" s="70" t="n"/>
+      <c r="N17" s="69" t="n"/>
+      <c r="O17" s="70" t="n"/>
       <c r="AB17" s="85" t="n"/>
       <c r="AC17" s="85" t="n"/>
       <c r="AD17" s="85" t="n"/>
@@ -12093,72 +11920,34 @@
       <c r="AX17" s="85" t="n"/>
       <c r="AY17" s="85" t="n"/>
     </row>
-    <row r="18" ht="174" customHeight="1" s="50">
-      <c r="A18" s="78" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B18" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
-      </c>
-      <c r="C18" s="76" t="inlineStr">
-        <is>
-          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
-        </is>
-      </c>
-      <c r="D18" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express (E03 row 47)
-1867 FedExport - BSI (E03 row 9)
-1868 FedImport - BSI (E03 row 10)
-3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
-4052 Interface Monitor (E03 row 61)
-3301 MQ Payment Monitor (E03 row 25, 29)
-1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
-1917 ReconXpert (E03 row 17)
-1936 Swift Interface - BSI (E03 row 7, 60)
-1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
-        </is>
-      </c>
-      <c r="E18" s="76" t="inlineStr">
-        <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
-Checked for Business Data validation:
-Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y</t>
-        </is>
-      </c>
-      <c r="F18" s="76" t="inlineStr">
-        <is>
-          <t>Supports Business Data validation (column F), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G18" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H18" s="70" t="n"/>
-      <c r="I18" s="70" t="n"/>
-      <c r="J18" s="70" t="n"/>
-      <c r="K18" s="70" t="n"/>
-      <c r="L18" s="70" t="n"/>
-      <c r="M18" s="69" t="n"/>
-      <c r="N18" s="70" t="n"/>
-      <c r="O18" s="70" t="n"/>
-      <c r="P18" s="70" t="n"/>
-      <c r="Q18" s="70" t="n"/>
-      <c r="R18" s="68" t="n"/>
-      <c r="S18" s="68" t="n"/>
-      <c r="T18" s="68" t="n"/>
-      <c r="U18" s="68" t="n"/>
-      <c r="V18" s="68" t="n"/>
-      <c r="W18" s="85" t="n"/>
-      <c r="X18" s="85" t="n"/>
-      <c r="Y18" s="85" t="n"/>
-      <c r="Z18" s="85" t="n"/>
-      <c r="AA18" s="85" t="n"/>
+    <row r="18" s="50">
+      <c r="A18" s="74" t="n"/>
+      <c r="B18" s="74" t="n"/>
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="74" t="n"/>
+      <c r="G18" s="74" t="n"/>
+      <c r="H18" s="74" t="n"/>
+      <c r="I18" s="74" t="n"/>
+      <c r="J18" s="74" t="n"/>
+      <c r="K18" s="74" t="n"/>
+      <c r="L18" s="74" t="n"/>
+      <c r="M18" s="74" t="n"/>
+      <c r="N18" s="74" t="n"/>
+      <c r="O18" s="74" t="n"/>
+      <c r="P18" s="74" t="n"/>
+      <c r="Q18" s="74" t="n"/>
+      <c r="R18" s="74" t="n"/>
+      <c r="S18" s="74" t="n"/>
+      <c r="T18" s="74" t="n"/>
+      <c r="U18" s="74" t="n"/>
+      <c r="V18" s="74" t="n"/>
+      <c r="W18" s="74" t="n"/>
+      <c r="X18" s="74" t="n"/>
+      <c r="Y18" s="74" t="n"/>
+      <c r="Z18" s="74" t="n"/>
+      <c r="AA18" s="74" t="n"/>
       <c r="AB18" s="85" t="n"/>
       <c r="AC18" s="85" t="n"/>
       <c r="AD18" s="85" t="n"/>
@@ -12184,34 +11973,18 @@
       <c r="AX18" s="85" t="n"/>
       <c r="AY18" s="85" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="74" t="n"/>
-      <c r="B19" s="74" t="n"/>
-      <c r="C19" s="74" t="n"/>
-      <c r="D19" s="74" t="n"/>
-      <c r="E19" s="74" t="n"/>
-      <c r="F19" s="74" t="n"/>
-      <c r="G19" s="74" t="n"/>
-      <c r="H19" s="68" t="n"/>
-      <c r="I19" s="68" t="n"/>
-      <c r="J19" s="68" t="n"/>
-      <c r="K19" s="68" t="n"/>
-      <c r="L19" s="68" t="n"/>
-      <c r="M19" s="68" t="n"/>
-      <c r="N19" s="68" t="n"/>
-      <c r="O19" s="68" t="n"/>
-      <c r="P19" s="68" t="n"/>
-      <c r="Q19" s="68" t="n"/>
-      <c r="R19" s="68" t="n"/>
-      <c r="S19" s="68" t="n"/>
-      <c r="T19" s="68" t="n"/>
-      <c r="U19" s="68" t="n"/>
-      <c r="V19" s="68" t="n"/>
-      <c r="W19" s="85" t="n"/>
-      <c r="X19" s="85" t="n"/>
-      <c r="Y19" s="85" t="n"/>
-      <c r="Z19" s="85" t="n"/>
-      <c r="AA19" s="85" t="n"/>
+    <row r="19" ht="15.5" customHeight="1" s="50">
+      <c r="A19" s="101" t="inlineStr">
+        <is>
+          <t>5. Business Tester (column F): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B19" s="97" t="n"/>
+      <c r="C19" s="97" t="n"/>
+      <c r="D19" s="97" t="n"/>
+      <c r="E19" s="97" t="n"/>
+      <c r="F19" s="97" t="n"/>
+      <c r="G19" s="98" t="n"/>
       <c r="AB19" s="85" t="n"/>
       <c r="AC19" s="85" t="n"/>
       <c r="AD19" s="85" t="n"/>
@@ -12237,38 +12010,43 @@
       <c r="AX19" s="85" t="n"/>
       <c r="AY19" s="85" t="n"/>
     </row>
-    <row r="20" ht="15.5" customHeight="1" s="50">
-      <c r="A20" s="71" t="inlineStr">
-        <is>
-          <t>6. Business line manager name (column G): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B20" s="97" t="n"/>
-      <c r="C20" s="97" t="n"/>
-      <c r="D20" s="97" t="n"/>
-      <c r="E20" s="97" t="n"/>
-      <c r="F20" s="97" t="n"/>
-      <c r="G20" s="98" t="n"/>
-      <c r="H20" s="68" t="n"/>
-      <c r="I20" s="68" t="n"/>
-      <c r="J20" s="68" t="n"/>
-      <c r="K20" s="68" t="n"/>
-      <c r="L20" s="68" t="n"/>
-      <c r="M20" s="68" t="n"/>
-      <c r="N20" s="68" t="n"/>
-      <c r="O20" s="68" t="n"/>
-      <c r="P20" s="68" t="n"/>
-      <c r="Q20" s="68" t="n"/>
-      <c r="R20" s="68" t="n"/>
-      <c r="S20" s="68" t="n"/>
-      <c r="T20" s="68" t="n"/>
-      <c r="U20" s="68" t="n"/>
-      <c r="V20" s="68" t="n"/>
-      <c r="W20" s="85" t="n"/>
-      <c r="X20" s="85" t="n"/>
-      <c r="Y20" s="85" t="n"/>
-      <c r="Z20" s="85" t="n"/>
-      <c r="AA20" s="85" t="n"/>
+    <row r="20" ht="26" customHeight="1" s="50">
+      <c r="A20" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D20" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E20" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F20" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G20" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H20" s="67" t="n"/>
       <c r="AB20" s="85" t="n"/>
       <c r="AC20" s="85" t="n"/>
       <c r="AD20" s="85" t="n"/>
@@ -12294,47 +12072,61 @@
       <c r="AX20" s="85" t="n"/>
       <c r="AY20" s="85" t="n"/>
     </row>
-    <row r="21" ht="26" customHeight="1" s="50">
-      <c r="A21" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B21" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C21" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D21" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E21" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F21" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G21" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H21" s="67" t="n"/>
-      <c r="X21" s="85" t="n"/>
-      <c r="Y21" s="85" t="n"/>
-      <c r="Z21" s="85" t="n"/>
-      <c r="AA21" s="85" t="n"/>
+    <row r="21" ht="174" customHeight="1" s="50">
+      <c r="A21" s="78" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B21" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
+      </c>
+      <c r="C21" s="76" t="inlineStr">
+        <is>
+          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
+        </is>
+      </c>
+      <c r="D21" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express (E03 row 47)
+1867 FedExport - BSI (E03 row 9)
+1868 FedImport - BSI (E03 row 10)
+3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
+4052 Interface Monitor (E03 row 61)
+3301 MQ Payment Monitor (E03 row 25, 29)
+1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
+1917 ReconXpert (E03 row 17)
+1936 Swift Interface - BSI (E03 row 7, 60)
+1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
+        </is>
+      </c>
+      <c r="E21" s="76" t="inlineStr">
+        <is>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+Checked for Business Tester:
+'Business Tester(s)' column</t>
+        </is>
+      </c>
+      <c r="F21" s="76" t="inlineStr">
+        <is>
+          <t>Supports Business Tester (column F), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G21" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H21" s="70" t="n"/>
+      <c r="I21" s="70" t="n"/>
+      <c r="J21" s="70" t="n"/>
+      <c r="K21" s="70" t="n"/>
+      <c r="L21" s="70" t="n"/>
+      <c r="M21" s="69" t="n"/>
+      <c r="N21" s="70" t="n"/>
+      <c r="O21" s="70" t="n"/>
+      <c r="P21" s="70" t="n"/>
       <c r="AB21" s="85" t="n"/>
       <c r="AC21" s="85" t="n"/>
       <c r="AD21" s="85" t="n"/>
@@ -12360,72 +12152,34 @@
       <c r="AX21" s="85" t="n"/>
       <c r="AY21" s="85" t="n"/>
     </row>
-    <row r="22" ht="174" customHeight="1" s="50">
-      <c r="A22" s="78" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B22" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
-      </c>
-      <c r="C22" s="76" t="inlineStr">
-        <is>
-          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
-        </is>
-      </c>
-      <c r="D22" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express (E03 row 47)
-1867 FedExport - BSI (E03 row 9)
-1868 FedImport - BSI (E03 row 10)
-3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
-4052 Interface Monitor (E03 row 61)
-3301 MQ Payment Monitor (E03 row 25, 29)
-1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
-1917 ReconXpert (E03 row 17)
-1936 Swift Interface - BSI (E03 row 7, 60)
-1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
-        </is>
-      </c>
-      <c r="E22" s="76" t="inlineStr">
-        <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
-Checked for Business line manager name:
-'Department Manager' column</t>
-        </is>
-      </c>
-      <c r="F22" s="76" t="inlineStr">
-        <is>
-          <t>Supports Business line manager name (column G), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G22" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H22" s="70" t="n"/>
-      <c r="I22" s="70" t="n"/>
-      <c r="J22" s="70" t="n"/>
-      <c r="K22" s="70" t="n"/>
-      <c r="L22" s="70" t="n"/>
-      <c r="M22" s="70" t="n"/>
-      <c r="N22" s="70" t="n"/>
-      <c r="O22" s="70" t="n"/>
-      <c r="P22" s="70" t="n"/>
-      <c r="Q22" s="70" t="n"/>
-      <c r="R22" s="70" t="n"/>
-      <c r="S22" s="70" t="n"/>
-      <c r="T22" s="70" t="n"/>
-      <c r="U22" s="69" t="n"/>
-      <c r="V22" s="86" t="n"/>
-      <c r="W22" s="87" t="n"/>
-      <c r="X22" s="85" t="n"/>
-      <c r="Y22" s="85" t="n"/>
-      <c r="Z22" s="85" t="n"/>
-      <c r="AA22" s="85" t="n"/>
+    <row r="22" s="50">
+      <c r="A22" s="74" t="n"/>
+      <c r="B22" s="74" t="n"/>
+      <c r="C22" s="74" t="n"/>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="74" t="n"/>
+      <c r="F22" s="74" t="n"/>
+      <c r="G22" s="74" t="n"/>
+      <c r="H22" s="74" t="n"/>
+      <c r="I22" s="74" t="n"/>
+      <c r="J22" s="74" t="n"/>
+      <c r="K22" s="74" t="n"/>
+      <c r="L22" s="74" t="n"/>
+      <c r="M22" s="74" t="n"/>
+      <c r="N22" s="74" t="n"/>
+      <c r="O22" s="74" t="n"/>
+      <c r="P22" s="74" t="n"/>
+      <c r="Q22" s="74" t="n"/>
+      <c r="R22" s="74" t="n"/>
+      <c r="S22" s="74" t="n"/>
+      <c r="T22" s="74" t="n"/>
+      <c r="U22" s="74" t="n"/>
+      <c r="V22" s="74" t="n"/>
+      <c r="W22" s="74" t="n"/>
+      <c r="X22" s="74" t="n"/>
+      <c r="Y22" s="74" t="n"/>
+      <c r="Z22" s="74" t="n"/>
+      <c r="AA22" s="74" t="n"/>
       <c r="AB22" s="85" t="n"/>
       <c r="AC22" s="85" t="n"/>
       <c r="AD22" s="85" t="n"/>
@@ -12451,34 +12205,18 @@
       <c r="AX22" s="85" t="n"/>
       <c r="AY22" s="85" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="74" t="n"/>
-      <c r="B23" s="74" t="n"/>
-      <c r="C23" s="74" t="n"/>
-      <c r="D23" s="74" t="n"/>
-      <c r="E23" s="74" t="n"/>
-      <c r="F23" s="74" t="n"/>
-      <c r="G23" s="74" t="n"/>
-      <c r="H23" s="68" t="n"/>
-      <c r="I23" s="68" t="n"/>
-      <c r="J23" s="68" t="n"/>
-      <c r="K23" s="68" t="n"/>
-      <c r="L23" s="68" t="n"/>
-      <c r="M23" s="68" t="n"/>
-      <c r="N23" s="68" t="n"/>
-      <c r="O23" s="68" t="n"/>
-      <c r="P23" s="68" t="n"/>
-      <c r="Q23" s="68" t="n"/>
-      <c r="R23" s="68" t="n"/>
-      <c r="S23" s="68" t="n"/>
-      <c r="T23" s="68" t="n"/>
-      <c r="U23" s="68" t="n"/>
-      <c r="V23" s="68" t="n"/>
-      <c r="W23" s="85" t="n"/>
-      <c r="X23" s="85" t="n"/>
-      <c r="Y23" s="85" t="n"/>
-      <c r="Z23" s="85" t="n"/>
-      <c r="AA23" s="85" t="n"/>
+    <row r="23" ht="15.5" customHeight="1" s="50">
+      <c r="A23" s="101" t="inlineStr">
+        <is>
+          <t>6. Business Data validation (column G): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B23" s="97" t="n"/>
+      <c r="C23" s="97" t="n"/>
+      <c r="D23" s="97" t="n"/>
+      <c r="E23" s="97" t="n"/>
+      <c r="F23" s="97" t="n"/>
+      <c r="G23" s="98" t="n"/>
       <c r="AB23" s="85" t="n"/>
       <c r="AC23" s="85" t="n"/>
       <c r="AD23" s="85" t="n"/>
@@ -12504,38 +12242,43 @@
       <c r="AX23" s="85" t="n"/>
       <c r="AY23" s="85" t="n"/>
     </row>
-    <row r="24" ht="15.5" customHeight="1" s="50">
-      <c r="A24" s="71" t="inlineStr">
-        <is>
-          <t>7. Business line manager approval dates (column H): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B24" s="97" t="n"/>
-      <c r="C24" s="97" t="n"/>
-      <c r="D24" s="97" t="n"/>
-      <c r="E24" s="97" t="n"/>
-      <c r="F24" s="97" t="n"/>
-      <c r="G24" s="98" t="n"/>
-      <c r="H24" s="68" t="n"/>
-      <c r="I24" s="68" t="n"/>
-      <c r="J24" s="68" t="n"/>
-      <c r="K24" s="68" t="n"/>
-      <c r="L24" s="68" t="n"/>
-      <c r="M24" s="68" t="n"/>
-      <c r="N24" s="68" t="n"/>
-      <c r="O24" s="68" t="n"/>
-      <c r="P24" s="68" t="n"/>
-      <c r="Q24" s="68" t="n"/>
-      <c r="R24" s="68" t="n"/>
-      <c r="S24" s="68" t="n"/>
-      <c r="T24" s="68" t="n"/>
-      <c r="U24" s="68" t="n"/>
-      <c r="V24" s="68" t="n"/>
-      <c r="W24" s="85" t="n"/>
-      <c r="X24" s="85" t="n"/>
-      <c r="Y24" s="85" t="n"/>
-      <c r="Z24" s="85" t="n"/>
-      <c r="AA24" s="85" t="n"/>
+    <row r="24" ht="26" customHeight="1" s="50">
+      <c r="A24" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B24" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C24" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D24" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E24" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G24" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H24" s="67" t="n"/>
       <c r="AB24" s="85" t="n"/>
       <c r="AC24" s="85" t="n"/>
       <c r="AD24" s="85" t="n"/>
@@ -12561,47 +12304,62 @@
       <c r="AX24" s="85" t="n"/>
       <c r="AY24" s="85" t="n"/>
     </row>
-    <row r="25" ht="26" customHeight="1" s="50">
-      <c r="A25" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B25" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C25" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D25" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E25" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F25" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G25" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H25" s="67" t="n"/>
-      <c r="X25" s="85" t="n"/>
-      <c r="Y25" s="85" t="n"/>
-      <c r="Z25" s="85" t="n"/>
-      <c r="AA25" s="85" t="n"/>
+    <row r="25" ht="174" customHeight="1" s="50">
+      <c r="A25" s="78" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B25" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
+      </c>
+      <c r="C25" s="76" t="inlineStr">
+        <is>
+          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
+        </is>
+      </c>
+      <c r="D25" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express (E03 row 47)
+1867 FedExport - BSI (E03 row 9)
+1868 FedImport - BSI (E03 row 10)
+3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
+4052 Interface Monitor (E03 row 61)
+3301 MQ Payment Monitor (E03 row 25, 29)
+1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
+1917 ReconXpert (E03 row 17)
+1936 Swift Interface - BSI (E03 row 7, 60)
+1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
+        </is>
+      </c>
+      <c r="E25" s="76" t="inlineStr">
+        <is>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+Checked for Business Data validation:
+Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y</t>
+        </is>
+      </c>
+      <c r="F25" s="76" t="inlineStr">
+        <is>
+          <t>Supports Business Data validation (column G), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G25" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H25" s="70" t="n"/>
+      <c r="I25" s="70" t="n"/>
+      <c r="J25" s="70" t="n"/>
+      <c r="K25" s="70" t="n"/>
+      <c r="L25" s="70" t="n"/>
+      <c r="M25" s="69" t="n"/>
+      <c r="N25" s="70" t="n"/>
+      <c r="O25" s="70" t="n"/>
+      <c r="P25" s="70" t="n"/>
+      <c r="Q25" s="70" t="n"/>
       <c r="AB25" s="85" t="n"/>
       <c r="AC25" s="85" t="n"/>
       <c r="AD25" s="85" t="n"/>
@@ -12627,72 +12385,34 @@
       <c r="AX25" s="85" t="n"/>
       <c r="AY25" s="85" t="n"/>
     </row>
-    <row r="26" ht="174" customHeight="1" s="50">
-      <c r="A26" s="78" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B26" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
-      </c>
-      <c r="C26" s="76" t="inlineStr">
-        <is>
-          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
-        </is>
-      </c>
-      <c r="D26" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express (E03 row 47)
-1867 FedExport - BSI (E03 row 9)
-1868 FedImport - BSI (E03 row 10)
-3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
-4052 Interface Monitor (E03 row 61)
-3301 MQ Payment Monitor (E03 row 25, 29)
-1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
-1917 ReconXpert (E03 row 17)
-1936 Swift Interface - BSI (E03 row 7, 60)
-1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
-        </is>
-      </c>
-      <c r="E26" s="76" t="inlineStr">
-        <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
-Checked for Business line manager approval dates:
-'Department Manager Approval Date' and 'Attestation Date' columns</t>
-        </is>
-      </c>
-      <c r="F26" s="76" t="inlineStr">
-        <is>
-          <t>Supports Business line manager approval dates (column H), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G26" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H26" s="70" t="n"/>
-      <c r="I26" s="70" t="n"/>
-      <c r="J26" s="70" t="n"/>
-      <c r="K26" s="70" t="n"/>
-      <c r="L26" s="70" t="n"/>
-      <c r="M26" s="70" t="n"/>
-      <c r="N26" s="70" t="n"/>
-      <c r="O26" s="70" t="n"/>
-      <c r="P26" s="70" t="n"/>
-      <c r="Q26" s="70" t="n"/>
-      <c r="R26" s="70" t="n"/>
-      <c r="S26" s="70" t="n"/>
-      <c r="T26" s="70" t="n"/>
-      <c r="U26" s="69" t="n"/>
-      <c r="V26" s="86" t="n"/>
-      <c r="W26" s="87" t="n"/>
-      <c r="X26" s="85" t="n"/>
-      <c r="Y26" s="85" t="n"/>
-      <c r="Z26" s="85" t="n"/>
-      <c r="AA26" s="85" t="n"/>
+    <row r="26" s="50">
+      <c r="A26" s="74" t="n"/>
+      <c r="B26" s="74" t="n"/>
+      <c r="C26" s="74" t="n"/>
+      <c r="D26" s="74" t="n"/>
+      <c r="E26" s="74" t="n"/>
+      <c r="F26" s="74" t="n"/>
+      <c r="G26" s="74" t="n"/>
+      <c r="H26" s="74" t="n"/>
+      <c r="I26" s="74" t="n"/>
+      <c r="J26" s="74" t="n"/>
+      <c r="K26" s="74" t="n"/>
+      <c r="L26" s="74" t="n"/>
+      <c r="M26" s="74" t="n"/>
+      <c r="N26" s="74" t="n"/>
+      <c r="O26" s="74" t="n"/>
+      <c r="P26" s="74" t="n"/>
+      <c r="Q26" s="74" t="n"/>
+      <c r="R26" s="74" t="n"/>
+      <c r="S26" s="74" t="n"/>
+      <c r="T26" s="74" t="n"/>
+      <c r="U26" s="74" t="n"/>
+      <c r="V26" s="74" t="n"/>
+      <c r="W26" s="74" t="n"/>
+      <c r="X26" s="74" t="n"/>
+      <c r="Y26" s="74" t="n"/>
+      <c r="Z26" s="74" t="n"/>
+      <c r="AA26" s="74" t="n"/>
       <c r="AB26" s="85" t="n"/>
       <c r="AC26" s="85" t="n"/>
       <c r="AD26" s="85" t="n"/>
@@ -12718,34 +12438,18 @@
       <c r="AX26" s="85" t="n"/>
       <c r="AY26" s="85" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="74" t="n"/>
-      <c r="B27" s="74" t="n"/>
-      <c r="C27" s="74" t="n"/>
-      <c r="D27" s="74" t="n"/>
-      <c r="E27" s="74" t="n"/>
-      <c r="F27" s="74" t="n"/>
-      <c r="G27" s="74" t="n"/>
-      <c r="H27" s="68" t="n"/>
-      <c r="I27" s="68" t="n"/>
-      <c r="J27" s="68" t="n"/>
-      <c r="K27" s="68" t="n"/>
-      <c r="L27" s="68" t="n"/>
-      <c r="M27" s="68" t="n"/>
-      <c r="N27" s="68" t="n"/>
-      <c r="O27" s="68" t="n"/>
-      <c r="P27" s="68" t="n"/>
-      <c r="Q27" s="68" t="n"/>
-      <c r="R27" s="68" t="n"/>
-      <c r="S27" s="68" t="n"/>
-      <c r="T27" s="68" t="n"/>
-      <c r="U27" s="68" t="n"/>
-      <c r="V27" s="68" t="n"/>
-      <c r="W27" s="85" t="n"/>
-      <c r="X27" s="85" t="n"/>
-      <c r="Y27" s="85" t="n"/>
-      <c r="Z27" s="85" t="n"/>
-      <c r="AA27" s="85" t="n"/>
+    <row r="27" ht="15.5" customHeight="1" s="50">
+      <c r="A27" s="101" t="inlineStr">
+        <is>
+          <t>7. Business line manager name (column H): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B27" s="97" t="n"/>
+      <c r="C27" s="97" t="n"/>
+      <c r="D27" s="97" t="n"/>
+      <c r="E27" s="97" t="n"/>
+      <c r="F27" s="97" t="n"/>
+      <c r="G27" s="98" t="n"/>
       <c r="AB27" s="85" t="n"/>
       <c r="AC27" s="85" t="n"/>
       <c r="AD27" s="85" t="n"/>
@@ -12771,38 +12475,43 @@
       <c r="AX27" s="85" t="n"/>
       <c r="AY27" s="85" t="n"/>
     </row>
-    <row r="28" ht="15.5" customHeight="1" s="50">
-      <c r="A28" s="71" t="inlineStr">
-        <is>
-          <t>8. DIV Test procedures listed within the Test results document (column I): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B28" s="97" t="n"/>
-      <c r="C28" s="97" t="n"/>
-      <c r="D28" s="97" t="n"/>
-      <c r="E28" s="97" t="n"/>
-      <c r="F28" s="97" t="n"/>
-      <c r="G28" s="98" t="n"/>
-      <c r="H28" s="68" t="n"/>
-      <c r="I28" s="68" t="n"/>
-      <c r="J28" s="68" t="n"/>
-      <c r="K28" s="68" t="n"/>
-      <c r="L28" s="68" t="n"/>
-      <c r="M28" s="68" t="n"/>
-      <c r="N28" s="68" t="n"/>
-      <c r="O28" s="68" t="n"/>
-      <c r="P28" s="68" t="n"/>
-      <c r="Q28" s="68" t="n"/>
-      <c r="R28" s="68" t="n"/>
-      <c r="S28" s="68" t="n"/>
-      <c r="T28" s="68" t="n"/>
-      <c r="U28" s="68" t="n"/>
-      <c r="V28" s="68" t="n"/>
-      <c r="W28" s="85" t="n"/>
-      <c r="X28" s="85" t="n"/>
-      <c r="Y28" s="85" t="n"/>
-      <c r="Z28" s="85" t="n"/>
-      <c r="AA28" s="85" t="n"/>
+    <row r="28" ht="26" customHeight="1" s="50">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B28" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C28" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D28" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E28" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F28" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G28" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H28" s="67" t="n"/>
       <c r="AB28" s="85" t="n"/>
       <c r="AC28" s="85" t="n"/>
       <c r="AD28" s="85" t="n"/>
@@ -12828,56 +12537,68 @@
       <c r="AX28" s="85" t="n"/>
       <c r="AY28" s="85" t="n"/>
     </row>
-    <row r="29" ht="26" customHeight="1" s="50">
-      <c r="A29" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B29" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C29" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D29" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E29" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F29" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G29" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H29" s="67" t="n"/>
-      <c r="O29" s="68" t="n"/>
-      <c r="P29" s="68" t="n"/>
-      <c r="Q29" s="68" t="n"/>
-      <c r="R29" s="68" t="n"/>
-      <c r="S29" s="68" t="n"/>
-      <c r="T29" s="68" t="n"/>
-      <c r="U29" s="68" t="n"/>
-      <c r="V29" s="68" t="n"/>
-      <c r="W29" s="85" t="n"/>
-      <c r="X29" s="85" t="n"/>
-      <c r="Y29" s="85" t="n"/>
-      <c r="Z29" s="85" t="n"/>
-      <c r="AA29" s="85" t="n"/>
+    <row r="29" ht="174" customHeight="1" s="50">
+      <c r="A29" s="78" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B29" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
+      </c>
+      <c r="C29" s="76" t="inlineStr">
+        <is>
+          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
+        </is>
+      </c>
+      <c r="D29" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express (E03 row 47)
+1867 FedExport - BSI (E03 row 9)
+1868 FedImport - BSI (E03 row 10)
+3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
+4052 Interface Monitor (E03 row 61)
+3301 MQ Payment Monitor (E03 row 25, 29)
+1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
+1917 ReconXpert (E03 row 17)
+1936 Swift Interface - BSI (E03 row 7, 60)
+1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
+        </is>
+      </c>
+      <c r="E29" s="76" t="inlineStr">
+        <is>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+Checked for Business line manager name:
+'Department Manager' column</t>
+        </is>
+      </c>
+      <c r="F29" s="76" t="inlineStr">
+        <is>
+          <t>Supports Business line manager name (column H), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G29" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H29" s="70" t="n"/>
+      <c r="I29" s="70" t="n"/>
+      <c r="J29" s="70" t="n"/>
+      <c r="K29" s="70" t="n"/>
+      <c r="L29" s="70" t="n"/>
+      <c r="M29" s="70" t="n"/>
+      <c r="N29" s="70" t="n"/>
+      <c r="O29" s="70" t="n"/>
+      <c r="P29" s="70" t="n"/>
+      <c r="Q29" s="70" t="n"/>
+      <c r="R29" s="70" t="n"/>
+      <c r="S29" s="70" t="n"/>
+      <c r="T29" s="70" t="n"/>
+      <c r="U29" s="69" t="n"/>
+      <c r="V29" s="86" t="n"/>
+      <c r="W29" s="87" t="n"/>
       <c r="AB29" s="85" t="n"/>
       <c r="AC29" s="85" t="n"/>
       <c r="AD29" s="85" t="n"/>
@@ -12903,72 +12624,34 @@
       <c r="AX29" s="85" t="n"/>
       <c r="AY29" s="85" t="n"/>
     </row>
-    <row r="30" ht="174" customHeight="1" s="50">
-      <c r="A30" s="78" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-      <c r="B30" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
-        <v/>
-      </c>
-      <c r="C30" s="76" t="inlineStr">
-        <is>
-          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
-        </is>
-      </c>
-      <c r="D30" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express (E03 row 47)
-1867 FedExport - BSI (E03 row 9)
-1868 FedImport - BSI (E03 row 10)
-3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
-4052 Interface Monitor (E03 row 61)
-3301 MQ Payment Monitor (E03 row 25, 29)
-1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
-1917 ReconXpert (E03 row 17)
-1936 Swift Interface - BSI (E03 row 7, 60)
-1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
-        </is>
-      </c>
-      <c r="E30" s="76" t="inlineStr">
-        <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
-Checked for DIV Test procedures listed within the Test results document:
-'Data Integrity Validation Procedures' column</t>
-        </is>
-      </c>
-      <c r="F30" s="76" t="inlineStr">
-        <is>
-          <t>Supports DIV Test procedures listed within the Test results document (column I), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G30" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H30" s="70" t="n"/>
-      <c r="I30" s="70" t="n"/>
-      <c r="J30" s="70" t="n"/>
-      <c r="K30" s="70" t="n"/>
-      <c r="L30" s="70" t="n"/>
-      <c r="M30" s="69" t="n"/>
-      <c r="N30" s="70" t="n"/>
-      <c r="O30" s="68" t="n"/>
-      <c r="P30" s="68" t="n"/>
-      <c r="Q30" s="68" t="n"/>
-      <c r="R30" s="68" t="n"/>
-      <c r="S30" s="68" t="n"/>
-      <c r="T30" s="68" t="n"/>
-      <c r="U30" s="68" t="n"/>
-      <c r="V30" s="68" t="n"/>
-      <c r="W30" s="85" t="n"/>
-      <c r="X30" s="85" t="n"/>
-      <c r="Y30" s="85" t="n"/>
-      <c r="Z30" s="85" t="n"/>
-      <c r="AA30" s="85" t="n"/>
+    <row r="30" s="50">
+      <c r="A30" s="74" t="n"/>
+      <c r="B30" s="74" t="n"/>
+      <c r="C30" s="74" t="n"/>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="74" t="n"/>
+      <c r="F30" s="74" t="n"/>
+      <c r="G30" s="74" t="n"/>
+      <c r="H30" s="74" t="n"/>
+      <c r="I30" s="74" t="n"/>
+      <c r="J30" s="74" t="n"/>
+      <c r="K30" s="74" t="n"/>
+      <c r="L30" s="74" t="n"/>
+      <c r="M30" s="74" t="n"/>
+      <c r="N30" s="74" t="n"/>
+      <c r="O30" s="74" t="n"/>
+      <c r="P30" s="74" t="n"/>
+      <c r="Q30" s="74" t="n"/>
+      <c r="R30" s="74" t="n"/>
+      <c r="S30" s="74" t="n"/>
+      <c r="T30" s="74" t="n"/>
+      <c r="U30" s="74" t="n"/>
+      <c r="V30" s="74" t="n"/>
+      <c r="W30" s="74" t="n"/>
+      <c r="X30" s="74" t="n"/>
+      <c r="Y30" s="74" t="n"/>
+      <c r="Z30" s="74" t="n"/>
+      <c r="AA30" s="74" t="n"/>
       <c r="AB30" s="85" t="n"/>
       <c r="AC30" s="85" t="n"/>
       <c r="AD30" s="85" t="n"/>
@@ -12994,34 +12677,18 @@
       <c r="AX30" s="85" t="n"/>
       <c r="AY30" s="85" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="74" t="n"/>
-      <c r="B31" s="74" t="n"/>
-      <c r="C31" s="74" t="n"/>
-      <c r="D31" s="74" t="n"/>
-      <c r="E31" s="74" t="n"/>
-      <c r="F31" s="74" t="n"/>
-      <c r="G31" s="74" t="n"/>
-      <c r="H31" s="68" t="n"/>
-      <c r="I31" s="68" t="n"/>
-      <c r="J31" s="68" t="n"/>
-      <c r="K31" s="68" t="n"/>
-      <c r="L31" s="68" t="n"/>
-      <c r="M31" s="68" t="n"/>
-      <c r="N31" s="68" t="n"/>
-      <c r="O31" s="68" t="n"/>
-      <c r="P31" s="68" t="n"/>
-      <c r="Q31" s="68" t="n"/>
-      <c r="R31" s="68" t="n"/>
-      <c r="S31" s="68" t="n"/>
-      <c r="T31" s="68" t="n"/>
-      <c r="U31" s="68" t="n"/>
-      <c r="V31" s="68" t="n"/>
-      <c r="W31" s="85" t="n"/>
-      <c r="X31" s="85" t="n"/>
-      <c r="Y31" s="85" t="n"/>
-      <c r="Z31" s="85" t="n"/>
-      <c r="AA31" s="85" t="n"/>
+    <row r="31" ht="15.5" customHeight="1" s="50">
+      <c r="A31" s="101" t="inlineStr">
+        <is>
+          <t>8. Business line manager approval dates (column I): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B31" s="97" t="n"/>
+      <c r="C31" s="97" t="n"/>
+      <c r="D31" s="97" t="n"/>
+      <c r="E31" s="97" t="n"/>
+      <c r="F31" s="97" t="n"/>
+      <c r="G31" s="98" t="n"/>
       <c r="AB31" s="85" t="n"/>
       <c r="AC31" s="85" t="n"/>
       <c r="AD31" s="85" t="n"/>
@@ -13047,38 +12714,43 @@
       <c r="AX31" s="85" t="n"/>
       <c r="AY31" s="85" t="n"/>
     </row>
-    <row r="32" ht="15.5" customHeight="1" s="50">
-      <c r="A32" s="71" t="inlineStr">
-        <is>
-          <t>9. Emails showing Business line manager approval of DIV testing results (column J): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B32" s="97" t="n"/>
-      <c r="C32" s="97" t="n"/>
-      <c r="D32" s="97" t="n"/>
-      <c r="E32" s="97" t="n"/>
-      <c r="F32" s="97" t="n"/>
-      <c r="G32" s="98" t="n"/>
-      <c r="H32" s="68" t="n"/>
-      <c r="I32" s="68" t="n"/>
-      <c r="J32" s="68" t="n"/>
-      <c r="K32" s="68" t="n"/>
-      <c r="L32" s="68" t="n"/>
-      <c r="M32" s="68" t="n"/>
-      <c r="N32" s="68" t="n"/>
-      <c r="O32" s="68" t="n"/>
-      <c r="P32" s="68" t="n"/>
-      <c r="Q32" s="68" t="n"/>
-      <c r="R32" s="68" t="n"/>
-      <c r="S32" s="68" t="n"/>
-      <c r="T32" s="68" t="n"/>
-      <c r="U32" s="68" t="n"/>
-      <c r="V32" s="68" t="n"/>
-      <c r="W32" s="85" t="n"/>
-      <c r="X32" s="85" t="n"/>
-      <c r="Y32" s="85" t="n"/>
-      <c r="Z32" s="85" t="n"/>
-      <c r="AA32" s="85" t="n"/>
+    <row r="32" ht="26" customHeight="1" s="50">
+      <c r="A32" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B32" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C32" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D32" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E32" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F32" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G32" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H32" s="67" t="n"/>
       <c r="AB32" s="85" t="n"/>
       <c r="AC32" s="85" t="n"/>
       <c r="AD32" s="85" t="n"/>
@@ -13104,49 +12776,68 @@
       <c r="AX32" s="85" t="n"/>
       <c r="AY32" s="85" t="n"/>
     </row>
-    <row r="33" ht="26" customHeight="1" s="50">
-      <c r="A33" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B33" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C33" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D33" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E33" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F33" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G33" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H33" s="67" t="n"/>
-      <c r="V33" s="68" t="n"/>
-      <c r="W33" s="85" t="n"/>
-      <c r="X33" s="85" t="n"/>
-      <c r="Y33" s="85" t="n"/>
-      <c r="Z33" s="85" t="n"/>
-      <c r="AA33" s="85" t="n"/>
+    <row r="33" ht="174" customHeight="1" s="50">
+      <c r="A33" s="78" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B33" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
+      </c>
+      <c r="C33" s="76" t="inlineStr">
+        <is>
+          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
+        </is>
+      </c>
+      <c r="D33" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express (E03 row 47)
+1867 FedExport - BSI (E03 row 9)
+1868 FedImport - BSI (E03 row 10)
+3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
+4052 Interface Monitor (E03 row 61)
+3301 MQ Payment Monitor (E03 row 25, 29)
+1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
+1917 ReconXpert (E03 row 17)
+1936 Swift Interface - BSI (E03 row 7, 60)
+1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
+        </is>
+      </c>
+      <c r="E33" s="76" t="inlineStr">
+        <is>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+Checked for Business line manager approval dates:
+'Department Manager Approval Date' and 'Attestation Date' columns</t>
+        </is>
+      </c>
+      <c r="F33" s="76" t="inlineStr">
+        <is>
+          <t>Supports Business line manager approval dates (column I), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G33" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H33" s="70" t="n"/>
+      <c r="I33" s="70" t="n"/>
+      <c r="J33" s="70" t="n"/>
+      <c r="K33" s="70" t="n"/>
+      <c r="L33" s="70" t="n"/>
+      <c r="M33" s="70" t="n"/>
+      <c r="N33" s="70" t="n"/>
+      <c r="O33" s="70" t="n"/>
+      <c r="P33" s="70" t="n"/>
+      <c r="Q33" s="70" t="n"/>
+      <c r="R33" s="70" t="n"/>
+      <c r="S33" s="70" t="n"/>
+      <c r="T33" s="70" t="n"/>
+      <c r="U33" s="69" t="n"/>
+      <c r="V33" s="86" t="n"/>
+      <c r="W33" s="87" t="n"/>
       <c r="AB33" s="85" t="n"/>
       <c r="AC33" s="85" t="n"/>
       <c r="AD33" s="85" t="n"/>
@@ -13172,64 +12863,34 @@
       <c r="AX33" s="85" t="n"/>
       <c r="AY33" s="85" t="n"/>
     </row>
-    <row r="34" ht="90" customHeight="1" s="50">
-      <c r="A34" s="78" t="inlineStr">
-        <is>
-          <t>BLA06</t>
-        </is>
-      </c>
-      <c r="B34" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C34" s="76" t="inlineStr">
-        <is>
-          <t>12/31/2025 &amp; 01/26/2026, Sadis Alvarenga</t>
-        </is>
-      </c>
-      <c r="D34" s="76" t="inlineStr">
-        <is>
-          <t>1917 ReconXpert
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E34" s="76" t="inlineStr">
-        <is>
-          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.
-Checked for Emails showing Business line manager approval of DIV testing results:
-Application / record agreed to the evidence.</t>
-        </is>
-      </c>
-      <c r="F34" s="76" t="inlineStr">
-        <is>
-          <t>Supports Emails showing Business line manager approval of DIV testing results (column J), samples 1917, 1937</t>
-        </is>
-      </c>
-      <c r="G34" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H34" s="69" t="n"/>
-      <c r="I34" s="69" t="n"/>
-      <c r="J34" s="69" t="n"/>
-      <c r="K34" s="69" t="n"/>
-      <c r="L34" s="69" t="n"/>
-      <c r="M34" s="70" t="n"/>
-      <c r="N34" s="70" t="n"/>
-      <c r="O34" s="70" t="n"/>
-      <c r="P34" s="70" t="n"/>
-      <c r="Q34" s="70" t="n"/>
-      <c r="R34" s="70" t="n"/>
-      <c r="S34" s="70" t="n"/>
-      <c r="T34" s="70" t="n"/>
-      <c r="U34" s="70" t="n"/>
-      <c r="V34" s="68" t="n"/>
-      <c r="W34" s="85" t="n"/>
-      <c r="X34" s="85" t="n"/>
-      <c r="Y34" s="85" t="n"/>
-      <c r="Z34" s="85" t="n"/>
-      <c r="AA34" s="85" t="n"/>
+    <row r="34" s="50">
+      <c r="A34" s="74" t="n"/>
+      <c r="B34" s="74" t="n"/>
+      <c r="C34" s="74" t="n"/>
+      <c r="D34" s="74" t="n"/>
+      <c r="E34" s="74" t="n"/>
+      <c r="F34" s="74" t="n"/>
+      <c r="G34" s="74" t="n"/>
+      <c r="H34" s="74" t="n"/>
+      <c r="I34" s="74" t="n"/>
+      <c r="J34" s="74" t="n"/>
+      <c r="K34" s="74" t="n"/>
+      <c r="L34" s="74" t="n"/>
+      <c r="M34" s="74" t="n"/>
+      <c r="N34" s="74" t="n"/>
+      <c r="O34" s="74" t="n"/>
+      <c r="P34" s="74" t="n"/>
+      <c r="Q34" s="74" t="n"/>
+      <c r="R34" s="74" t="n"/>
+      <c r="S34" s="74" t="n"/>
+      <c r="T34" s="74" t="n"/>
+      <c r="U34" s="74" t="n"/>
+      <c r="V34" s="74" t="n"/>
+      <c r="W34" s="74" t="n"/>
+      <c r="X34" s="74" t="n"/>
+      <c r="Y34" s="74" t="n"/>
+      <c r="Z34" s="74" t="n"/>
+      <c r="AA34" s="74" t="n"/>
       <c r="AB34" s="85" t="n"/>
       <c r="AC34" s="85" t="n"/>
       <c r="AD34" s="85" t="n"/>
@@ -13255,67 +12916,18 @@
       <c r="AX34" s="85" t="n"/>
       <c r="AY34" s="85" t="n"/>
     </row>
-    <row r="35" ht="90" customHeight="1" s="50">
-      <c r="A35" s="78" t="inlineStr">
-        <is>
-          <t>DMA01</t>
-        </is>
-      </c>
-      <c r="B35" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C35" s="76" t="inlineStr">
-        <is>
-          <t>08/18/2026, Claudia Romero</t>
-        </is>
-      </c>
-      <c r="D35" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express
-1867 FedExport - BSI
-1868 FedImport - BSI
-3299 Imaging101
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E35" s="76" t="inlineStr">
-        <is>
-          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation, attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).
-Checked for Emails showing Business line manager approval of DIV testing results:
-Application / record agreed to the evidence.</t>
-        </is>
-      </c>
-      <c r="F35" s="76" t="inlineStr">
-        <is>
-          <t>Supports Emails showing Business line manager approval of DIV testing results (column J), samples 1822, 1867, 1868, 3299, 1937</t>
-        </is>
-      </c>
-      <c r="G35" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H35" s="68" t="n"/>
-      <c r="I35" s="68" t="n"/>
-      <c r="J35" s="68" t="n"/>
-      <c r="K35" s="68" t="n"/>
-      <c r="L35" s="68" t="n"/>
-      <c r="M35" s="68" t="n"/>
-      <c r="N35" s="68" t="n"/>
-      <c r="O35" s="68" t="n"/>
-      <c r="P35" s="68" t="n"/>
-      <c r="Q35" s="68" t="n"/>
-      <c r="R35" s="68" t="n"/>
-      <c r="S35" s="68" t="n"/>
-      <c r="T35" s="68" t="n"/>
-      <c r="U35" s="68" t="n"/>
-      <c r="V35" s="68" t="n"/>
-      <c r="W35" s="85" t="n"/>
-      <c r="X35" s="85" t="n"/>
-      <c r="Y35" s="85" t="n"/>
-      <c r="Z35" s="85" t="n"/>
-      <c r="AA35" s="85" t="n"/>
+    <row r="35" ht="15.5" customHeight="1" s="50">
+      <c r="A35" s="101" t="inlineStr">
+        <is>
+          <t>9. DIV Test procedures listed within the Test results document (column J): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B35" s="97" t="n"/>
+      <c r="C35" s="97" t="n"/>
+      <c r="D35" s="97" t="n"/>
+      <c r="E35" s="97" t="n"/>
+      <c r="F35" s="97" t="n"/>
+      <c r="G35" s="98" t="n"/>
       <c r="AB35" s="85" t="n"/>
       <c r="AC35" s="85" t="n"/>
       <c r="AD35" s="85" t="n"/>
@@ -13341,66 +12953,43 @@
       <c r="AX35" s="85" t="n"/>
       <c r="AY35" s="85" t="n"/>
     </row>
-    <row r="36" ht="148" customHeight="1" s="50">
-      <c r="A36" s="78" t="inlineStr">
-        <is>
-          <t>DMA02</t>
-        </is>
-      </c>
-      <c r="B36" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C36" s="76" t="inlineStr">
-        <is>
-          <t>08/19/2026, David Marquez</t>
-        </is>
-      </c>
-      <c r="D36" s="76" t="inlineStr">
-        <is>
-          <t>3299 Imaging101
-1903 OFAC - BSI
-1936 Swift Interface - BSI
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E36" s="76" t="inlineStr">
-        <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
-Checked for Emails showing Business line manager approval of DIV testing results:
-Application / record agreed to the evidence.</t>
-        </is>
-      </c>
-      <c r="F36" s="76" t="inlineStr">
-        <is>
-          <t>Supports Emails showing Business line manager approval of DIV testing results (column J), samples 3299, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G36" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H36" s="68" t="n"/>
-      <c r="I36" s="68" t="n"/>
-      <c r="J36" s="68" t="n"/>
-      <c r="K36" s="68" t="n"/>
-      <c r="L36" s="68" t="n"/>
-      <c r="M36" s="68" t="n"/>
-      <c r="N36" s="68" t="n"/>
-      <c r="O36" s="68" t="n"/>
-      <c r="P36" s="68" t="n"/>
-      <c r="Q36" s="68" t="n"/>
-      <c r="R36" s="68" t="n"/>
-      <c r="S36" s="68" t="n"/>
-      <c r="T36" s="68" t="n"/>
-      <c r="U36" s="68" t="n"/>
-      <c r="V36" s="68" t="n"/>
-      <c r="W36" s="85" t="n"/>
-      <c r="X36" s="85" t="n"/>
-      <c r="Y36" s="85" t="n"/>
-      <c r="Z36" s="85" t="n"/>
-      <c r="AA36" s="85" t="n"/>
+    <row r="36" ht="26" customHeight="1" s="50">
+      <c r="A36" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B36" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C36" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D36" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E36" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F36" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G36" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H36" s="67" t="n"/>
       <c r="AB36" s="85" t="n"/>
       <c r="AC36" s="85" t="n"/>
       <c r="AD36" s="85" t="n"/>
@@ -13426,38 +13015,45 @@
       <c r="AX36" s="85" t="n"/>
       <c r="AY36" s="85" t="n"/>
     </row>
-    <row r="37" ht="90" customHeight="1" s="50">
+    <row r="37" ht="174" customHeight="1" s="50">
       <c r="A37" s="78" t="inlineStr">
         <is>
-          <t>DMA03</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B37" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
         <v/>
       </c>
       <c r="C37" s="76" t="inlineStr">
         <is>
-          <t>08/18/2026, Frank Puentes</t>
+          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="D37" s="76" t="inlineStr">
         <is>
-          <t>3301 MQ Payment Monitor
-1903 OFAC - BSI
-1937 T24</t>
+          <t>1822 ACH Express (E03 row 47)
+1867 FedExport - BSI (E03 row 9)
+1868 FedImport - BSI (E03 row 10)
+3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
+4052 Interface Monitor (E03 row 61)
+3301 MQ Payment Monitor (E03 row 25, 29)
+1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
+1917 ReconXpert (E03 row 17)
+1936 Swift Interface - BSI (E03 row 7, 60)
+1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
         </is>
       </c>
       <c r="E37" s="76" t="inlineStr">
         <is>
-          <t>Frank Puentes returns the signed attestation: attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).
-Checked for Emails showing Business line manager approval of DIV testing results:
-Application / record agreed to the evidence.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+Checked for DIV Test procedures listed within the Test results document:
+'Data Integrity Validation Procedures' column</t>
         </is>
       </c>
       <c r="F37" s="76" t="inlineStr">
         <is>
-          <t>Supports Emails showing Business line manager approval of DIV testing results (column J), samples 3301, 1903, 1937</t>
+          <t>Supports DIV Test procedures listed within the Test results document (column J), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="G37" s="77" t="inlineStr">
@@ -13465,26 +13061,13 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H37" s="68" t="n"/>
-      <c r="I37" s="68" t="n"/>
-      <c r="J37" s="68" t="n"/>
-      <c r="K37" s="68" t="n"/>
-      <c r="L37" s="68" t="n"/>
-      <c r="M37" s="68" t="n"/>
-      <c r="N37" s="68" t="n"/>
-      <c r="O37" s="68" t="n"/>
-      <c r="P37" s="68" t="n"/>
-      <c r="Q37" s="68" t="n"/>
-      <c r="R37" s="68" t="n"/>
-      <c r="S37" s="68" t="n"/>
-      <c r="T37" s="68" t="n"/>
-      <c r="U37" s="68" t="n"/>
-      <c r="V37" s="68" t="n"/>
-      <c r="W37" s="85" t="n"/>
-      <c r="X37" s="85" t="n"/>
-      <c r="Y37" s="85" t="n"/>
-      <c r="Z37" s="85" t="n"/>
-      <c r="AA37" s="85" t="n"/>
+      <c r="H37" s="70" t="n"/>
+      <c r="I37" s="70" t="n"/>
+      <c r="J37" s="70" t="n"/>
+      <c r="K37" s="70" t="n"/>
+      <c r="L37" s="70" t="n"/>
+      <c r="M37" s="69" t="n"/>
+      <c r="N37" s="70" t="n"/>
       <c r="AB37" s="85" t="n"/>
       <c r="AC37" s="85" t="n"/>
       <c r="AD37" s="85" t="n"/>
@@ -13510,65 +13093,34 @@
       <c r="AX37" s="85" t="n"/>
       <c r="AY37" s="85" t="n"/>
     </row>
-    <row r="38" ht="100" customHeight="1" s="50">
-      <c r="A38" s="78" t="inlineStr">
-        <is>
-          <t>DMA04</t>
-        </is>
-      </c>
-      <c r="B38" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C38" s="76" t="inlineStr">
-        <is>
-          <t>08/17/2026, Michelle Oropesa</t>
-        </is>
-      </c>
-      <c r="D38" s="76" t="inlineStr">
-        <is>
-          <t>4052 Interface Monitor
-1936 Swift Interface - BSI
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E38" s="76" t="inlineStr">
-        <is>
-          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).
-Checked for Emails showing Business line manager approval of DIV testing results:
-Application / record agreed to the evidence.</t>
-        </is>
-      </c>
-      <c r="F38" s="76" t="inlineStr">
-        <is>
-          <t>Supports Emails showing Business line manager approval of DIV testing results (column J), samples 4052, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G38" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H38" s="68" t="n"/>
-      <c r="I38" s="68" t="n"/>
-      <c r="J38" s="68" t="n"/>
-      <c r="K38" s="68" t="n"/>
-      <c r="L38" s="68" t="n"/>
-      <c r="M38" s="68" t="n"/>
-      <c r="N38" s="68" t="n"/>
-      <c r="O38" s="68" t="n"/>
-      <c r="P38" s="68" t="n"/>
-      <c r="Q38" s="68" t="n"/>
-      <c r="R38" s="68" t="n"/>
-      <c r="S38" s="68" t="n"/>
-      <c r="T38" s="68" t="n"/>
-      <c r="U38" s="68" t="n"/>
-      <c r="V38" s="68" t="n"/>
-      <c r="W38" s="85" t="n"/>
-      <c r="X38" s="85" t="n"/>
-      <c r="Y38" s="85" t="n"/>
-      <c r="Z38" s="85" t="n"/>
-      <c r="AA38" s="85" t="n"/>
+    <row r="38" s="50">
+      <c r="A38" s="74" t="n"/>
+      <c r="B38" s="74" t="n"/>
+      <c r="C38" s="74" t="n"/>
+      <c r="D38" s="74" t="n"/>
+      <c r="E38" s="74" t="n"/>
+      <c r="F38" s="74" t="n"/>
+      <c r="G38" s="74" t="n"/>
+      <c r="H38" s="74" t="n"/>
+      <c r="I38" s="74" t="n"/>
+      <c r="J38" s="74" t="n"/>
+      <c r="K38" s="74" t="n"/>
+      <c r="L38" s="74" t="n"/>
+      <c r="M38" s="74" t="n"/>
+      <c r="N38" s="74" t="n"/>
+      <c r="O38" s="74" t="n"/>
+      <c r="P38" s="74" t="n"/>
+      <c r="Q38" s="74" t="n"/>
+      <c r="R38" s="74" t="n"/>
+      <c r="S38" s="74" t="n"/>
+      <c r="T38" s="74" t="n"/>
+      <c r="U38" s="74" t="n"/>
+      <c r="V38" s="74" t="n"/>
+      <c r="W38" s="74" t="n"/>
+      <c r="X38" s="74" t="n"/>
+      <c r="Y38" s="74" t="n"/>
+      <c r="Z38" s="74" t="n"/>
+      <c r="AA38" s="74" t="n"/>
       <c r="AB38" s="85" t="n"/>
       <c r="AC38" s="85" t="n"/>
       <c r="AD38" s="85" t="n"/>
@@ -13594,34 +13146,18 @@
       <c r="AX38" s="85" t="n"/>
       <c r="AY38" s="85" t="n"/>
     </row>
-    <row r="39">
-      <c r="A39" s="74" t="n"/>
-      <c r="B39" s="74" t="n"/>
-      <c r="C39" s="74" t="n"/>
-      <c r="D39" s="74" t="n"/>
-      <c r="E39" s="74" t="n"/>
-      <c r="F39" s="74" t="n"/>
-      <c r="G39" s="74" t="n"/>
-      <c r="H39" s="68" t="n"/>
-      <c r="I39" s="68" t="n"/>
-      <c r="J39" s="68" t="n"/>
-      <c r="K39" s="68" t="n"/>
-      <c r="L39" s="68" t="n"/>
-      <c r="M39" s="68" t="n"/>
-      <c r="N39" s="68" t="n"/>
-      <c r="O39" s="68" t="n"/>
-      <c r="P39" s="68" t="n"/>
-      <c r="Q39" s="68" t="n"/>
-      <c r="R39" s="68" t="n"/>
-      <c r="S39" s="68" t="n"/>
-      <c r="T39" s="68" t="n"/>
-      <c r="U39" s="68" t="n"/>
-      <c r="V39" s="68" t="n"/>
-      <c r="W39" s="85" t="n"/>
-      <c r="X39" s="85" t="n"/>
-      <c r="Y39" s="85" t="n"/>
-      <c r="Z39" s="85" t="n"/>
-      <c r="AA39" s="85" t="n"/>
+    <row r="39" ht="15.5" customHeight="1" s="50">
+      <c r="A39" s="101" t="inlineStr">
+        <is>
+          <t>10. Emails showing Business line manager approval of DIV testing results (column K): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B39" s="97" t="n"/>
+      <c r="C39" s="97" t="n"/>
+      <c r="D39" s="97" t="n"/>
+      <c r="E39" s="97" t="n"/>
+      <c r="F39" s="97" t="n"/>
+      <c r="G39" s="98" t="n"/>
       <c r="AB39" s="85" t="n"/>
       <c r="AC39" s="85" t="n"/>
       <c r="AD39" s="85" t="n"/>
@@ -13647,38 +13183,43 @@
       <c r="AX39" s="85" t="n"/>
       <c r="AY39" s="85" t="n"/>
     </row>
-    <row r="40" ht="15.5" customHeight="1" s="50">
-      <c r="A40" s="71" t="inlineStr">
-        <is>
-          <t>10. All evidence of Data Integrity DR test in BCIC (column K): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B40" s="97" t="n"/>
-      <c r="C40" s="97" t="n"/>
-      <c r="D40" s="97" t="n"/>
-      <c r="E40" s="97" t="n"/>
-      <c r="F40" s="97" t="n"/>
-      <c r="G40" s="98" t="n"/>
-      <c r="H40" s="68" t="n"/>
-      <c r="I40" s="68" t="n"/>
-      <c r="J40" s="68" t="n"/>
-      <c r="K40" s="68" t="n"/>
-      <c r="L40" s="68" t="n"/>
-      <c r="M40" s="68" t="n"/>
-      <c r="N40" s="68" t="n"/>
-      <c r="O40" s="68" t="n"/>
-      <c r="P40" s="68" t="n"/>
-      <c r="Q40" s="68" t="n"/>
-      <c r="R40" s="68" t="n"/>
-      <c r="S40" s="68" t="n"/>
-      <c r="T40" s="68" t="n"/>
-      <c r="U40" s="68" t="n"/>
-      <c r="V40" s="68" t="n"/>
-      <c r="W40" s="85" t="n"/>
-      <c r="X40" s="85" t="n"/>
-      <c r="Y40" s="85" t="n"/>
-      <c r="Z40" s="85" t="n"/>
-      <c r="AA40" s="85" t="n"/>
+    <row r="40" ht="26" customHeight="1" s="50">
+      <c r="A40" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B40" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C40" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D40" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E40" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F40" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G40" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H40" s="67" t="n"/>
       <c r="AB40" s="85" t="n"/>
       <c r="AC40" s="85" t="n"/>
       <c r="AD40" s="85" t="n"/>
@@ -13704,57 +13245,58 @@
       <c r="AX40" s="85" t="n"/>
       <c r="AY40" s="85" t="n"/>
     </row>
-    <row r="41" ht="26" customHeight="1" s="50">
-      <c r="A41" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B41" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C41" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D41" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E41" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F41" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G41" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H41" s="67" t="n"/>
-      <c r="N41" s="68" t="n"/>
-      <c r="O41" s="68" t="n"/>
-      <c r="P41" s="68" t="n"/>
-      <c r="Q41" s="68" t="n"/>
-      <c r="R41" s="68" t="n"/>
-      <c r="S41" s="68" t="n"/>
-      <c r="T41" s="68" t="n"/>
-      <c r="U41" s="68" t="n"/>
-      <c r="V41" s="68" t="n"/>
-      <c r="W41" s="85" t="n"/>
-      <c r="X41" s="85" t="n"/>
-      <c r="Y41" s="85" t="n"/>
-      <c r="Z41" s="85" t="n"/>
-      <c r="AA41" s="85" t="n"/>
+    <row r="41" ht="90" customHeight="1" s="50">
+      <c r="A41" s="78" t="inlineStr">
+        <is>
+          <t>BLA06</t>
+        </is>
+      </c>
+      <c r="B41" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C41" s="76" t="inlineStr">
+        <is>
+          <t>12/31/2025 &amp; 01/26/2026, Sadis Alvarenga</t>
+        </is>
+      </c>
+      <c r="D41" s="76" t="inlineStr">
+        <is>
+          <t>1917 ReconXpert
+1937 T24</t>
+        </is>
+      </c>
+      <c r="E41" s="76" t="inlineStr">
+        <is>
+          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.
+Checked for Emails showing Business line manager approval of DIV testing results:
+Application / record agreed to the evidence.</t>
+        </is>
+      </c>
+      <c r="F41" s="76" t="inlineStr">
+        <is>
+          <t>Supports Emails showing Business line manager approval of DIV testing results (column K), samples 1917, 1937</t>
+        </is>
+      </c>
+      <c r="G41" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H41" s="69" t="n"/>
+      <c r="I41" s="69" t="n"/>
+      <c r="J41" s="69" t="n"/>
+      <c r="K41" s="69" t="n"/>
+      <c r="L41" s="69" t="n"/>
+      <c r="M41" s="70" t="n"/>
+      <c r="N41" s="70" t="n"/>
+      <c r="O41" s="70" t="n"/>
+      <c r="P41" s="70" t="n"/>
+      <c r="Q41" s="70" t="n"/>
+      <c r="R41" s="70" t="n"/>
+      <c r="S41" s="70" t="n"/>
+      <c r="T41" s="70" t="n"/>
+      <c r="U41" s="70" t="n"/>
       <c r="AB41" s="85" t="n"/>
       <c r="AC41" s="85" t="n"/>
       <c r="AD41" s="85" t="n"/>
@@ -13780,45 +13322,40 @@
       <c r="AX41" s="85" t="n"/>
       <c r="AY41" s="85" t="n"/>
     </row>
-    <row r="42" ht="174" customHeight="1" s="50">
+    <row r="42" ht="90" customHeight="1" s="50">
       <c r="A42" s="78" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>DMA01</t>
         </is>
       </c>
       <c r="B42" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
         <v/>
       </c>
       <c r="C42" s="76" t="inlineStr">
         <is>
-          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
+          <t>08/18/2026, Claudia Romero</t>
         </is>
       </c>
       <c r="D42" s="76" t="inlineStr">
         <is>
-          <t>1822 ACH Express (E03 row 47)
-1867 FedExport - BSI (E03 row 9)
-1868 FedImport - BSI (E03 row 10)
-3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
-4052 Interface Monitor (E03 row 61)
-3301 MQ Payment Monitor (E03 row 25, 29)
-1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
-1917 ReconXpert (E03 row 17)
-1936 Swift Interface - BSI (E03 row 7, 60)
-1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
+          <t>1822 ACH Express
+1867 FedExport - BSI
+1868 FedImport - BSI
+3299 Imaging101
+1937 T24</t>
         </is>
       </c>
       <c r="E42" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
-Checked for All evidence of Data Integrity DR test in BCIC:
-BCiC DIV export (tester, dates, manager, Y/N results, attestation)</t>
+          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation, attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).
+Checked for Emails showing Business line manager approval of DIV testing results:
+Application / record agreed to the evidence.</t>
         </is>
       </c>
       <c r="F42" s="76" t="inlineStr">
         <is>
-          <t>Supports All evidence of Data Integrity DR test in BCIC (column K), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>Supports Emails showing Business line manager approval of DIV testing results (column K), samples 1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="G42" s="77" t="inlineStr">
@@ -13826,26 +13363,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H42" s="70" t="n"/>
-      <c r="I42" s="70" t="n"/>
-      <c r="J42" s="70" t="n"/>
-      <c r="K42" s="69" t="n"/>
-      <c r="L42" s="70" t="n"/>
-      <c r="M42" s="70" t="n"/>
-      <c r="N42" s="68" t="n"/>
-      <c r="O42" s="68" t="n"/>
-      <c r="P42" s="68" t="n"/>
-      <c r="Q42" s="68" t="n"/>
-      <c r="R42" s="68" t="n"/>
-      <c r="S42" s="68" t="n"/>
-      <c r="T42" s="68" t="n"/>
-      <c r="U42" s="68" t="n"/>
-      <c r="V42" s="68" t="n"/>
-      <c r="W42" s="85" t="n"/>
-      <c r="X42" s="85" t="n"/>
-      <c r="Y42" s="85" t="n"/>
-      <c r="Z42" s="85" t="n"/>
-      <c r="AA42" s="85" t="n"/>
       <c r="AB42" s="85" t="n"/>
       <c r="AC42" s="85" t="n"/>
       <c r="AD42" s="85" t="n"/>
@@ -13871,34 +13388,46 @@
       <c r="AX42" s="85" t="n"/>
       <c r="AY42" s="85" t="n"/>
     </row>
-    <row r="43">
-      <c r="A43" s="74" t="n"/>
-      <c r="B43" s="74" t="n"/>
-      <c r="C43" s="74" t="n"/>
-      <c r="D43" s="74" t="n"/>
-      <c r="E43" s="74" t="n"/>
-      <c r="F43" s="74" t="n"/>
-      <c r="G43" s="74" t="n"/>
-      <c r="H43" s="68" t="n"/>
-      <c r="I43" s="68" t="n"/>
-      <c r="J43" s="68" t="n"/>
-      <c r="K43" s="68" t="n"/>
-      <c r="L43" s="68" t="n"/>
-      <c r="M43" s="68" t="n"/>
-      <c r="N43" s="68" t="n"/>
-      <c r="O43" s="68" t="n"/>
-      <c r="P43" s="68" t="n"/>
-      <c r="Q43" s="68" t="n"/>
-      <c r="R43" s="68" t="n"/>
-      <c r="S43" s="68" t="n"/>
-      <c r="T43" s="68" t="n"/>
-      <c r="U43" s="68" t="n"/>
-      <c r="V43" s="68" t="n"/>
-      <c r="W43" s="85" t="n"/>
-      <c r="X43" s="85" t="n"/>
-      <c r="Y43" s="85" t="n"/>
-      <c r="Z43" s="85" t="n"/>
-      <c r="AA43" s="85" t="n"/>
+    <row r="43" ht="148" customHeight="1" s="50">
+      <c r="A43" s="78" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="B43" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C43" s="76" t="inlineStr">
+        <is>
+          <t>08/19/2026, David Marquez</t>
+        </is>
+      </c>
+      <c r="D43" s="76" t="inlineStr">
+        <is>
+          <t>3299 Imaging101
+1903 OFAC - BSI
+1936 Swift Interface - BSI
+1937 T24</t>
+        </is>
+      </c>
+      <c r="E43" s="76" t="inlineStr">
+        <is>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
+Checked for Emails showing Business line manager approval of DIV testing results:
+Application / record agreed to the evidence.</t>
+        </is>
+      </c>
+      <c r="F43" s="76" t="inlineStr">
+        <is>
+          <t>Supports Emails showing Business line manager approval of DIV testing results (column K), samples 3299, 1903, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G43" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB43" s="85" t="n"/>
       <c r="AC43" s="85" t="n"/>
       <c r="AD43" s="85" t="n"/>
@@ -13924,38 +13453,45 @@
       <c r="AX43" s="85" t="n"/>
       <c r="AY43" s="85" t="n"/>
     </row>
-    <row r="44" ht="15.5" customHeight="1" s="50">
-      <c r="A44" s="71" t="inlineStr">
-        <is>
-          <t>11. Annual Testing Executed (column L): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B44" s="97" t="n"/>
-      <c r="C44" s="97" t="n"/>
-      <c r="D44" s="97" t="n"/>
-      <c r="E44" s="97" t="n"/>
-      <c r="F44" s="97" t="n"/>
-      <c r="G44" s="98" t="n"/>
-      <c r="H44" s="68" t="n"/>
-      <c r="I44" s="68" t="n"/>
-      <c r="J44" s="68" t="n"/>
-      <c r="K44" s="68" t="n"/>
-      <c r="L44" s="68" t="n"/>
-      <c r="M44" s="68" t="n"/>
-      <c r="N44" s="68" t="n"/>
-      <c r="O44" s="68" t="n"/>
-      <c r="P44" s="68" t="n"/>
-      <c r="Q44" s="68" t="n"/>
-      <c r="R44" s="68" t="n"/>
-      <c r="S44" s="68" t="n"/>
-      <c r="T44" s="68" t="n"/>
-      <c r="U44" s="68" t="n"/>
-      <c r="V44" s="68" t="n"/>
-      <c r="W44" s="85" t="n"/>
-      <c r="X44" s="85" t="n"/>
-      <c r="Y44" s="85" t="n"/>
-      <c r="Z44" s="85" t="n"/>
-      <c r="AA44" s="85" t="n"/>
+    <row r="44" ht="90" customHeight="1" s="50">
+      <c r="A44" s="78" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="B44" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C44" s="76" t="inlineStr">
+        <is>
+          <t>08/18/2026, Frank Puentes</t>
+        </is>
+      </c>
+      <c r="D44" s="76" t="inlineStr">
+        <is>
+          <t>3301 MQ Payment Monitor
+1903 OFAC - BSI
+1937 T24</t>
+        </is>
+      </c>
+      <c r="E44" s="76" t="inlineStr">
+        <is>
+          <t>Frank Puentes returns the signed attestation: attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).
+Checked for Emails showing Business line manager approval of DIV testing results:
+Application / record agreed to the evidence.</t>
+        </is>
+      </c>
+      <c r="F44" s="76" t="inlineStr">
+        <is>
+          <t>Supports Emails showing Business line manager approval of DIV testing results (column K), samples 3301, 1903, 1937</t>
+        </is>
+      </c>
+      <c r="G44" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB44" s="85" t="n"/>
       <c r="AC44" s="85" t="n"/>
       <c r="AD44" s="85" t="n"/>
@@ -13981,55 +13517,45 @@
       <c r="AX44" s="85" t="n"/>
       <c r="AY44" s="85" t="n"/>
     </row>
-    <row r="45" ht="26" customHeight="1" s="50">
-      <c r="A45" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B45" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C45" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D45" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E45" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F45" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G45" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H45" s="67" t="n"/>
-      <c r="P45" s="68" t="n"/>
-      <c r="Q45" s="68" t="n"/>
-      <c r="R45" s="68" t="n"/>
-      <c r="S45" s="68" t="n"/>
-      <c r="T45" s="68" t="n"/>
-      <c r="U45" s="68" t="n"/>
-      <c r="V45" s="68" t="n"/>
-      <c r="W45" s="85" t="n"/>
-      <c r="X45" s="85" t="n"/>
-      <c r="Y45" s="85" t="n"/>
-      <c r="Z45" s="85" t="n"/>
-      <c r="AA45" s="85" t="n"/>
+    <row r="45" ht="100" customHeight="1" s="50">
+      <c r="A45" s="78" t="inlineStr">
+        <is>
+          <t>DMA04</t>
+        </is>
+      </c>
+      <c r="B45" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C45" s="76" t="inlineStr">
+        <is>
+          <t>08/17/2026, Michelle Oropesa</t>
+        </is>
+      </c>
+      <c r="D45" s="76" t="inlineStr">
+        <is>
+          <t>4052 Interface Monitor
+1936 Swift Interface - BSI
+1937 T24</t>
+        </is>
+      </c>
+      <c r="E45" s="76" t="inlineStr">
+        <is>
+          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).
+Checked for Emails showing Business line manager approval of DIV testing results:
+Application / record agreed to the evidence.</t>
+        </is>
+      </c>
+      <c r="F45" s="76" t="inlineStr">
+        <is>
+          <t>Supports Emails showing Business line manager approval of DIV testing results (column K), samples 4052, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G45" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB45" s="85" t="n"/>
       <c r="AC45" s="85" t="n"/>
       <c r="AD45" s="85" t="n"/>
@@ -14055,73 +13581,34 @@
       <c r="AX45" s="85" t="n"/>
       <c r="AY45" s="85" t="n"/>
     </row>
-    <row r="46" ht="126" customHeight="1" s="50">
-      <c r="A46" s="78" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B46" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
-        <v/>
-      </c>
-      <c r="C46" s="76" t="inlineStr">
-        <is>
-          <t>BCiC: Applications In Scope for DR Test BSI</t>
-        </is>
-      </c>
-      <c r="D46" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express (E01 row 3)
-1867 FedExport - BSI (E01 row 19)
-1868 FedImport - BSI (E01 row 20)
-3299 Imaging101 (E01 row 24)
-4052 Interface Monitor (E01 row 25)
-3301 MQ Payment Monitor (E01 row 31)
-1903 OFAC - BSI (E01 row 34)
-1917 ReconXpert (E01 row 36)
-1936 Swift Interface - BSI (E01 row 42)
-1937 T24 (E01 row 43)</t>
-        </is>
-      </c>
-      <c r="E46" s="76" t="inlineStr">
-        <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.
-Checked for Annual Testing Executed:
-Exercise Date 12/11/2025 / 2025 DR Test Scope = True
-Exercise Date 11/15/2025 / 2025 DR Test Scope = True</t>
-        </is>
-      </c>
-      <c r="F46" s="76" t="inlineStr">
-        <is>
-          <t>Supports Annual Testing Executed (column L), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G46" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H46" s="70" t="n"/>
-      <c r="I46" s="70" t="n"/>
-      <c r="J46" s="70" t="n"/>
-      <c r="K46" s="70" t="n"/>
-      <c r="L46" s="70" t="n"/>
-      <c r="M46" s="70" t="n"/>
-      <c r="N46" s="69" t="n"/>
-      <c r="O46" s="70" t="n"/>
-      <c r="P46" s="68" t="n"/>
-      <c r="Q46" s="68" t="n"/>
-      <c r="R46" s="68" t="n"/>
-      <c r="S46" s="68" t="n"/>
-      <c r="T46" s="68" t="n"/>
-      <c r="U46" s="68" t="n"/>
-      <c r="V46" s="68" t="n"/>
-      <c r="W46" s="85" t="n"/>
-      <c r="X46" s="85" t="n"/>
-      <c r="Y46" s="85" t="n"/>
-      <c r="Z46" s="85" t="n"/>
-      <c r="AA46" s="85" t="n"/>
+    <row r="46" s="50">
+      <c r="A46" s="74" t="n"/>
+      <c r="B46" s="74" t="n"/>
+      <c r="C46" s="74" t="n"/>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="74" t="n"/>
+      <c r="F46" s="74" t="n"/>
+      <c r="G46" s="74" t="n"/>
+      <c r="H46" s="74" t="n"/>
+      <c r="I46" s="74" t="n"/>
+      <c r="J46" s="74" t="n"/>
+      <c r="K46" s="74" t="n"/>
+      <c r="L46" s="74" t="n"/>
+      <c r="M46" s="74" t="n"/>
+      <c r="N46" s="74" t="n"/>
+      <c r="O46" s="74" t="n"/>
+      <c r="P46" s="74" t="n"/>
+      <c r="Q46" s="74" t="n"/>
+      <c r="R46" s="74" t="n"/>
+      <c r="S46" s="74" t="n"/>
+      <c r="T46" s="74" t="n"/>
+      <c r="U46" s="74" t="n"/>
+      <c r="V46" s="74" t="n"/>
+      <c r="W46" s="74" t="n"/>
+      <c r="X46" s="74" t="n"/>
+      <c r="Y46" s="74" t="n"/>
+      <c r="Z46" s="74" t="n"/>
+      <c r="AA46" s="74" t="n"/>
       <c r="AB46" s="85" t="n"/>
       <c r="AC46" s="85" t="n"/>
       <c r="AD46" s="85" t="n"/>
@@ -14147,34 +13634,18 @@
       <c r="AX46" s="85" t="n"/>
       <c r="AY46" s="85" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="74" t="n"/>
-      <c r="B47" s="74" t="n"/>
-      <c r="C47" s="74" t="n"/>
-      <c r="D47" s="74" t="n"/>
-      <c r="E47" s="74" t="n"/>
-      <c r="F47" s="74" t="n"/>
-      <c r="G47" s="74" t="n"/>
-      <c r="H47" s="68" t="n"/>
-      <c r="I47" s="68" t="n"/>
-      <c r="J47" s="68" t="n"/>
-      <c r="K47" s="68" t="n"/>
-      <c r="L47" s="68" t="n"/>
-      <c r="M47" s="68" t="n"/>
-      <c r="N47" s="68" t="n"/>
-      <c r="O47" s="68" t="n"/>
-      <c r="P47" s="68" t="n"/>
-      <c r="Q47" s="68" t="n"/>
-      <c r="R47" s="68" t="n"/>
-      <c r="S47" s="68" t="n"/>
-      <c r="T47" s="68" t="n"/>
-      <c r="U47" s="68" t="n"/>
-      <c r="V47" s="68" t="n"/>
-      <c r="W47" s="85" t="n"/>
-      <c r="X47" s="85" t="n"/>
-      <c r="Y47" s="85" t="n"/>
-      <c r="Z47" s="85" t="n"/>
-      <c r="AA47" s="85" t="n"/>
+    <row r="47" ht="15.5" customHeight="1" s="50">
+      <c r="A47" s="101" t="inlineStr">
+        <is>
+          <t>11. All evidence of Data Integrity DR test in BCIC (column L): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B47" s="97" t="n"/>
+      <c r="C47" s="97" t="n"/>
+      <c r="D47" s="97" t="n"/>
+      <c r="E47" s="97" t="n"/>
+      <c r="F47" s="97" t="n"/>
+      <c r="G47" s="98" t="n"/>
       <c r="AB47" s="85" t="n"/>
       <c r="AC47" s="85" t="n"/>
       <c r="AD47" s="85" t="n"/>
@@ -14200,38 +13671,43 @@
       <c r="AX47" s="85" t="n"/>
       <c r="AY47" s="85" t="n"/>
     </row>
-    <row r="48" ht="15.5" customHeight="1" s="50">
-      <c r="A48" s="71" t="inlineStr">
-        <is>
-          <t>12. Data Integrity Validation Performed by IT DR Team (column M): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B48" s="97" t="n"/>
-      <c r="C48" s="97" t="n"/>
-      <c r="D48" s="97" t="n"/>
-      <c r="E48" s="97" t="n"/>
-      <c r="F48" s="97" t="n"/>
-      <c r="G48" s="98" t="n"/>
-      <c r="H48" s="68" t="n"/>
-      <c r="I48" s="68" t="n"/>
-      <c r="J48" s="68" t="n"/>
-      <c r="K48" s="68" t="n"/>
-      <c r="L48" s="68" t="n"/>
-      <c r="M48" s="68" t="n"/>
-      <c r="N48" s="68" t="n"/>
-      <c r="O48" s="68" t="n"/>
-      <c r="P48" s="68" t="n"/>
-      <c r="Q48" s="68" t="n"/>
-      <c r="R48" s="68" t="n"/>
-      <c r="S48" s="68" t="n"/>
-      <c r="T48" s="68" t="n"/>
-      <c r="U48" s="68" t="n"/>
-      <c r="V48" s="68" t="n"/>
-      <c r="W48" s="85" t="n"/>
-      <c r="X48" s="85" t="n"/>
-      <c r="Y48" s="85" t="n"/>
-      <c r="Z48" s="85" t="n"/>
-      <c r="AA48" s="85" t="n"/>
+    <row r="48" ht="26" customHeight="1" s="50">
+      <c r="A48" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B48" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C48" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D48" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E48" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F48" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G48" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H48" s="67" t="n"/>
       <c r="AB48" s="85" t="n"/>
       <c r="AC48" s="85" t="n"/>
       <c r="AD48" s="85" t="n"/>
@@ -14257,52 +13733,58 @@
       <c r="AX48" s="85" t="n"/>
       <c r="AY48" s="85" t="n"/>
     </row>
-    <row r="49" ht="26" customHeight="1" s="50">
-      <c r="A49" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B49" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C49" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D49" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E49" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F49" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G49" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H49" s="67" t="n"/>
-      <c r="S49" s="68" t="n"/>
-      <c r="T49" s="68" t="n"/>
-      <c r="U49" s="68" t="n"/>
-      <c r="V49" s="68" t="n"/>
-      <c r="W49" s="85" t="n"/>
-      <c r="X49" s="85" t="n"/>
-      <c r="Y49" s="85" t="n"/>
-      <c r="Z49" s="85" t="n"/>
-      <c r="AA49" s="85" t="n"/>
+    <row r="49" ht="174" customHeight="1" s="50">
+      <c r="A49" s="78" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+      <c r="B49" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <v/>
+      </c>
+      <c r="C49" s="76" t="inlineStr">
+        <is>
+          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
+        </is>
+      </c>
+      <c r="D49" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express (E03 row 47)
+1867 FedExport - BSI (E03 row 9)
+1868 FedImport - BSI (E03 row 10)
+3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
+4052 Interface Monitor (E03 row 61)
+3301 MQ Payment Monitor (E03 row 25, 29)
+1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
+1917 ReconXpert (E03 row 17)
+1936 Swift Interface - BSI (E03 row 7, 60)
+1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
+        </is>
+      </c>
+      <c r="E49" s="76" t="inlineStr">
+        <is>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+Checked for All evidence of Data Integrity DR test in BCIC:
+BCiC DIV export (tester, dates, manager, Y/N results, attestation)</t>
+        </is>
+      </c>
+      <c r="F49" s="76" t="inlineStr">
+        <is>
+          <t>Supports All evidence of Data Integrity DR test in BCIC (column L), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G49" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H49" s="70" t="n"/>
+      <c r="I49" s="70" t="n"/>
+      <c r="J49" s="70" t="n"/>
+      <c r="K49" s="69" t="n"/>
+      <c r="L49" s="70" t="n"/>
+      <c r="M49" s="70" t="n"/>
       <c r="AB49" s="85" t="n"/>
       <c r="AC49" s="85" t="n"/>
       <c r="AD49" s="85" t="n"/>
@@ -14328,72 +13810,34 @@
       <c r="AX49" s="85" t="n"/>
       <c r="AY49" s="85" t="n"/>
     </row>
-    <row r="50" ht="126" customHeight="1" s="50">
-      <c r="A50" s="78" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-      <c r="B50" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
-        <v/>
-      </c>
-      <c r="C50" s="76" t="inlineStr">
-        <is>
-          <t>09/15/2025, Elizabeth Noda</t>
-        </is>
-      </c>
-      <c r="D50" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express
-1867 FedExport - BSI
-1868 FedImport - BSI
-3299 Imaging101
-4052 Interface Monitor
-3301 MQ Payment Monitor
-1903 OFAC - BSI
-1917 ReconXpert
-1936 Swift Interface - BSI
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E50" s="76" t="inlineStr">
-        <is>
-          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025, duplicate E06 removed).
-Checked for Data Integrity Validation Performed by IT DR Team:
-IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)</t>
-        </is>
-      </c>
-      <c r="F50" s="76" t="inlineStr">
-        <is>
-          <t>Supports Data Integrity Validation Performed by IT DR Team (column M), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G50" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H50" s="70" t="n"/>
-      <c r="I50" s="70" t="n"/>
-      <c r="J50" s="70" t="n"/>
-      <c r="K50" s="70" t="n"/>
-      <c r="L50" s="70" t="n"/>
-      <c r="M50" s="70" t="n"/>
-      <c r="N50" s="70" t="n"/>
-      <c r="O50" s="69" t="n"/>
-      <c r="P50" s="70" t="n"/>
-      <c r="Q50" s="70" t="n"/>
-      <c r="R50" s="70" t="n"/>
-      <c r="S50" s="68" t="n"/>
-      <c r="T50" s="68" t="n"/>
-      <c r="U50" s="68" t="n"/>
-      <c r="V50" s="68" t="n"/>
-      <c r="W50" s="85" t="n"/>
-      <c r="X50" s="85" t="n"/>
-      <c r="Y50" s="85" t="n"/>
-      <c r="Z50" s="85" t="n"/>
-      <c r="AA50" s="85" t="n"/>
+    <row r="50" s="50">
+      <c r="A50" s="74" t="n"/>
+      <c r="B50" s="74" t="n"/>
+      <c r="C50" s="74" t="n"/>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="74" t="n"/>
+      <c r="F50" s="74" t="n"/>
+      <c r="G50" s="74" t="n"/>
+      <c r="H50" s="74" t="n"/>
+      <c r="I50" s="74" t="n"/>
+      <c r="J50" s="74" t="n"/>
+      <c r="K50" s="74" t="n"/>
+      <c r="L50" s="74" t="n"/>
+      <c r="M50" s="74" t="n"/>
+      <c r="N50" s="74" t="n"/>
+      <c r="O50" s="74" t="n"/>
+      <c r="P50" s="74" t="n"/>
+      <c r="Q50" s="74" t="n"/>
+      <c r="R50" s="74" t="n"/>
+      <c r="S50" s="74" t="n"/>
+      <c r="T50" s="74" t="n"/>
+      <c r="U50" s="74" t="n"/>
+      <c r="V50" s="74" t="n"/>
+      <c r="W50" s="74" t="n"/>
+      <c r="X50" s="74" t="n"/>
+      <c r="Y50" s="74" t="n"/>
+      <c r="Z50" s="74" t="n"/>
+      <c r="AA50" s="74" t="n"/>
       <c r="AB50" s="85" t="n"/>
       <c r="AC50" s="85" t="n"/>
       <c r="AD50" s="85" t="n"/>
@@ -14419,34 +13863,18 @@
       <c r="AX50" s="85" t="n"/>
       <c r="AY50" s="85" t="n"/>
     </row>
-    <row r="51">
-      <c r="A51" s="74" t="n"/>
-      <c r="B51" s="74" t="n"/>
-      <c r="C51" s="74" t="n"/>
-      <c r="D51" s="74" t="n"/>
-      <c r="E51" s="74" t="n"/>
-      <c r="F51" s="74" t="n"/>
-      <c r="G51" s="74" t="n"/>
-      <c r="H51" s="68" t="n"/>
-      <c r="I51" s="68" t="n"/>
-      <c r="J51" s="68" t="n"/>
-      <c r="K51" s="68" t="n"/>
-      <c r="L51" s="68" t="n"/>
-      <c r="M51" s="68" t="n"/>
-      <c r="N51" s="68" t="n"/>
-      <c r="O51" s="68" t="n"/>
-      <c r="P51" s="68" t="n"/>
-      <c r="Q51" s="68" t="n"/>
-      <c r="R51" s="68" t="n"/>
-      <c r="S51" s="68" t="n"/>
-      <c r="T51" s="68" t="n"/>
-      <c r="U51" s="68" t="n"/>
-      <c r="V51" s="68" t="n"/>
-      <c r="W51" s="85" t="n"/>
-      <c r="X51" s="85" t="n"/>
-      <c r="Y51" s="85" t="n"/>
-      <c r="Z51" s="85" t="n"/>
-      <c r="AA51" s="85" t="n"/>
+    <row r="51" ht="15.5" customHeight="1" s="50">
+      <c r="A51" s="101" t="inlineStr">
+        <is>
+          <t>12. Annual Testing Executed (column M): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B51" s="97" t="n"/>
+      <c r="C51" s="97" t="n"/>
+      <c r="D51" s="97" t="n"/>
+      <c r="E51" s="97" t="n"/>
+      <c r="F51" s="97" t="n"/>
+      <c r="G51" s="98" t="n"/>
       <c r="AB51" s="85" t="n"/>
       <c r="AC51" s="85" t="n"/>
       <c r="AD51" s="85" t="n"/>
@@ -14472,38 +13900,43 @@
       <c r="AX51" s="85" t="n"/>
       <c r="AY51" s="85" t="n"/>
     </row>
-    <row r="52" ht="15.5" customHeight="1" s="50">
-      <c r="A52" s="71" t="inlineStr">
-        <is>
-          <t>13. Applications in Scope Identified (column N): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B52" s="97" t="n"/>
-      <c r="C52" s="97" t="n"/>
-      <c r="D52" s="97" t="n"/>
-      <c r="E52" s="97" t="n"/>
-      <c r="F52" s="97" t="n"/>
-      <c r="G52" s="98" t="n"/>
-      <c r="H52" s="68" t="n"/>
-      <c r="I52" s="68" t="n"/>
-      <c r="J52" s="68" t="n"/>
-      <c r="K52" s="68" t="n"/>
-      <c r="L52" s="68" t="n"/>
-      <c r="M52" s="68" t="n"/>
-      <c r="N52" s="68" t="n"/>
-      <c r="O52" s="68" t="n"/>
-      <c r="P52" s="68" t="n"/>
-      <c r="Q52" s="68" t="n"/>
-      <c r="R52" s="68" t="n"/>
-      <c r="S52" s="68" t="n"/>
-      <c r="T52" s="68" t="n"/>
-      <c r="U52" s="68" t="n"/>
-      <c r="V52" s="68" t="n"/>
-      <c r="W52" s="85" t="n"/>
-      <c r="X52" s="85" t="n"/>
-      <c r="Y52" s="85" t="n"/>
-      <c r="Z52" s="85" t="n"/>
-      <c r="AA52" s="85" t="n"/>
+    <row r="52" ht="26" customHeight="1" s="50">
+      <c r="A52" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B52" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C52" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D52" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E52" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F52" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G52" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H52" s="67" t="n"/>
       <c r="AB52" s="85" t="n"/>
       <c r="AC52" s="85" t="n"/>
       <c r="AD52" s="85" t="n"/>
@@ -14529,57 +13962,61 @@
       <c r="AX52" s="85" t="n"/>
       <c r="AY52" s="85" t="n"/>
     </row>
-    <row r="53" ht="26" customHeight="1" s="50">
-      <c r="A53" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B53" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C53" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D53" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E53" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F53" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G53" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H53" s="67" t="n"/>
-      <c r="N53" s="68" t="n"/>
-      <c r="O53" s="68" t="n"/>
-      <c r="P53" s="68" t="n"/>
-      <c r="Q53" s="68" t="n"/>
-      <c r="R53" s="68" t="n"/>
-      <c r="S53" s="68" t="n"/>
-      <c r="T53" s="68" t="n"/>
-      <c r="U53" s="68" t="n"/>
-      <c r="V53" s="68" t="n"/>
-      <c r="W53" s="85" t="n"/>
-      <c r="X53" s="85" t="n"/>
-      <c r="Y53" s="85" t="n"/>
-      <c r="Z53" s="85" t="n"/>
-      <c r="AA53" s="85" t="n"/>
+    <row r="53" ht="126" customHeight="1" s="50">
+      <c r="A53" s="78" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B53" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <v/>
+      </c>
+      <c r="C53" s="76" t="inlineStr">
+        <is>
+          <t>BCiC: Applications In Scope for DR Test BSI</t>
+        </is>
+      </c>
+      <c r="D53" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express (E01 row 3)
+1867 FedExport - BSI (E01 row 19)
+1868 FedImport - BSI (E01 row 20)
+3299 Imaging101 (E01 row 24)
+4052 Interface Monitor (E01 row 25)
+3301 MQ Payment Monitor (E01 row 31)
+1903 OFAC - BSI (E01 row 34)
+1917 ReconXpert (E01 row 36)
+1936 Swift Interface - BSI (E01 row 42)
+1937 T24 (E01 row 43)</t>
+        </is>
+      </c>
+      <c r="E53" s="76" t="inlineStr">
+        <is>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.
+Checked for Annual Testing Executed:
+Exercise Date 12/11/2025 / 2025 DR Test Scope = True
+Exercise Date 11/15/2025 / 2025 DR Test Scope = True</t>
+        </is>
+      </c>
+      <c r="F53" s="76" t="inlineStr">
+        <is>
+          <t>Supports Annual Testing Executed (column M), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G53" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H53" s="70" t="n"/>
+      <c r="I53" s="70" t="n"/>
+      <c r="J53" s="70" t="n"/>
+      <c r="K53" s="70" t="n"/>
+      <c r="L53" s="70" t="n"/>
+      <c r="M53" s="70" t="n"/>
+      <c r="N53" s="69" t="n"/>
+      <c r="O53" s="70" t="n"/>
       <c r="AB53" s="85" t="n"/>
       <c r="AC53" s="85" t="n"/>
       <c r="AD53" s="85" t="n"/>
@@ -14605,81 +14042,34 @@
       <c r="AX53" s="85" t="n"/>
       <c r="AY53" s="85" t="n"/>
     </row>
-    <row r="54" ht="409" customHeight="1" s="50">
-      <c r="A54" s="78" t="inlineStr">
-        <is>
-          <t>MA01</t>
-        </is>
-      </c>
-      <c r="B54" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
-        <v/>
-      </c>
-      <c r="C54" s="76" t="inlineStr">
-        <is>
-          <t>09/23/2026, Cesar Vidal (BCiC walkthrough)</t>
-        </is>
-      </c>
-      <c r="D54" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express
-1867 FedExport - BSI
-1868 FedImport - BSI
-3299 Imaging101
-4052 Interface Monitor
-3301 MQ Payment Monitor
-1903 OFAC - BSI
-1917 ReconXpert
-1936 Swift Interface - BSI
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E54" s="76" t="inlineStr">
-        <is>
-          <t>BC in the Cloud 'Applications In Scope for DR Test BSI' view (filter Scope Entity = BSI; 43 items). The 10 tested applications are selected (1822, 1867, 1868, 1903, 1917, 1937, 1936, 3301, 3299, 4052) and each shows 2025 DR Test Scope = True, 2025 Backup/Restore Test Scope = True and 2025 Backup/Restore DIV Scope = True.
-Checked for Applications in Scope Identified:
-BSI In-Scope Applications-2026: App ID 1822 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 1867 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 1868 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 3299 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 4052 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 3301 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 1903 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 1917 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 1936 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-BSI In-Scope Applications-2026: App ID 1937 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True</t>
-        </is>
-      </c>
-      <c r="F54" s="76" t="inlineStr">
-        <is>
-          <t>Supports Applications in Scope Identified (column N), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G54" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H54" s="70" t="n"/>
-      <c r="I54" s="69" t="n"/>
-      <c r="J54" s="70" t="n"/>
-      <c r="K54" s="70" t="n"/>
-      <c r="L54" s="70" t="n"/>
-      <c r="M54" s="70" t="n"/>
-      <c r="N54" s="68" t="n"/>
-      <c r="O54" s="68" t="n"/>
-      <c r="P54" s="68" t="n"/>
-      <c r="Q54" s="68" t="n"/>
-      <c r="R54" s="68" t="n"/>
-      <c r="S54" s="68" t="n"/>
-      <c r="T54" s="68" t="n"/>
-      <c r="U54" s="68" t="n"/>
-      <c r="V54" s="68" t="n"/>
-      <c r="W54" s="85" t="n"/>
-      <c r="X54" s="85" t="n"/>
-      <c r="Y54" s="85" t="n"/>
-      <c r="Z54" s="85" t="n"/>
-      <c r="AA54" s="85" t="n"/>
+    <row r="54" s="50">
+      <c r="A54" s="74" t="n"/>
+      <c r="B54" s="74" t="n"/>
+      <c r="C54" s="74" t="n"/>
+      <c r="D54" s="74" t="n"/>
+      <c r="E54" s="74" t="n"/>
+      <c r="F54" s="74" t="n"/>
+      <c r="G54" s="74" t="n"/>
+      <c r="H54" s="74" t="n"/>
+      <c r="I54" s="74" t="n"/>
+      <c r="J54" s="74" t="n"/>
+      <c r="K54" s="74" t="n"/>
+      <c r="L54" s="74" t="n"/>
+      <c r="M54" s="74" t="n"/>
+      <c r="N54" s="74" t="n"/>
+      <c r="O54" s="74" t="n"/>
+      <c r="P54" s="74" t="n"/>
+      <c r="Q54" s="74" t="n"/>
+      <c r="R54" s="74" t="n"/>
+      <c r="S54" s="74" t="n"/>
+      <c r="T54" s="74" t="n"/>
+      <c r="U54" s="74" t="n"/>
+      <c r="V54" s="74" t="n"/>
+      <c r="W54" s="74" t="n"/>
+      <c r="X54" s="74" t="n"/>
+      <c r="Y54" s="74" t="n"/>
+      <c r="Z54" s="74" t="n"/>
+      <c r="AA54" s="74" t="n"/>
       <c r="AB54" s="85" t="n"/>
       <c r="AC54" s="85" t="n"/>
       <c r="AD54" s="85" t="n"/>
@@ -14705,34 +14095,18 @@
       <c r="AX54" s="85" t="n"/>
       <c r="AY54" s="85" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" s="74" t="n"/>
-      <c r="B55" s="74" t="n"/>
-      <c r="C55" s="74" t="n"/>
-      <c r="D55" s="74" t="n"/>
-      <c r="E55" s="74" t="n"/>
-      <c r="F55" s="74" t="n"/>
-      <c r="G55" s="74" t="n"/>
-      <c r="H55" s="68" t="n"/>
-      <c r="I55" s="68" t="n"/>
-      <c r="J55" s="68" t="n"/>
-      <c r="K55" s="68" t="n"/>
-      <c r="L55" s="68" t="n"/>
-      <c r="M55" s="68" t="n"/>
-      <c r="N55" s="68" t="n"/>
-      <c r="O55" s="68" t="n"/>
-      <c r="P55" s="68" t="n"/>
-      <c r="Q55" s="68" t="n"/>
-      <c r="R55" s="68" t="n"/>
-      <c r="S55" s="68" t="n"/>
-      <c r="T55" s="68" t="n"/>
-      <c r="U55" s="68" t="n"/>
-      <c r="V55" s="68" t="n"/>
-      <c r="W55" s="85" t="n"/>
-      <c r="X55" s="85" t="n"/>
-      <c r="Y55" s="85" t="n"/>
-      <c r="Z55" s="85" t="n"/>
-      <c r="AA55" s="85" t="n"/>
+    <row r="55" ht="15.5" customHeight="1" s="50">
+      <c r="A55" s="101" t="inlineStr">
+        <is>
+          <t>13. Data Integrity Validation Performed by IT DR Team (column N): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B55" s="97" t="n"/>
+      <c r="C55" s="97" t="n"/>
+      <c r="D55" s="97" t="n"/>
+      <c r="E55" s="97" t="n"/>
+      <c r="F55" s="97" t="n"/>
+      <c r="G55" s="98" t="n"/>
       <c r="AB55" s="85" t="n"/>
       <c r="AC55" s="85" t="n"/>
       <c r="AD55" s="85" t="n"/>
@@ -14758,38 +14132,43 @@
       <c r="AX55" s="85" t="n"/>
       <c r="AY55" s="85" t="n"/>
     </row>
-    <row r="56" ht="15.5" customHeight="1" s="50">
-      <c r="A56" s="71" t="inlineStr">
-        <is>
-          <t>14. Business Line Approval of Results (column O): review of evidence files and results</t>
-        </is>
-      </c>
-      <c r="B56" s="97" t="n"/>
-      <c r="C56" s="97" t="n"/>
-      <c r="D56" s="97" t="n"/>
-      <c r="E56" s="97" t="n"/>
-      <c r="F56" s="97" t="n"/>
-      <c r="G56" s="98" t="n"/>
-      <c r="H56" s="68" t="n"/>
-      <c r="I56" s="68" t="n"/>
-      <c r="J56" s="68" t="n"/>
-      <c r="K56" s="68" t="n"/>
-      <c r="L56" s="68" t="n"/>
-      <c r="M56" s="68" t="n"/>
-      <c r="N56" s="68" t="n"/>
-      <c r="O56" s="68" t="n"/>
-      <c r="P56" s="68" t="n"/>
-      <c r="Q56" s="68" t="n"/>
-      <c r="R56" s="68" t="n"/>
-      <c r="S56" s="68" t="n"/>
-      <c r="T56" s="68" t="n"/>
-      <c r="U56" s="68" t="n"/>
-      <c r="V56" s="68" t="n"/>
-      <c r="W56" s="85" t="n"/>
-      <c r="X56" s="85" t="n"/>
-      <c r="Y56" s="85" t="n"/>
-      <c r="Z56" s="85" t="n"/>
-      <c r="AA56" s="85" t="n"/>
+    <row r="56" ht="26" customHeight="1" s="50">
+      <c r="A56" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B56" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C56" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D56" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E56" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F56" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G56" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H56" s="67" t="n"/>
       <c r="AB56" s="85" t="n"/>
       <c r="AC56" s="85" t="n"/>
       <c r="AD56" s="85" t="n"/>
@@ -14815,43 +14194,63 @@
       <c r="AX56" s="85" t="n"/>
       <c r="AY56" s="85" t="n"/>
     </row>
-    <row r="57" ht="26" customHeight="1" s="50">
-      <c r="A57" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B57" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C57" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner / operator</t>
-        </is>
-      </c>
-      <c r="D57" s="73" t="inlineStr">
-        <is>
-          <t>Applications tested (source rows)</t>
-        </is>
-      </c>
-      <c r="E57" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F57" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G57" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H57" s="67" t="n"/>
+    <row r="57" ht="126" customHeight="1" s="50">
+      <c r="A57" s="78" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B57" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
+        <v/>
+      </c>
+      <c r="C57" s="76" t="inlineStr">
+        <is>
+          <t>09/15/2025, Elizabeth Noda</t>
+        </is>
+      </c>
+      <c r="D57" s="76" t="inlineStr">
+        <is>
+          <t>1822 ACH Express
+1867 FedExport - BSI
+1868 FedImport - BSI
+3299 Imaging101
+4052 Interface Monitor
+3301 MQ Payment Monitor
+1903 OFAC - BSI
+1917 ReconXpert
+1936 Swift Interface - BSI
+1937 T24</t>
+        </is>
+      </c>
+      <c r="E57" s="76" t="inlineStr">
+        <is>
+          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025, duplicate E06 removed).
+Checked for Data Integrity Validation Performed by IT DR Team:
+IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)</t>
+        </is>
+      </c>
+      <c r="F57" s="76" t="inlineStr">
+        <is>
+          <t>Supports Data Integrity Validation Performed by IT DR Team (column N), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G57" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H57" s="70" t="n"/>
+      <c r="I57" s="70" t="n"/>
+      <c r="J57" s="70" t="n"/>
+      <c r="K57" s="70" t="n"/>
+      <c r="L57" s="70" t="n"/>
+      <c r="M57" s="70" t="n"/>
+      <c r="N57" s="70" t="n"/>
+      <c r="O57" s="69" t="n"/>
+      <c r="P57" s="70" t="n"/>
+      <c r="Q57" s="70" t="n"/>
+      <c r="R57" s="70" t="n"/>
       <c r="AB57" s="85" t="n"/>
       <c r="AC57" s="85" t="n"/>
       <c r="AD57" s="85" t="n"/>
@@ -14877,64 +14276,34 @@
       <c r="AX57" s="85" t="n"/>
       <c r="AY57" s="85" t="n"/>
     </row>
-    <row r="58" ht="78" customHeight="1" s="50">
-      <c r="A58" s="78" t="inlineStr">
-        <is>
-          <t>BLA06</t>
-        </is>
-      </c>
-      <c r="B58" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C58" s="76" t="inlineStr">
-        <is>
-          <t>12/31/2025 &amp; 01/26/2026, Sadis Alvarenga</t>
-        </is>
-      </c>
-      <c r="D58" s="76" t="inlineStr">
-        <is>
-          <t>1917 ReconXpert
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E58" s="76" t="inlineStr">
-        <is>
-          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.
-Checked for Business Line Approval of Results:
-Application / record agreed to the evidence.</t>
-        </is>
-      </c>
-      <c r="F58" s="76" t="inlineStr">
-        <is>
-          <t>Supports Business Line Approval of Results (column O), samples 1917, 1937</t>
-        </is>
-      </c>
-      <c r="G58" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H58" s="70" t="n"/>
-      <c r="I58" s="70" t="n"/>
-      <c r="J58" s="70" t="n"/>
-      <c r="K58" s="70" t="n"/>
-      <c r="L58" s="70" t="n"/>
-      <c r="M58" s="69" t="n"/>
-      <c r="N58" s="69" t="n"/>
-      <c r="O58" s="69" t="n"/>
-      <c r="P58" s="69" t="n"/>
-      <c r="Q58" s="69" t="n"/>
-      <c r="R58" s="70" t="n"/>
-      <c r="S58" s="70" t="n"/>
-      <c r="T58" s="70" t="n"/>
-      <c r="U58" s="70" t="n"/>
-      <c r="V58" s="86" t="n"/>
-      <c r="W58" s="87" t="n"/>
-      <c r="X58" s="87" t="n"/>
-      <c r="Y58" s="87" t="n"/>
-      <c r="Z58" s="87" t="n"/>
-      <c r="AA58" s="87" t="n"/>
+    <row r="58" s="50">
+      <c r="A58" s="74" t="n"/>
+      <c r="B58" s="74" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
+      <c r="G58" s="74" t="n"/>
+      <c r="H58" s="74" t="n"/>
+      <c r="I58" s="74" t="n"/>
+      <c r="J58" s="74" t="n"/>
+      <c r="K58" s="74" t="n"/>
+      <c r="L58" s="74" t="n"/>
+      <c r="M58" s="74" t="n"/>
+      <c r="N58" s="74" t="n"/>
+      <c r="O58" s="74" t="n"/>
+      <c r="P58" s="74" t="n"/>
+      <c r="Q58" s="74" t="n"/>
+      <c r="R58" s="74" t="n"/>
+      <c r="S58" s="74" t="n"/>
+      <c r="T58" s="74" t="n"/>
+      <c r="U58" s="74" t="n"/>
+      <c r="V58" s="74" t="n"/>
+      <c r="W58" s="74" t="n"/>
+      <c r="X58" s="74" t="n"/>
+      <c r="Y58" s="74" t="n"/>
+      <c r="Z58" s="74" t="n"/>
+      <c r="AA58" s="74" t="n"/>
       <c r="AB58" s="85" t="n"/>
       <c r="AC58" s="85" t="n"/>
       <c r="AD58" s="85" t="n"/>
@@ -14960,67 +14329,18 @@
       <c r="AX58" s="85" t="n"/>
       <c r="AY58" s="85" t="n"/>
     </row>
-    <row r="59" ht="78" customHeight="1" s="50">
-      <c r="A59" s="78" t="inlineStr">
-        <is>
-          <t>DMA01</t>
-        </is>
-      </c>
-      <c r="B59" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C59" s="76" t="inlineStr">
-        <is>
-          <t>08/18/2026, Claudia Romero</t>
-        </is>
-      </c>
-      <c r="D59" s="76" t="inlineStr">
-        <is>
-          <t>1822 ACH Express
-1867 FedExport - BSI
-1868 FedImport - BSI
-3299 Imaging101
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E59" s="76" t="inlineStr">
-        <is>
-          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation, attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).
-Checked for Business Line Approval of Results:
-Application / record agreed to the evidence.</t>
-        </is>
-      </c>
-      <c r="F59" s="76" t="inlineStr">
-        <is>
-          <t>Supports Business Line Approval of Results (column O), samples 1822, 1867, 1868, 3299, 1937</t>
-        </is>
-      </c>
-      <c r="G59" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H59" s="68" t="n"/>
-      <c r="I59" s="68" t="n"/>
-      <c r="J59" s="68" t="n"/>
-      <c r="K59" s="68" t="n"/>
-      <c r="L59" s="68" t="n"/>
-      <c r="M59" s="68" t="n"/>
-      <c r="N59" s="68" t="n"/>
-      <c r="O59" s="68" t="n"/>
-      <c r="P59" s="68" t="n"/>
-      <c r="Q59" s="68" t="n"/>
-      <c r="R59" s="68" t="n"/>
-      <c r="S59" s="68" t="n"/>
-      <c r="T59" s="68" t="n"/>
-      <c r="U59" s="68" t="n"/>
-      <c r="V59" s="68" t="n"/>
-      <c r="W59" s="85" t="n"/>
-      <c r="X59" s="85" t="n"/>
-      <c r="Y59" s="85" t="n"/>
-      <c r="Z59" s="85" t="n"/>
-      <c r="AA59" s="85" t="n"/>
+    <row r="59" ht="15.5" customHeight="1" s="50">
+      <c r="A59" s="101" t="inlineStr">
+        <is>
+          <t>14. Business Line Approval of Results (column O): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B59" s="97" t="n"/>
+      <c r="C59" s="97" t="n"/>
+      <c r="D59" s="97" t="n"/>
+      <c r="E59" s="97" t="n"/>
+      <c r="F59" s="97" t="n"/>
+      <c r="G59" s="98" t="n"/>
       <c r="AB59" s="85" t="n"/>
       <c r="AC59" s="85" t="n"/>
       <c r="AD59" s="85" t="n"/>
@@ -15046,66 +14366,43 @@
       <c r="AX59" s="85" t="n"/>
       <c r="AY59" s="85" t="n"/>
     </row>
-    <row r="60" ht="136" customHeight="1" s="50">
-      <c r="A60" s="78" t="inlineStr">
-        <is>
-          <t>DMA02</t>
-        </is>
-      </c>
-      <c r="B60" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C60" s="76" t="inlineStr">
-        <is>
-          <t>08/19/2026, David Marquez</t>
-        </is>
-      </c>
-      <c r="D60" s="76" t="inlineStr">
-        <is>
-          <t>3299 Imaging101
-1903 OFAC - BSI
-1936 Swift Interface - BSI
-1937 T24</t>
-        </is>
-      </c>
-      <c r="E60" s="76" t="inlineStr">
-        <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
-Checked for Business Line Approval of Results:
-Application / record agreed to the evidence.</t>
-        </is>
-      </c>
-      <c r="F60" s="76" t="inlineStr">
-        <is>
-          <t>Supports Business Line Approval of Results (column O), samples 3299, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G60" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H60" s="68" t="n"/>
-      <c r="I60" s="68" t="n"/>
-      <c r="J60" s="68" t="n"/>
-      <c r="K60" s="68" t="n"/>
-      <c r="L60" s="68" t="n"/>
-      <c r="M60" s="68" t="n"/>
-      <c r="N60" s="68" t="n"/>
-      <c r="O60" s="68" t="n"/>
-      <c r="P60" s="68" t="n"/>
-      <c r="Q60" s="68" t="n"/>
-      <c r="R60" s="68" t="n"/>
-      <c r="S60" s="68" t="n"/>
-      <c r="T60" s="68" t="n"/>
-      <c r="U60" s="68" t="n"/>
-      <c r="V60" s="68" t="n"/>
-      <c r="W60" s="85" t="n"/>
-      <c r="X60" s="85" t="n"/>
-      <c r="Y60" s="85" t="n"/>
-      <c r="Z60" s="85" t="n"/>
-      <c r="AA60" s="85" t="n"/>
+    <row r="60" ht="26" customHeight="1" s="50">
+      <c r="A60" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B60" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C60" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D60" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E60" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F60" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G60" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H60" s="67" t="n"/>
       <c r="AB60" s="85" t="n"/>
       <c r="AC60" s="85" t="n"/>
       <c r="AD60" s="85" t="n"/>
@@ -15134,35 +14431,34 @@
     <row r="61" ht="78" customHeight="1" s="50">
       <c r="A61" s="78" t="inlineStr">
         <is>
-          <t>DMA03</t>
+          <t>BLA06</t>
         </is>
       </c>
       <c r="B61" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
         <v/>
       </c>
       <c r="C61" s="76" t="inlineStr">
         <is>
-          <t>08/18/2026, Frank Puentes</t>
+          <t>12/31/2025 &amp; 01/26/2026, Sadis Alvarenga</t>
         </is>
       </c>
       <c r="D61" s="76" t="inlineStr">
         <is>
-          <t>3301 MQ Payment Monitor
-1903 OFAC - BSI
+          <t>1917 ReconXpert
 1937 T24</t>
         </is>
       </c>
       <c r="E61" s="76" t="inlineStr">
         <is>
-          <t>Frank Puentes returns the signed attestation: attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).
+          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.
 Checked for Business Line Approval of Results:
 Application / record agreed to the evidence.</t>
         </is>
       </c>
       <c r="F61" s="76" t="inlineStr">
         <is>
-          <t>Supports Business Line Approval of Results (column O), samples 3301, 1903, 1937</t>
+          <t>Supports Business Line Approval of Results (column O), samples 1917, 1937</t>
         </is>
       </c>
       <c r="G61" s="77" t="inlineStr">
@@ -15170,26 +14466,26 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H61" s="68" t="n"/>
-      <c r="I61" s="68" t="n"/>
-      <c r="J61" s="68" t="n"/>
-      <c r="K61" s="68" t="n"/>
-      <c r="L61" s="68" t="n"/>
-      <c r="M61" s="68" t="n"/>
-      <c r="N61" s="68" t="n"/>
-      <c r="O61" s="68" t="n"/>
-      <c r="P61" s="68" t="n"/>
-      <c r="Q61" s="68" t="n"/>
-      <c r="R61" s="68" t="n"/>
-      <c r="S61" s="68" t="n"/>
-      <c r="T61" s="68" t="n"/>
-      <c r="U61" s="68" t="n"/>
-      <c r="V61" s="68" t="n"/>
-      <c r="W61" s="85" t="n"/>
-      <c r="X61" s="85" t="n"/>
-      <c r="Y61" s="85" t="n"/>
-      <c r="Z61" s="85" t="n"/>
-      <c r="AA61" s="85" t="n"/>
+      <c r="H61" s="70" t="n"/>
+      <c r="I61" s="70" t="n"/>
+      <c r="J61" s="70" t="n"/>
+      <c r="K61" s="70" t="n"/>
+      <c r="L61" s="70" t="n"/>
+      <c r="M61" s="69" t="n"/>
+      <c r="N61" s="69" t="n"/>
+      <c r="O61" s="69" t="n"/>
+      <c r="P61" s="69" t="n"/>
+      <c r="Q61" s="69" t="n"/>
+      <c r="R61" s="70" t="n"/>
+      <c r="S61" s="70" t="n"/>
+      <c r="T61" s="70" t="n"/>
+      <c r="U61" s="70" t="n"/>
+      <c r="V61" s="86" t="n"/>
+      <c r="W61" s="87" t="n"/>
+      <c r="X61" s="87" t="n"/>
+      <c r="Y61" s="87" t="n"/>
+      <c r="Z61" s="87" t="n"/>
+      <c r="AA61" s="87" t="n"/>
       <c r="AB61" s="85" t="n"/>
       <c r="AC61" s="85" t="n"/>
       <c r="AD61" s="85" t="n"/>
@@ -15215,38 +14511,40 @@
       <c r="AX61" s="85" t="n"/>
       <c r="AY61" s="85" t="n"/>
     </row>
-    <row r="62" ht="88" customHeight="1" s="50">
+    <row r="62" ht="78" customHeight="1" s="50">
       <c r="A62" s="78" t="inlineStr">
         <is>
-          <t>DMA04</t>
+          <t>DMA01</t>
         </is>
       </c>
       <c r="B62" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
         <v/>
       </c>
       <c r="C62" s="76" t="inlineStr">
         <is>
-          <t>08/17/2026, Michelle Oropesa</t>
+          <t>08/18/2026, Claudia Romero</t>
         </is>
       </c>
       <c r="D62" s="76" t="inlineStr">
         <is>
-          <t>4052 Interface Monitor
-1936 Swift Interface - BSI
+          <t>1822 ACH Express
+1867 FedExport - BSI
+1868 FedImport - BSI
+3299 Imaging101
 1937 T24</t>
         </is>
       </c>
       <c r="E62" s="76" t="inlineStr">
         <is>
-          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).
+          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation, attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).
 Checked for Business Line Approval of Results:
 Application / record agreed to the evidence.</t>
         </is>
       </c>
       <c r="F62" s="76" t="inlineStr">
         <is>
-          <t>Supports Business Line Approval of Results (column O), samples 4052, 1936, 1937</t>
+          <t>Supports Business Line Approval of Results (column O), samples 1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="G62" s="77" t="inlineStr">
@@ -15254,26 +14552,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H62" s="68" t="n"/>
-      <c r="I62" s="68" t="n"/>
-      <c r="J62" s="68" t="n"/>
-      <c r="K62" s="68" t="n"/>
-      <c r="L62" s="68" t="n"/>
-      <c r="M62" s="68" t="n"/>
-      <c r="N62" s="68" t="n"/>
-      <c r="O62" s="68" t="n"/>
-      <c r="P62" s="68" t="n"/>
-      <c r="Q62" s="68" t="n"/>
-      <c r="R62" s="68" t="n"/>
-      <c r="S62" s="68" t="n"/>
-      <c r="T62" s="68" t="n"/>
-      <c r="U62" s="68" t="n"/>
-      <c r="V62" s="68" t="n"/>
-      <c r="W62" s="85" t="n"/>
-      <c r="X62" s="85" t="n"/>
-      <c r="Y62" s="85" t="n"/>
-      <c r="Z62" s="85" t="n"/>
-      <c r="AA62" s="85" t="n"/>
       <c r="AB62" s="85" t="n"/>
       <c r="AC62" s="85" t="n"/>
       <c r="AD62" s="85" t="n"/>
@@ -15299,34 +14577,46 @@
       <c r="AX62" s="85" t="n"/>
       <c r="AY62" s="85" t="n"/>
     </row>
-    <row r="63">
-      <c r="A63" s="74" t="n"/>
-      <c r="B63" s="74" t="n"/>
-      <c r="C63" s="74" t="n"/>
-      <c r="D63" s="74" t="n"/>
-      <c r="E63" s="74" t="n"/>
-      <c r="F63" s="74" t="n"/>
-      <c r="G63" s="74" t="n"/>
-      <c r="H63" s="68" t="n"/>
-      <c r="I63" s="68" t="n"/>
-      <c r="J63" s="68" t="n"/>
-      <c r="K63" s="68" t="n"/>
-      <c r="L63" s="68" t="n"/>
-      <c r="M63" s="68" t="n"/>
-      <c r="N63" s="68" t="n"/>
-      <c r="O63" s="68" t="n"/>
-      <c r="P63" s="68" t="n"/>
-      <c r="Q63" s="68" t="n"/>
-      <c r="R63" s="68" t="n"/>
-      <c r="S63" s="68" t="n"/>
-      <c r="T63" s="68" t="n"/>
-      <c r="U63" s="68" t="n"/>
-      <c r="V63" s="68" t="n"/>
-      <c r="W63" s="85" t="n"/>
-      <c r="X63" s="85" t="n"/>
-      <c r="Y63" s="85" t="n"/>
-      <c r="Z63" s="85" t="n"/>
-      <c r="AA63" s="85" t="n"/>
+    <row r="63" ht="136" customHeight="1" s="50">
+      <c r="A63" s="78" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="B63" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C63" s="76" t="inlineStr">
+        <is>
+          <t>08/19/2026, David Marquez</t>
+        </is>
+      </c>
+      <c r="D63" s="76" t="inlineStr">
+        <is>
+          <t>3299 Imaging101
+1903 OFAC - BSI
+1936 Swift Interface - BSI
+1937 T24</t>
+        </is>
+      </c>
+      <c r="E63" s="76" t="inlineStr">
+        <is>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
+Checked for Business Line Approval of Results:
+Application / record agreed to the evidence.</t>
+        </is>
+      </c>
+      <c r="F63" s="76" t="inlineStr">
+        <is>
+          <t>Supports Business Line Approval of Results (column O), samples 3299, 1903, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G63" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB63" s="85" t="n"/>
       <c r="AC63" s="85" t="n"/>
       <c r="AD63" s="85" t="n"/>
@@ -15352,38 +14642,45 @@
       <c r="AX63" s="85" t="n"/>
       <c r="AY63" s="85" t="n"/>
     </row>
-    <row r="64" ht="15.5" customHeight="1" s="50">
-      <c r="A64" s="71" t="inlineStr">
-        <is>
-          <t>Business Line Approval Results: Email (folder 02), Review of results documents and approval email</t>
-        </is>
-      </c>
-      <c r="B64" s="97" t="n"/>
-      <c r="C64" s="97" t="n"/>
-      <c r="D64" s="97" t="n"/>
-      <c r="E64" s="97" t="n"/>
-      <c r="F64" s="97" t="n"/>
-      <c r="G64" s="98" t="n"/>
-      <c r="H64" s="68" t="n"/>
-      <c r="I64" s="68" t="n"/>
-      <c r="J64" s="68" t="n"/>
-      <c r="K64" s="68" t="n"/>
-      <c r="L64" s="68" t="n"/>
-      <c r="M64" s="68" t="n"/>
-      <c r="N64" s="68" t="n"/>
-      <c r="O64" s="68" t="n"/>
-      <c r="P64" s="68" t="n"/>
-      <c r="Q64" s="68" t="n"/>
-      <c r="R64" s="68" t="n"/>
-      <c r="S64" s="68" t="n"/>
-      <c r="T64" s="68" t="n"/>
-      <c r="U64" s="68" t="n"/>
-      <c r="V64" s="68" t="n"/>
-      <c r="W64" s="85" t="n"/>
-      <c r="X64" s="85" t="n"/>
-      <c r="Y64" s="85" t="n"/>
-      <c r="Z64" s="85" t="n"/>
-      <c r="AA64" s="85" t="n"/>
+    <row r="64" ht="78" customHeight="1" s="50">
+      <c r="A64" s="78" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="B64" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C64" s="76" t="inlineStr">
+        <is>
+          <t>08/18/2026, Frank Puentes</t>
+        </is>
+      </c>
+      <c r="D64" s="76" t="inlineStr">
+        <is>
+          <t>3301 MQ Payment Monitor
+1903 OFAC - BSI
+1937 T24</t>
+        </is>
+      </c>
+      <c r="E64" s="76" t="inlineStr">
+        <is>
+          <t>Frank Puentes returns the signed attestation: attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).
+Checked for Business Line Approval of Results:
+Application / record agreed to the evidence.</t>
+        </is>
+      </c>
+      <c r="F64" s="76" t="inlineStr">
+        <is>
+          <t>Supports Business Line Approval of Results (column O), samples 3301, 1903, 1937</t>
+        </is>
+      </c>
+      <c r="G64" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB64" s="85" t="n"/>
       <c r="AC64" s="85" t="n"/>
       <c r="AD64" s="85" t="n"/>
@@ -15409,62 +14706,45 @@
       <c r="AX64" s="85" t="n"/>
       <c r="AY64" s="85" t="n"/>
     </row>
-    <row r="65" ht="26" customHeight="1" s="50">
-      <c r="A65" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B65" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C65" s="73" t="inlineStr">
-        <is>
-          <t>Business line / date / operator</t>
-        </is>
-      </c>
-      <c r="D65" s="73" t="inlineStr">
-        <is>
-          <t>DIV applications in scope (per document)</t>
-        </is>
-      </c>
-      <c r="E65" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F65" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G65" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H65" s="68" t="n"/>
-      <c r="I65" s="68" t="n"/>
-      <c r="J65" s="68" t="n"/>
-      <c r="K65" s="68" t="n"/>
-      <c r="L65" s="68" t="n"/>
-      <c r="M65" s="68" t="n"/>
-      <c r="N65" s="68" t="n"/>
-      <c r="O65" s="68" t="n"/>
-      <c r="P65" s="68" t="n"/>
-      <c r="Q65" s="68" t="n"/>
-      <c r="R65" s="68" t="n"/>
-      <c r="S65" s="68" t="n"/>
-      <c r="T65" s="68" t="n"/>
-      <c r="U65" s="68" t="n"/>
-      <c r="V65" s="68" t="n"/>
-      <c r="W65" s="85" t="n"/>
-      <c r="X65" s="85" t="n"/>
-      <c r="Y65" s="85" t="n"/>
-      <c r="Z65" s="85" t="n"/>
-      <c r="AA65" s="85" t="n"/>
+    <row r="65" ht="88" customHeight="1" s="50">
+      <c r="A65" s="78" t="inlineStr">
+        <is>
+          <t>DMA04</t>
+        </is>
+      </c>
+      <c r="B65" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C65" s="76" t="inlineStr">
+        <is>
+          <t>08/17/2026, Michelle Oropesa</t>
+        </is>
+      </c>
+      <c r="D65" s="76" t="inlineStr">
+        <is>
+          <t>4052 Interface Monitor
+1936 Swift Interface - BSI
+1937 T24</t>
+        </is>
+      </c>
+      <c r="E65" s="76" t="inlineStr">
+        <is>
+          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).
+Checked for Business Line Approval of Results:
+Application / record agreed to the evidence.</t>
+        </is>
+      </c>
+      <c r="F65" s="76" t="inlineStr">
+        <is>
+          <t>Supports Business Line Approval of Results (column O), samples 4052, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="G65" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB65" s="85" t="n"/>
       <c r="AC65" s="85" t="n"/>
       <c r="AD65" s="85" t="n"/>
@@ -15490,61 +14770,34 @@
       <c r="AX65" s="85" t="n"/>
       <c r="AY65" s="85" t="n"/>
     </row>
-    <row r="66" ht="64" customHeight="1" s="50">
-      <c r="A66" s="76" t="inlineStr">
-        <is>
-          <t>BLA01</t>
-        </is>
-      </c>
-      <c r="B66" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
-      </c>
-      <c r="C66" s="76" t="inlineStr">
-        <is>
-          <t>11/15/2025, Client Back Office (operator Raimy Ayala)</t>
-        </is>
-      </c>
-      <c r="D66" s="76" t="inlineStr">
-        <is>
-          <t>FedImport, FedExport, Imaging101, T24 (ACH Express import step evidenced p.5)</t>
-        </is>
-      </c>
-      <c r="E66" s="76" t="inlineStr">
-        <is>
-          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y, "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
-        </is>
-      </c>
-      <c r="F66" s="76" t="inlineStr">
-        <is>
-          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 1822, 1867, 1868, 3299, 1937</t>
-        </is>
-      </c>
-      <c r="G66" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H66" s="68" t="n"/>
-      <c r="I66" s="68" t="n"/>
-      <c r="J66" s="68" t="n"/>
-      <c r="K66" s="68" t="n"/>
-      <c r="L66" s="68" t="n"/>
-      <c r="M66" s="68" t="n"/>
-      <c r="N66" s="68" t="n"/>
-      <c r="O66" s="68" t="n"/>
-      <c r="P66" s="68" t="n"/>
-      <c r="Q66" s="68" t="n"/>
-      <c r="R66" s="68" t="n"/>
-      <c r="S66" s="68" t="n"/>
-      <c r="T66" s="68" t="n"/>
-      <c r="U66" s="68" t="n"/>
-      <c r="V66" s="68" t="n"/>
-      <c r="W66" s="85" t="n"/>
-      <c r="X66" s="85" t="n"/>
-      <c r="Y66" s="85" t="n"/>
-      <c r="Z66" s="85" t="n"/>
-      <c r="AA66" s="85" t="n"/>
+    <row r="66" s="50">
+      <c r="A66" s="74" t="n"/>
+      <c r="B66" s="74" t="n"/>
+      <c r="C66" s="74" t="n"/>
+      <c r="D66" s="74" t="n"/>
+      <c r="E66" s="74" t="n"/>
+      <c r="F66" s="74" t="n"/>
+      <c r="G66" s="74" t="n"/>
+      <c r="H66" s="74" t="n"/>
+      <c r="I66" s="74" t="n"/>
+      <c r="J66" s="74" t="n"/>
+      <c r="K66" s="74" t="n"/>
+      <c r="L66" s="74" t="n"/>
+      <c r="M66" s="74" t="n"/>
+      <c r="N66" s="74" t="n"/>
+      <c r="O66" s="74" t="n"/>
+      <c r="P66" s="74" t="n"/>
+      <c r="Q66" s="74" t="n"/>
+      <c r="R66" s="74" t="n"/>
+      <c r="S66" s="74" t="n"/>
+      <c r="T66" s="74" t="n"/>
+      <c r="U66" s="74" t="n"/>
+      <c r="V66" s="74" t="n"/>
+      <c r="W66" s="74" t="n"/>
+      <c r="X66" s="74" t="n"/>
+      <c r="Y66" s="74" t="n"/>
+      <c r="Z66" s="74" t="n"/>
+      <c r="AA66" s="74" t="n"/>
       <c r="AB66" s="85" t="n"/>
       <c r="AC66" s="85" t="n"/>
       <c r="AD66" s="85" t="n"/>
@@ -15570,61 +14823,18 @@
       <c r="AX66" s="85" t="n"/>
       <c r="AY66" s="85" t="n"/>
     </row>
-    <row r="67" ht="64" customHeight="1" s="50">
-      <c r="A67" s="76" t="inlineStr">
-        <is>
-          <t>BLA02</t>
-        </is>
-      </c>
-      <c r="B67" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
-      </c>
-      <c r="C67" s="76" t="inlineStr">
-        <is>
-          <t>11/15/2025, BSA/AML/OFAC Compliance (operator David Marquez)</t>
-        </is>
-      </c>
-      <c r="D67" s="76" t="inlineStr">
-        <is>
-          <t>T24, Imaging101, OFAC</t>
-        </is>
-      </c>
-      <c r="E67" s="76" t="inlineStr">
-        <is>
-          <t>OFAC Verifier test script. Application in-scope: T24, Imaging101, OFAC. DIV procedure instructions listed; production-day (11/14/2025) versus test-day (11/15/2025) screenshots for T24, Imaging101/ModeloIC and OFAC Report 64. NOTE: DIV Yes/No answer boxes on p.1 are blank.</t>
-        </is>
-      </c>
-      <c r="F67" s="76" t="inlineStr">
-        <is>
-          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 3299, 1903, 1937</t>
-        </is>
-      </c>
-      <c r="G67" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H67" s="68" t="n"/>
-      <c r="I67" s="68" t="n"/>
-      <c r="J67" s="68" t="n"/>
-      <c r="K67" s="68" t="n"/>
-      <c r="L67" s="68" t="n"/>
-      <c r="M67" s="68" t="n"/>
-      <c r="N67" s="68" t="n"/>
-      <c r="O67" s="68" t="n"/>
-      <c r="P67" s="68" t="n"/>
-      <c r="Q67" s="68" t="n"/>
-      <c r="R67" s="68" t="n"/>
-      <c r="S67" s="68" t="n"/>
-      <c r="T67" s="68" t="n"/>
-      <c r="U67" s="68" t="n"/>
-      <c r="V67" s="68" t="n"/>
-      <c r="W67" s="85" t="n"/>
-      <c r="X67" s="85" t="n"/>
-      <c r="Y67" s="85" t="n"/>
-      <c r="Z67" s="85" t="n"/>
-      <c r="AA67" s="85" t="n"/>
+    <row r="67" ht="41" customHeight="1" s="50">
+      <c r="A67" s="101" t="inlineStr">
+        <is>
+          <t>15. Results Documented in BCMS (column P): review of evidence files and results</t>
+        </is>
+      </c>
+      <c r="B67" s="97" t="n"/>
+      <c r="C67" s="97" t="n"/>
+      <c r="D67" s="97" t="n"/>
+      <c r="E67" s="97" t="n"/>
+      <c r="F67" s="97" t="n"/>
+      <c r="G67" s="98" t="n"/>
       <c r="AB67" s="85" t="n"/>
       <c r="AC67" s="85" t="n"/>
       <c r="AD67" s="85" t="n"/>
@@ -15650,61 +14860,43 @@
       <c r="AX67" s="85" t="n"/>
       <c r="AY67" s="85" t="n"/>
     </row>
-    <row r="68" ht="52" customHeight="1" s="50">
-      <c r="A68" s="76" t="inlineStr">
-        <is>
-          <t>BLA03</t>
-        </is>
-      </c>
-      <c r="B68" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
-      </c>
-      <c r="C68" s="76" t="inlineStr">
-        <is>
-          <t>11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)</t>
-        </is>
-      </c>
-      <c r="D68" s="76" t="inlineStr">
-        <is>
-          <t>T24, MQ Payment Monitor, OFAC - BSI, Fedlink - BSI, Swift Interface - BSI</t>
-        </is>
-      </c>
-      <c r="E68" s="76" t="inlineStr">
-        <is>
-          <t>Wire Transfer / Cash Mgt / Financial Messaging script. DIV application in-scope: T24, MQ Payment Monitor, OFAC - BSI, Fedlink - BSI, Swift Interface - BSI. Format / Headers / Content = yes; data from 11/14/2025 Fed &amp; SWIFT reconciled.</t>
-        </is>
-      </c>
-      <c r="F68" s="76" t="inlineStr">
-        <is>
-          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="G68" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H68" s="68" t="n"/>
-      <c r="I68" s="68" t="n"/>
-      <c r="J68" s="68" t="n"/>
-      <c r="K68" s="68" t="n"/>
-      <c r="L68" s="68" t="n"/>
-      <c r="M68" s="68" t="n"/>
-      <c r="N68" s="68" t="n"/>
-      <c r="O68" s="68" t="n"/>
-      <c r="P68" s="68" t="n"/>
-      <c r="Q68" s="68" t="n"/>
-      <c r="R68" s="68" t="n"/>
-      <c r="S68" s="68" t="n"/>
-      <c r="T68" s="68" t="n"/>
-      <c r="U68" s="68" t="n"/>
-      <c r="V68" s="68" t="n"/>
-      <c r="W68" s="85" t="n"/>
-      <c r="X68" s="85" t="n"/>
-      <c r="Y68" s="85" t="n"/>
-      <c r="Z68" s="85" t="n"/>
-      <c r="AA68" s="85" t="n"/>
+    <row r="68" ht="26" customHeight="1" s="50">
+      <c r="A68" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B68" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C68" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner / operator</t>
+        </is>
+      </c>
+      <c r="D68" s="73" t="inlineStr">
+        <is>
+          <t>Applications tested (source rows)</t>
+        </is>
+      </c>
+      <c r="E68" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F68" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G68" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="H68" s="67" t="n"/>
       <c r="AB68" s="85" t="n"/>
       <c r="AC68" s="85" t="n"/>
       <c r="AD68" s="85" t="n"/>
@@ -15730,34 +14922,45 @@
       <c r="AX68" s="85" t="n"/>
       <c r="AY68" s="85" t="n"/>
     </row>
-    <row r="69" ht="64" customHeight="1" s="50">
-      <c r="A69" s="76" t="inlineStr">
-        <is>
-          <t>BLA04</t>
+    <row r="69" ht="174" customHeight="1" s="50">
+      <c r="A69" s="78" t="inlineStr">
+        <is>
+          <t>E03</t>
         </is>
       </c>
       <c r="B69" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
         <v/>
       </c>
       <c r="C69" s="76" t="inlineStr">
         <is>
-          <t>11/15/2025, Investment Operations (operator Michelle Oropesa)</t>
+          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="D69" s="76" t="inlineStr">
         <is>
-          <t>T24 &amp; Swift Interface - BSI (Swift Interface Monitor accessed)</t>
+          <t>1822 ACH Express (E03 row 47)
+1867 FedExport - BSI (E03 row 9)
+1868 FedImport - BSI (E03 row 10)
+3299 Imaging101 (E03 row 5, 11, 13, 51, 53, 57)
+4052 Interface Monitor (E03 row 61)
+3301 MQ Payment Monitor (E03 row 25, 29)
+1903 OFAC - BSI (E03 row 6, 26, 30, 34, 58)
+1917 ReconXpert (E03 row 17)
+1936 Swift Interface - BSI (E03 row 7, 60)
+1937 T24 (E03 row 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63)</t>
         </is>
       </c>
       <c r="E69" s="76" t="inlineStr">
         <is>
-          <t>Treasury Hub &amp; Derivatives Operations script. Systems accessed: Swift Interface Monitor - BSI, T24, MS Office, DTCC. DIV application in-scope: T24 &amp; Swift Interface - BSI. Incoming MT300 and FX S reports matched 11/14 versus 11/15; Format / Headers / Content = Yes.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+Checked for Results Documented in BCMS:
+DIV results, business tester, validation date, manager approval and attestation fields recorded in BCMS (BC in the Cloud) for each application</t>
         </is>
       </c>
       <c r="F69" s="76" t="inlineStr">
         <is>
-          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 4052, 1936, 1937</t>
+          <t>Supports Results Documented in BCMS (column P), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="G69" s="77" t="inlineStr">
@@ -15765,26 +14968,12 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H69" s="68" t="n"/>
-      <c r="I69" s="68" t="n"/>
-      <c r="J69" s="68" t="n"/>
-      <c r="K69" s="68" t="n"/>
-      <c r="L69" s="68" t="n"/>
-      <c r="M69" s="68" t="n"/>
-      <c r="N69" s="68" t="n"/>
-      <c r="O69" s="68" t="n"/>
-      <c r="P69" s="68" t="n"/>
-      <c r="Q69" s="68" t="n"/>
-      <c r="R69" s="68" t="n"/>
-      <c r="S69" s="68" t="n"/>
-      <c r="T69" s="68" t="n"/>
-      <c r="U69" s="68" t="n"/>
-      <c r="V69" s="68" t="n"/>
-      <c r="W69" s="85" t="n"/>
-      <c r="X69" s="85" t="n"/>
-      <c r="Y69" s="85" t="n"/>
-      <c r="Z69" s="85" t="n"/>
-      <c r="AA69" s="85" t="n"/>
+      <c r="H69" s="70" t="n"/>
+      <c r="I69" s="70" t="n"/>
+      <c r="J69" s="70" t="n"/>
+      <c r="K69" s="69" t="n"/>
+      <c r="L69" s="70" t="n"/>
+      <c r="M69" s="70" t="n"/>
       <c r="AB69" s="85" t="n"/>
       <c r="AC69" s="85" t="n"/>
       <c r="AD69" s="85" t="n"/>
@@ -15810,61 +14999,14 @@
       <c r="AX69" s="85" t="n"/>
       <c r="AY69" s="85" t="n"/>
     </row>
-    <row r="70" ht="46" customHeight="1" s="50">
-      <c r="A70" s="76" t="inlineStr">
-        <is>
-          <t>BLA05</t>
-        </is>
-      </c>
-      <c r="B70" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
-        <v/>
-      </c>
-      <c r="C70" s="76" t="inlineStr">
-        <is>
-          <t>11/15/2025, Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)</t>
-        </is>
-      </c>
-      <c r="D70" s="76" t="inlineStr">
-        <is>
-          <t>T24 &amp; ReconXpert</t>
-        </is>
-      </c>
-      <c r="E70" s="76" t="inlineStr">
-        <is>
-          <t>General ledger review script. DIV application in-scope: T24 &amp; ReconXpert. Reconciliations passed; Format / Headers / Content = Yes, "No discrepancies found on the report".</t>
-        </is>
-      </c>
-      <c r="F70" s="76" t="inlineStr">
-        <is>
-          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 1917, 1937</t>
-        </is>
-      </c>
-      <c r="G70" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H70" s="68" t="n"/>
-      <c r="I70" s="68" t="n"/>
-      <c r="J70" s="68" t="n"/>
-      <c r="K70" s="68" t="n"/>
-      <c r="L70" s="68" t="n"/>
-      <c r="M70" s="68" t="n"/>
-      <c r="N70" s="68" t="n"/>
-      <c r="O70" s="68" t="n"/>
-      <c r="P70" s="68" t="n"/>
-      <c r="Q70" s="68" t="n"/>
-      <c r="R70" s="68" t="n"/>
-      <c r="S70" s="68" t="n"/>
-      <c r="T70" s="68" t="n"/>
-      <c r="U70" s="68" t="n"/>
-      <c r="V70" s="68" t="n"/>
-      <c r="W70" s="85" t="n"/>
-      <c r="X70" s="85" t="n"/>
-      <c r="Y70" s="85" t="n"/>
-      <c r="Z70" s="85" t="n"/>
-      <c r="AA70" s="85" t="n"/>
+    <row r="70" s="50">
+      <c r="A70" s="74" t="n"/>
+      <c r="B70" s="74" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
+      <c r="G70" s="74" t="n"/>
       <c r="AB70" s="85" t="n"/>
       <c r="AC70" s="85" t="n"/>
       <c r="AD70" s="85" t="n"/>
@@ -15890,61 +15032,18 @@
       <c r="AX70" s="85" t="n"/>
       <c r="AY70" s="85" t="n"/>
     </row>
-    <row r="71" ht="46" customHeight="1" s="50">
-      <c r="A71" s="76" t="inlineStr">
-        <is>
-          <t>BLA06</t>
-        </is>
-      </c>
-      <c r="B71" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C71" s="76" t="inlineStr">
-        <is>
-          <t>12/31/2025 &amp; 01/26/2026, Sadis Alvarenga</t>
-        </is>
-      </c>
-      <c r="D71" s="76" t="inlineStr">
-        <is>
-          <t>Financial Analysis &amp; Control (T24, ReconXpert)</t>
-        </is>
-      </c>
-      <c r="E71" s="76" t="inlineStr">
-        <is>
-          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.</t>
-        </is>
-      </c>
-      <c r="F71" s="76" t="inlineStr">
-        <is>
-          <t>Business line manager approval (Sadis Alvarenga), in period (01/26/2026), samples 1917, 1937</t>
-        </is>
-      </c>
-      <c r="G71" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H71" s="68" t="n"/>
-      <c r="I71" s="68" t="n"/>
-      <c r="J71" s="68" t="n"/>
-      <c r="K71" s="68" t="n"/>
-      <c r="L71" s="68" t="n"/>
-      <c r="M71" s="68" t="n"/>
-      <c r="N71" s="68" t="n"/>
-      <c r="O71" s="68" t="n"/>
-      <c r="P71" s="68" t="n"/>
-      <c r="Q71" s="68" t="n"/>
-      <c r="R71" s="68" t="n"/>
-      <c r="S71" s="68" t="n"/>
-      <c r="T71" s="68" t="n"/>
-      <c r="U71" s="68" t="n"/>
-      <c r="V71" s="68" t="n"/>
-      <c r="W71" s="85" t="n"/>
-      <c r="X71" s="85" t="n"/>
-      <c r="Y71" s="85" t="n"/>
-      <c r="Z71" s="85" t="n"/>
-      <c r="AA71" s="85" t="n"/>
+    <row r="71" ht="15.5" customHeight="1" s="50">
+      <c r="A71" s="71" t="inlineStr">
+        <is>
+          <t>Business Line Approval Results: Email (folder 02), Review of results documents and approval email</t>
+        </is>
+      </c>
+      <c r="B71" s="97" t="n"/>
+      <c r="C71" s="97" t="n"/>
+      <c r="D71" s="97" t="n"/>
+      <c r="E71" s="97" t="n"/>
+      <c r="F71" s="97" t="n"/>
+      <c r="G71" s="98" t="n"/>
       <c r="AB71" s="85" t="n"/>
       <c r="AC71" s="85" t="n"/>
       <c r="AD71" s="85" t="n"/>
@@ -15970,34 +15069,42 @@
       <c r="AX71" s="85" t="n"/>
       <c r="AY71" s="85" t="n"/>
     </row>
-    <row r="72">
-      <c r="A72" s="74" t="n"/>
-      <c r="B72" s="74" t="n"/>
-      <c r="C72" s="74" t="n"/>
-      <c r="D72" s="74" t="n"/>
-      <c r="E72" s="74" t="n"/>
-      <c r="F72" s="74" t="n"/>
-      <c r="G72" s="74" t="n"/>
-      <c r="H72" s="68" t="n"/>
-      <c r="I72" s="68" t="n"/>
-      <c r="J72" s="68" t="n"/>
-      <c r="K72" s="68" t="n"/>
-      <c r="L72" s="68" t="n"/>
-      <c r="M72" s="68" t="n"/>
-      <c r="N72" s="68" t="n"/>
-      <c r="O72" s="68" t="n"/>
-      <c r="P72" s="68" t="n"/>
-      <c r="Q72" s="68" t="n"/>
-      <c r="R72" s="68" t="n"/>
-      <c r="S72" s="68" t="n"/>
-      <c r="T72" s="68" t="n"/>
-      <c r="U72" s="68" t="n"/>
-      <c r="V72" s="68" t="n"/>
-      <c r="W72" s="85" t="n"/>
-      <c r="X72" s="85" t="n"/>
-      <c r="Y72" s="85" t="n"/>
-      <c r="Z72" s="85" t="n"/>
-      <c r="AA72" s="85" t="n"/>
+    <row r="72" ht="26" customHeight="1" s="50">
+      <c r="A72" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B72" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C72" s="73" t="inlineStr">
+        <is>
+          <t>Business line / date / operator</t>
+        </is>
+      </c>
+      <c r="D72" s="73" t="inlineStr">
+        <is>
+          <t>DIV applications in scope (per document)</t>
+        </is>
+      </c>
+      <c r="E72" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F72" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G72" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
       <c r="AB72" s="85" t="n"/>
       <c r="AC72" s="85" t="n"/>
       <c r="AD72" s="85" t="n"/>
@@ -16023,38 +15130,41 @@
       <c r="AX72" s="85" t="n"/>
       <c r="AY72" s="85" t="n"/>
     </row>
-    <row r="73" ht="15.5" customHeight="1" s="50">
-      <c r="A73" s="71" t="inlineStr">
-        <is>
-          <t>DIV Manager Attestation Email Approvals (folder 03), application-specific business line manager approvals</t>
-        </is>
-      </c>
-      <c r="B73" s="97" t="n"/>
-      <c r="C73" s="97" t="n"/>
-      <c r="D73" s="97" t="n"/>
-      <c r="E73" s="97" t="n"/>
-      <c r="F73" s="97" t="n"/>
-      <c r="G73" s="98" t="n"/>
-      <c r="H73" s="68" t="n"/>
-      <c r="I73" s="68" t="n"/>
-      <c r="J73" s="68" t="n"/>
-      <c r="K73" s="68" t="n"/>
-      <c r="L73" s="68" t="n"/>
-      <c r="M73" s="68" t="n"/>
-      <c r="N73" s="68" t="n"/>
-      <c r="O73" s="68" t="n"/>
-      <c r="P73" s="68" t="n"/>
-      <c r="Q73" s="68" t="n"/>
-      <c r="R73" s="68" t="n"/>
-      <c r="S73" s="68" t="n"/>
-      <c r="T73" s="68" t="n"/>
-      <c r="U73" s="68" t="n"/>
-      <c r="V73" s="68" t="n"/>
-      <c r="W73" s="85" t="n"/>
-      <c r="X73" s="85" t="n"/>
-      <c r="Y73" s="85" t="n"/>
-      <c r="Z73" s="85" t="n"/>
-      <c r="AA73" s="85" t="n"/>
+    <row r="73" ht="64" customHeight="1" s="50">
+      <c r="A73" s="76" t="inlineStr">
+        <is>
+          <t>BLA01</t>
+        </is>
+      </c>
+      <c r="B73" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
+      </c>
+      <c r="C73" s="76" t="inlineStr">
+        <is>
+          <t>11/15/2025, Client Back Office (operator Raimy Ayala)</t>
+        </is>
+      </c>
+      <c r="D73" s="76" t="inlineStr">
+        <is>
+          <t>FedImport, FedExport, Imaging101, T24 (ACH Express import step evidenced p.5)</t>
+        </is>
+      </c>
+      <c r="E73" s="76" t="inlineStr">
+        <is>
+          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y, "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
+        </is>
+      </c>
+      <c r="F73" s="76" t="inlineStr">
+        <is>
+          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 1822, 1867, 1868, 3299, 1937</t>
+        </is>
+      </c>
+      <c r="G73" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB73" s="85" t="n"/>
       <c r="AC73" s="85" t="n"/>
       <c r="AD73" s="85" t="n"/>
@@ -16080,62 +15190,41 @@
       <c r="AX73" s="85" t="n"/>
       <c r="AY73" s="85" t="n"/>
     </row>
-    <row r="74" ht="26" customHeight="1" s="50">
-      <c r="A74" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B74" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C74" s="73" t="inlineStr">
-        <is>
-          <t>Approver / date</t>
-        </is>
-      </c>
-      <c r="D74" s="73" t="inlineStr">
-        <is>
-          <t>BCiC Department Manager and tested applications (E03 rows)</t>
-        </is>
-      </c>
-      <c r="E74" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F74" s="73" t="inlineStr">
-        <is>
-          <t>Conclusion / samples supported</t>
-        </is>
-      </c>
-      <c r="G74" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H74" s="68" t="n"/>
-      <c r="I74" s="68" t="n"/>
-      <c r="J74" s="68" t="n"/>
-      <c r="K74" s="68" t="n"/>
-      <c r="L74" s="68" t="n"/>
-      <c r="M74" s="68" t="n"/>
-      <c r="N74" s="68" t="n"/>
-      <c r="O74" s="68" t="n"/>
-      <c r="P74" s="68" t="n"/>
-      <c r="Q74" s="68" t="n"/>
-      <c r="R74" s="68" t="n"/>
-      <c r="S74" s="68" t="n"/>
-      <c r="T74" s="68" t="n"/>
-      <c r="U74" s="68" t="n"/>
-      <c r="V74" s="68" t="n"/>
-      <c r="W74" s="85" t="n"/>
-      <c r="X74" s="85" t="n"/>
-      <c r="Y74" s="85" t="n"/>
-      <c r="Z74" s="85" t="n"/>
-      <c r="AA74" s="85" t="n"/>
+    <row r="74" ht="64" customHeight="1" s="50">
+      <c r="A74" s="76" t="inlineStr">
+        <is>
+          <t>BLA02</t>
+        </is>
+      </c>
+      <c r="B74" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf")</f>
+        <v/>
+      </c>
+      <c r="C74" s="76" t="inlineStr">
+        <is>
+          <t>11/15/2025, BSA/AML/OFAC Compliance (operator David Marquez)</t>
+        </is>
+      </c>
+      <c r="D74" s="76" t="inlineStr">
+        <is>
+          <t>T24, Imaging101, OFAC</t>
+        </is>
+      </c>
+      <c r="E74" s="76" t="inlineStr">
+        <is>
+          <t>OFAC Verifier test script. Application in-scope: T24, Imaging101, OFAC. DIV procedure instructions listed; production-day (11/14/2025) versus test-day (11/15/2025) screenshots for T24, Imaging101/ModeloIC and OFAC Report 64. NOTE: DIV Yes/No answer boxes on p.1 are blank.</t>
+        </is>
+      </c>
+      <c r="F74" s="76" t="inlineStr">
+        <is>
+          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 3299, 1903, 1937</t>
+        </is>
+      </c>
+      <c r="G74" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB74" s="85" t="n"/>
       <c r="AC74" s="85" t="n"/>
       <c r="AD74" s="85" t="n"/>
@@ -16161,34 +15250,34 @@
       <c r="AX74" s="85" t="n"/>
       <c r="AY74" s="85" t="n"/>
     </row>
-    <row r="75" ht="46" customHeight="1" s="50">
+    <row r="75" ht="52" customHeight="1" s="50">
       <c r="A75" s="76" t="inlineStr">
         <is>
-          <t>DMA01</t>
+          <t>BLA03</t>
         </is>
       </c>
       <c r="B75" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf")</f>
         <v/>
       </c>
       <c r="C75" s="76" t="inlineStr">
         <is>
-          <t>08/18/2026, Claudia Romero</t>
+          <t>11/15/2025, Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)</t>
         </is>
       </c>
       <c r="D75" s="76" t="inlineStr">
         <is>
-          <t>FedExport - BSI (row 9); FedImport - BSI (row 10); Imaging101 (rows 11, 13); T24 (rows 12, 14, 48); ACH Express (row 47)</t>
+          <t>T24, MQ Payment Monitor, OFAC - BSI, Fedlink - BSI, Swift Interface - BSI</t>
         </is>
       </c>
       <c r="E75" s="76" t="inlineStr">
         <is>
-          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation, attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).</t>
+          <t>Wire Transfer / Cash Mgt / Financial Messaging script. DIV application in-scope: T24, MQ Payment Monitor, OFAC - BSI, Fedlink - BSI, Swift Interface - BSI. Format / Headers / Content = yes; data from 11/14/2025 Fed &amp; SWIFT reconciled.</t>
         </is>
       </c>
       <c r="F75" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 8 DIV records: in-period approval evidence, samples 1822, 1867, 1868, 3299, 1937</t>
+          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="G75" s="77" t="inlineStr">
@@ -16196,26 +15285,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H75" s="68" t="n"/>
-      <c r="I75" s="68" t="n"/>
-      <c r="J75" s="68" t="n"/>
-      <c r="K75" s="68" t="n"/>
-      <c r="L75" s="68" t="n"/>
-      <c r="M75" s="68" t="n"/>
-      <c r="N75" s="68" t="n"/>
-      <c r="O75" s="68" t="n"/>
-      <c r="P75" s="68" t="n"/>
-      <c r="Q75" s="68" t="n"/>
-      <c r="R75" s="68" t="n"/>
-      <c r="S75" s="68" t="n"/>
-      <c r="T75" s="68" t="n"/>
-      <c r="U75" s="68" t="n"/>
-      <c r="V75" s="68" t="n"/>
-      <c r="W75" s="85" t="n"/>
-      <c r="X75" s="85" t="n"/>
-      <c r="Y75" s="85" t="n"/>
-      <c r="Z75" s="85" t="n"/>
-      <c r="AA75" s="85" t="n"/>
       <c r="AB75" s="85" t="n"/>
       <c r="AC75" s="85" t="n"/>
       <c r="AD75" s="85" t="n"/>
@@ -16241,34 +15310,34 @@
       <c r="AX75" s="85" t="n"/>
       <c r="AY75" s="85" t="n"/>
     </row>
-    <row r="76" ht="100" customHeight="1" s="50">
+    <row r="76" ht="64" customHeight="1" s="50">
       <c r="A76" s="76" t="inlineStr">
         <is>
-          <t>DMA02</t>
+          <t>BLA04</t>
         </is>
       </c>
       <c r="B76" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx","\","/"),"02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx")</f>
         <v/>
       </c>
       <c r="C76" s="76" t="inlineStr">
         <is>
-          <t>08/19/2026, David Marquez</t>
+          <t>11/15/2025, Investment Operations (operator Michelle Oropesa)</t>
         </is>
       </c>
       <c r="D76" s="76" t="inlineStr">
         <is>
-          <t>Imaging101 (row 5); OFAC - BSI (row 6); Swift Interface - BSI (row 7); T24 (row 8)</t>
+          <t>T24 &amp; Swift Interface - BSI (Swift Interface Monitor accessed)</t>
         </is>
       </c>
       <c r="E76" s="76" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.</t>
+          <t>Treasury Hub &amp; Derivatives Operations script. Systems accessed: Swift Interface Monitor - BSI, T24, MS Office, DTCC. DIV application in-scope: T24 &amp; Swift Interface - BSI. Incoming MT300 and FX S reports matched 11/14 versus 11/15; Format / Headers / Content = Yes.</t>
         </is>
       </c>
       <c r="F76" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 4 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 11/15/2025), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 4052, 1936, 1937</t>
         </is>
       </c>
       <c r="G76" s="77" t="inlineStr">
@@ -16276,26 +15345,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H76" s="68" t="n"/>
-      <c r="I76" s="68" t="n"/>
-      <c r="J76" s="68" t="n"/>
-      <c r="K76" s="68" t="n"/>
-      <c r="L76" s="68" t="n"/>
-      <c r="M76" s="68" t="n"/>
-      <c r="N76" s="68" t="n"/>
-      <c r="O76" s="68" t="n"/>
-      <c r="P76" s="68" t="n"/>
-      <c r="Q76" s="68" t="n"/>
-      <c r="R76" s="68" t="n"/>
-      <c r="S76" s="68" t="n"/>
-      <c r="T76" s="68" t="n"/>
-      <c r="U76" s="68" t="n"/>
-      <c r="V76" s="68" t="n"/>
-      <c r="W76" s="85" t="n"/>
-      <c r="X76" s="85" t="n"/>
-      <c r="Y76" s="85" t="n"/>
-      <c r="Z76" s="85" t="n"/>
-      <c r="AA76" s="85" t="n"/>
       <c r="AB76" s="85" t="n"/>
       <c r="AC76" s="85" t="n"/>
       <c r="AD76" s="85" t="n"/>
@@ -16324,31 +15373,31 @@
     <row r="77" ht="46" customHeight="1" s="50">
       <c r="A77" s="76" t="inlineStr">
         <is>
-          <t>DMA03</t>
+          <t>BLA05</t>
         </is>
       </c>
       <c r="B77" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf","\","/"),"02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf")</f>
         <v/>
       </c>
       <c r="C77" s="76" t="inlineStr">
         <is>
-          <t>08/18/2026, Frank Puentes</t>
+          <t>11/15/2025, Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)</t>
         </is>
       </c>
       <c r="D77" s="76" t="inlineStr">
         <is>
-          <t>T24 (rows 23, 27, 31, 33); MQ Payment Monitor (rows 25, 29); OFAC - BSI (rows 26, 30, 34)</t>
+          <t>T24 &amp; ReconXpert</t>
         </is>
       </c>
       <c r="E77" s="76" t="inlineStr">
         <is>
-          <t>Frank Puentes returns the signed attestation: attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).</t>
+          <t>General ledger review script. DIV application in-scope: T24 &amp; ReconXpert. Reconciliations passed; Format / Headers / Content = Yes, "No discrepancies found on the report".</t>
         </is>
       </c>
       <c r="F77" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 9 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 12/18/2025), samples 3301, 1903, 1937</t>
+          <t>Business line DIV results document supports Business Data Validation, DIV procedures and Business Line Approval of Results, samples 1917, 1937</t>
         </is>
       </c>
       <c r="G77" s="77" t="inlineStr">
@@ -16356,26 +15405,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H77" s="68" t="n"/>
-      <c r="I77" s="68" t="n"/>
-      <c r="J77" s="68" t="n"/>
-      <c r="K77" s="68" t="n"/>
-      <c r="L77" s="68" t="n"/>
-      <c r="M77" s="68" t="n"/>
-      <c r="N77" s="68" t="n"/>
-      <c r="O77" s="68" t="n"/>
-      <c r="P77" s="68" t="n"/>
-      <c r="Q77" s="68" t="n"/>
-      <c r="R77" s="68" t="n"/>
-      <c r="S77" s="68" t="n"/>
-      <c r="T77" s="68" t="n"/>
-      <c r="U77" s="68" t="n"/>
-      <c r="V77" s="68" t="n"/>
-      <c r="W77" s="85" t="n"/>
-      <c r="X77" s="85" t="n"/>
-      <c r="Y77" s="85" t="n"/>
-      <c r="Z77" s="85" t="n"/>
-      <c r="AA77" s="85" t="n"/>
       <c r="AB77" s="85" t="n"/>
       <c r="AC77" s="85" t="n"/>
       <c r="AD77" s="85" t="n"/>
@@ -16401,34 +15430,34 @@
       <c r="AX77" s="85" t="n"/>
       <c r="AY77" s="85" t="n"/>
     </row>
-    <row r="78" ht="52" customHeight="1" s="50">
+    <row r="78" ht="46" customHeight="1" s="50">
       <c r="A78" s="76" t="inlineStr">
         <is>
-          <t>DMA04</t>
+          <t>BLA06</t>
         </is>
       </c>
       <c r="B78" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg","\","/"),"02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg"),"BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg")</f>
         <v/>
       </c>
       <c r="C78" s="76" t="inlineStr">
         <is>
-          <t>08/17/2026, Michelle Oropesa</t>
+          <t>12/31/2025 &amp; 01/26/2026, Sadis Alvarenga</t>
         </is>
       </c>
       <c r="D78" s="76" t="inlineStr">
         <is>
-          <t>T24 (rows 19, 20, 21); Swift Interface - BSI (row 60); Interface Monitor (row 61)</t>
+          <t>Financial Analysis &amp; Control (T24, ReconXpert)</t>
         </is>
       </c>
       <c r="E78" s="76" t="inlineStr">
         <is>
-          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).</t>
+          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.</t>
         </is>
       </c>
       <c r="F78" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 5 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/17/2026), samples 4052, 1936, 1937</t>
+          <t>Business line manager approval (Sadis Alvarenga), in period (01/26/2026), samples 1917, 1937</t>
         </is>
       </c>
       <c r="G78" s="77" t="inlineStr">
@@ -16436,26 +15465,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H78" s="68" t="n"/>
-      <c r="I78" s="68" t="n"/>
-      <c r="J78" s="68" t="n"/>
-      <c r="K78" s="68" t="n"/>
-      <c r="L78" s="68" t="n"/>
-      <c r="M78" s="68" t="n"/>
-      <c r="N78" s="68" t="n"/>
-      <c r="O78" s="68" t="n"/>
-      <c r="P78" s="68" t="n"/>
-      <c r="Q78" s="68" t="n"/>
-      <c r="R78" s="68" t="n"/>
-      <c r="S78" s="68" t="n"/>
-      <c r="T78" s="68" t="n"/>
-      <c r="U78" s="68" t="n"/>
-      <c r="V78" s="68" t="n"/>
-      <c r="W78" s="85" t="n"/>
-      <c r="X78" s="85" t="n"/>
-      <c r="Y78" s="85" t="n"/>
-      <c r="Z78" s="85" t="n"/>
-      <c r="AA78" s="85" t="n"/>
       <c r="AB78" s="85" t="n"/>
       <c r="AC78" s="85" t="n"/>
       <c r="AD78" s="85" t="n"/>
@@ -16481,61 +15490,14 @@
       <c r="AX78" s="85" t="n"/>
       <c r="AY78" s="85" t="n"/>
     </row>
-    <row r="79" ht="52" customHeight="1" s="50">
-      <c r="A79" s="76" t="inlineStr">
-        <is>
-          <t>DMA05</t>
-        </is>
-      </c>
-      <c r="B79" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C79" s="76" t="inlineStr">
-        <is>
-          <t>08/19/2026, Maria Teresa (Mayte) Del Cerro</t>
-        </is>
-      </c>
-      <c r="D79" s="76" t="inlineStr">
-        <is>
-          <t>T24 (rows 18, 54, 59); Imaging101 (rows 53, 57); OFAC - BSI (row 58)</t>
-        </is>
-      </c>
-      <c r="E79" s="76" t="inlineStr">
-        <is>
-          <t>Senior Director of Operations returns the signed attestation, attachments: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Maria Teresa Del Cerro Hontanilla, Director of Operations, 08/19/2026) and the BCiC export (same file as E16b).</t>
-        </is>
-      </c>
-      <c r="F79" s="76" t="inlineStr">
-        <is>
-          <t>Approval evidence for 6 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/19/2026), samples 3299, 1903, 1937</t>
-        </is>
-      </c>
-      <c r="G79" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H79" s="68" t="n"/>
-      <c r="I79" s="68" t="n"/>
-      <c r="J79" s="68" t="n"/>
-      <c r="K79" s="68" t="n"/>
-      <c r="L79" s="68" t="n"/>
-      <c r="M79" s="68" t="n"/>
-      <c r="N79" s="68" t="n"/>
-      <c r="O79" s="68" t="n"/>
-      <c r="P79" s="68" t="n"/>
-      <c r="Q79" s="68" t="n"/>
-      <c r="R79" s="68" t="n"/>
-      <c r="S79" s="68" t="n"/>
-      <c r="T79" s="68" t="n"/>
-      <c r="U79" s="68" t="n"/>
-      <c r="V79" s="68" t="n"/>
-      <c r="W79" s="85" t="n"/>
-      <c r="X79" s="85" t="n"/>
-      <c r="Y79" s="85" t="n"/>
-      <c r="Z79" s="85" t="n"/>
-      <c r="AA79" s="85" t="n"/>
+    <row r="79" s="50">
+      <c r="A79" s="74" t="n"/>
+      <c r="B79" s="74" t="n"/>
+      <c r="C79" s="74" t="n"/>
+      <c r="D79" s="74" t="n"/>
+      <c r="E79" s="74" t="n"/>
+      <c r="F79" s="74" t="n"/>
+      <c r="G79" s="74" t="n"/>
       <c r="AB79" s="85" t="n"/>
       <c r="AC79" s="85" t="n"/>
       <c r="AD79" s="85" t="n"/>
@@ -16561,61 +15523,18 @@
       <c r="AX79" s="85" t="n"/>
       <c r="AY79" s="85" t="n"/>
     </row>
-    <row r="80" ht="52" customHeight="1" s="50">
-      <c r="A80" s="76" t="inlineStr">
-        <is>
-          <t>DMA06</t>
-        </is>
-      </c>
-      <c r="B80" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C80" s="76" t="inlineStr">
-        <is>
-          <t>08/18/2026, Ricardo Garcia-Marques</t>
-        </is>
-      </c>
-      <c r="D80" s="76" t="inlineStr">
-        <is>
-          <t>T24 (rows 3, 35, 36, 37, 38, 39, 40, 63)</t>
-        </is>
-      </c>
-      <c r="E80" s="76" t="inlineStr">
-        <is>
-          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia), attachment: Data_Integrity_Attestation_Santander-BCiC_signed.pdf (e-signed MD, Head of Trading &amp; Capital Markets, 08/18/2026 11:45 AM EDT).</t>
-        </is>
-      </c>
-      <c r="F80" s="76" t="inlineStr">
-        <is>
-          <t>Approval evidence for 8 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026), samples 1937</t>
-        </is>
-      </c>
-      <c r="G80" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H80" s="68" t="n"/>
-      <c r="I80" s="68" t="n"/>
-      <c r="J80" s="68" t="n"/>
-      <c r="K80" s="68" t="n"/>
-      <c r="L80" s="68" t="n"/>
-      <c r="M80" s="68" t="n"/>
-      <c r="N80" s="68" t="n"/>
-      <c r="O80" s="68" t="n"/>
-      <c r="P80" s="68" t="n"/>
-      <c r="Q80" s="68" t="n"/>
-      <c r="R80" s="68" t="n"/>
-      <c r="S80" s="68" t="n"/>
-      <c r="T80" s="68" t="n"/>
-      <c r="U80" s="68" t="n"/>
-      <c r="V80" s="68" t="n"/>
-      <c r="W80" s="85" t="n"/>
-      <c r="X80" s="85" t="n"/>
-      <c r="Y80" s="85" t="n"/>
-      <c r="Z80" s="85" t="n"/>
-      <c r="AA80" s="85" t="n"/>
+    <row r="80" ht="15.5" customHeight="1" s="50">
+      <c r="A80" s="71" t="inlineStr">
+        <is>
+          <t>DIV Manager Attestation Email Approvals (folder 03), application-specific business line manager approvals</t>
+        </is>
+      </c>
+      <c r="B80" s="97" t="n"/>
+      <c r="C80" s="97" t="n"/>
+      <c r="D80" s="97" t="n"/>
+      <c r="E80" s="97" t="n"/>
+      <c r="F80" s="97" t="n"/>
+      <c r="G80" s="98" t="n"/>
       <c r="AB80" s="85" t="n"/>
       <c r="AC80" s="85" t="n"/>
       <c r="AD80" s="85" t="n"/>
@@ -16641,61 +15560,42 @@
       <c r="AX80" s="85" t="n"/>
       <c r="AY80" s="85" t="n"/>
     </row>
-    <row r="81" ht="46" customHeight="1" s="50">
-      <c r="A81" s="76" t="inlineStr">
-        <is>
-          <t>DMA07</t>
-        </is>
-      </c>
-      <c r="B81" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
-        <v/>
-      </c>
-      <c r="C81" s="76" t="inlineStr">
-        <is>
-          <t>08/18/2026, Martha Sullivan</t>
-        </is>
-      </c>
-      <c r="D81" s="76" t="inlineStr">
-        <is>
-          <t>T24 (rows 41, 42, 43, 44, 45, 46)</t>
-        </is>
-      </c>
-      <c r="E81" s="76" t="inlineStr">
-        <is>
-          <t>Martha Sullivan returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Balance Sheet Manager, Treasury).</t>
-        </is>
-      </c>
-      <c r="F81" s="76" t="inlineStr">
-        <is>
-          <t>Approval evidence for 6 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026), samples 1937</t>
-        </is>
-      </c>
-      <c r="G81" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H81" s="68" t="n"/>
-      <c r="I81" s="68" t="n"/>
-      <c r="J81" s="68" t="n"/>
-      <c r="K81" s="68" t="n"/>
-      <c r="L81" s="68" t="n"/>
-      <c r="M81" s="68" t="n"/>
-      <c r="N81" s="68" t="n"/>
-      <c r="O81" s="68" t="n"/>
-      <c r="P81" s="68" t="n"/>
-      <c r="Q81" s="68" t="n"/>
-      <c r="R81" s="68" t="n"/>
-      <c r="S81" s="68" t="n"/>
-      <c r="T81" s="68" t="n"/>
-      <c r="U81" s="68" t="n"/>
-      <c r="V81" s="68" t="n"/>
-      <c r="W81" s="85" t="n"/>
-      <c r="X81" s="85" t="n"/>
-      <c r="Y81" s="85" t="n"/>
-      <c r="Z81" s="85" t="n"/>
-      <c r="AA81" s="85" t="n"/>
+    <row r="81" ht="26" customHeight="1" s="50">
+      <c r="A81" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B81" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C81" s="73" t="inlineStr">
+        <is>
+          <t>Approver / date</t>
+        </is>
+      </c>
+      <c r="D81" s="73" t="inlineStr">
+        <is>
+          <t>BCiC Department Manager and tested applications (E03 rows)</t>
+        </is>
+      </c>
+      <c r="E81" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F81" s="73" t="inlineStr">
+        <is>
+          <t>Conclusion / samples supported</t>
+        </is>
+      </c>
+      <c r="G81" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
       <c r="AB81" s="85" t="n"/>
       <c r="AC81" s="85" t="n"/>
       <c r="AD81" s="85" t="n"/>
@@ -16724,31 +15624,31 @@
     <row r="82" ht="46" customHeight="1" s="50">
       <c r="A82" s="76" t="inlineStr">
         <is>
-          <t>DMA08</t>
+          <t>DMA01</t>
         </is>
       </c>
       <c r="B82" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg")</f>
         <v/>
       </c>
       <c r="C82" s="76" t="inlineStr">
         <is>
-          <t>08/18/2026, Ivan Caisapanta</t>
+          <t>08/18/2026, Claudia Romero</t>
         </is>
       </c>
       <c r="D82" s="76" t="inlineStr">
         <is>
-          <t>T24 (rows 55, 56)</t>
+          <t>FedExport - BSI (row 9); FedImport - BSI (row 10); Imaging101 (rows 11, 13); T24 (rows 12, 14, 48); ACH Express (row 47)</t>
         </is>
       </c>
       <c r="E82" s="76" t="inlineStr">
         <is>
-          <t>"Hi Elizabeth, You have my approval", Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
+          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation, attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).</t>
         </is>
       </c>
       <c r="F82" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 2 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026), samples 1937</t>
+          <t>Approval evidence for 8 DIV records: in-period approval evidence, samples 1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="G82" s="77" t="inlineStr">
@@ -16756,26 +15656,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H82" s="68" t="n"/>
-      <c r="I82" s="68" t="n"/>
-      <c r="J82" s="68" t="n"/>
-      <c r="K82" s="68" t="n"/>
-      <c r="L82" s="68" t="n"/>
-      <c r="M82" s="68" t="n"/>
-      <c r="N82" s="68" t="n"/>
-      <c r="O82" s="68" t="n"/>
-      <c r="P82" s="68" t="n"/>
-      <c r="Q82" s="68" t="n"/>
-      <c r="R82" s="68" t="n"/>
-      <c r="S82" s="68" t="n"/>
-      <c r="T82" s="68" t="n"/>
-      <c r="U82" s="68" t="n"/>
-      <c r="V82" s="68" t="n"/>
-      <c r="W82" s="85" t="n"/>
-      <c r="X82" s="85" t="n"/>
-      <c r="Y82" s="85" t="n"/>
-      <c r="Z82" s="85" t="n"/>
-      <c r="AA82" s="85" t="n"/>
       <c r="AB82" s="85" t="n"/>
       <c r="AC82" s="85" t="n"/>
       <c r="AD82" s="85" t="n"/>
@@ -16801,34 +15681,34 @@
       <c r="AX82" s="85" t="n"/>
       <c r="AY82" s="85" t="n"/>
     </row>
-    <row r="83" ht="46" customHeight="1" s="50">
+    <row r="83" ht="100" customHeight="1" s="50">
       <c r="A83" s="76" t="inlineStr">
         <is>
-          <t>DMA09</t>
+          <t>DMA02</t>
         </is>
       </c>
       <c r="B83" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg")</f>
         <v/>
       </c>
       <c r="C83" s="76" t="inlineStr">
         <is>
-          <t>08/18/2026, Clara G. De Castro</t>
+          <t>08/19/2026, David Marquez</t>
         </is>
       </c>
       <c r="D83" s="76" t="inlineStr">
         <is>
-          <t>T24 (row 62)</t>
+          <t>Imaging101 (row 5); OFAC - BSI (row 6); Swift Interface - BSI (row 7); T24 (row 8)</t>
         </is>
       </c>
       <c r="E83" s="76" t="inlineStr">
         <is>
-          <t>Clara De Castro (Director, General Services &amp; Facilities) returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Clara G. De Castro).</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="F83" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 1 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026), samples 1937</t>
+          <t>Approval evidence for 4 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 11/15/2025), samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="G83" s="77" t="inlineStr">
@@ -16836,26 +15716,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H83" s="68" t="n"/>
-      <c r="I83" s="68" t="n"/>
-      <c r="J83" s="68" t="n"/>
-      <c r="K83" s="68" t="n"/>
-      <c r="L83" s="68" t="n"/>
-      <c r="M83" s="68" t="n"/>
-      <c r="N83" s="68" t="n"/>
-      <c r="O83" s="68" t="n"/>
-      <c r="P83" s="68" t="n"/>
-      <c r="Q83" s="68" t="n"/>
-      <c r="R83" s="68" t="n"/>
-      <c r="S83" s="68" t="n"/>
-      <c r="T83" s="68" t="n"/>
-      <c r="U83" s="68" t="n"/>
-      <c r="V83" s="68" t="n"/>
-      <c r="W83" s="85" t="n"/>
-      <c r="X83" s="85" t="n"/>
-      <c r="Y83" s="85" t="n"/>
-      <c r="Z83" s="85" t="n"/>
-      <c r="AA83" s="85" t="n"/>
       <c r="AB83" s="85" t="n"/>
       <c r="AC83" s="85" t="n"/>
       <c r="AD83" s="85" t="n"/>
@@ -16884,31 +15744,31 @@
     <row r="84" ht="46" customHeight="1" s="50">
       <c r="A84" s="76" t="inlineStr">
         <is>
-          <t>DMA10</t>
+          <t>DMA03</t>
         </is>
       </c>
       <c r="B84" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg")</f>
         <v/>
       </c>
       <c r="C84" s="76" t="inlineStr">
         <is>
-          <t>08/21/2026, Victoria Fernandez</t>
+          <t>08/18/2026, Frank Puentes</t>
         </is>
       </c>
       <c r="D84" s="76" t="inlineStr">
         <is>
-          <t>T24 (row 52)</t>
+          <t>T24 (rows 23, 27, 31, 33); MQ Payment Monitor (rows 25, 29); OFAC - BSI (rows 26, 30, 34)</t>
         </is>
       </c>
       <c r="E84" s="76" t="inlineStr">
         <is>
-          <t>"Approved": Digital Wealth.</t>
+          <t>Frank Puentes returns the signed attestation: attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).</t>
         </is>
       </c>
       <c r="F84" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 1 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/21/2026), samples 1937</t>
+          <t>Approval evidence for 9 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 12/18/2025), samples 3301, 1903, 1937</t>
         </is>
       </c>
       <c r="G84" s="77" t="inlineStr">
@@ -16916,26 +15776,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H84" s="68" t="n"/>
-      <c r="I84" s="68" t="n"/>
-      <c r="J84" s="68" t="n"/>
-      <c r="K84" s="68" t="n"/>
-      <c r="L84" s="68" t="n"/>
-      <c r="M84" s="68" t="n"/>
-      <c r="N84" s="68" t="n"/>
-      <c r="O84" s="68" t="n"/>
-      <c r="P84" s="68" t="n"/>
-      <c r="Q84" s="68" t="n"/>
-      <c r="R84" s="68" t="n"/>
-      <c r="S84" s="68" t="n"/>
-      <c r="T84" s="68" t="n"/>
-      <c r="U84" s="68" t="n"/>
-      <c r="V84" s="68" t="n"/>
-      <c r="W84" s="85" t="n"/>
-      <c r="X84" s="85" t="n"/>
-      <c r="Y84" s="85" t="n"/>
-      <c r="Z84" s="85" t="n"/>
-      <c r="AA84" s="85" t="n"/>
       <c r="AB84" s="85" t="n"/>
       <c r="AC84" s="85" t="n"/>
       <c r="AD84" s="85" t="n"/>
@@ -16961,34 +15801,34 @@
       <c r="AX84" s="85" t="n"/>
       <c r="AY84" s="85" t="n"/>
     </row>
-    <row r="85" ht="46" customHeight="1" s="50">
+    <row r="85" ht="52" customHeight="1" s="50">
       <c r="A85" s="76" t="inlineStr">
         <is>
-          <t>DMA11</t>
+          <t>DMA04</t>
         </is>
       </c>
       <c r="B85" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg")</f>
         <v/>
       </c>
       <c r="C85" s="76" t="inlineStr">
         <is>
-          <t>09/09/2026, Miguel Orozco</t>
+          <t>08/17/2026, Michelle Oropesa</t>
         </is>
       </c>
       <c r="D85" s="76" t="inlineStr">
         <is>
-          <t>T24 (rows 15, 50); Imaging101 (row 51)</t>
+          <t>T24 (rows 19, 20, 21); Swift Interface - BSI (row 60); Interface Monitor (row 61)</t>
         </is>
       </c>
       <c r="E85" s="76" t="inlineStr">
         <is>
-          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
+          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).</t>
         </is>
       </c>
       <c r="F85" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 3 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026), samples 3299, 1937</t>
+          <t>Approval evidence for 5 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/17/2026), samples 4052, 1936, 1937</t>
         </is>
       </c>
       <c r="G85" s="77" t="inlineStr">
@@ -16996,26 +15836,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H85" s="68" t="n"/>
-      <c r="I85" s="68" t="n"/>
-      <c r="J85" s="68" t="n"/>
-      <c r="K85" s="68" t="n"/>
-      <c r="L85" s="68" t="n"/>
-      <c r="M85" s="68" t="n"/>
-      <c r="N85" s="68" t="n"/>
-      <c r="O85" s="68" t="n"/>
-      <c r="P85" s="68" t="n"/>
-      <c r="Q85" s="68" t="n"/>
-      <c r="R85" s="68" t="n"/>
-      <c r="S85" s="68" t="n"/>
-      <c r="T85" s="68" t="n"/>
-      <c r="U85" s="68" t="n"/>
-      <c r="V85" s="68" t="n"/>
-      <c r="W85" s="85" t="n"/>
-      <c r="X85" s="85" t="n"/>
-      <c r="Y85" s="85" t="n"/>
-      <c r="Z85" s="85" t="n"/>
-      <c r="AA85" s="85" t="n"/>
       <c r="AB85" s="85" t="n"/>
       <c r="AC85" s="85" t="n"/>
       <c r="AD85" s="85" t="n"/>
@@ -17041,34 +15861,34 @@
       <c r="AX85" s="85" t="n"/>
       <c r="AY85" s="85" t="n"/>
     </row>
-    <row r="86" ht="46" customHeight="1" s="50">
+    <row r="86" ht="52" customHeight="1" s="50">
       <c r="A86" s="76" t="inlineStr">
         <is>
-          <t>DMA12</t>
+          <t>DMA05</t>
         </is>
       </c>
       <c r="B86" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg")</f>
         <v/>
       </c>
       <c r="C86" s="76" t="inlineStr">
         <is>
-          <t>09/09/2026, Liliana Vizhnay</t>
+          <t>08/19/2026, Maria Teresa (Mayte) Del Cerro</t>
         </is>
       </c>
       <c r="D86" s="76" t="inlineStr">
         <is>
-          <t>T24 (row 49)</t>
+          <t>T24 (rows 18, 54, 59); Imaging101 (rows 53, 57); OFAC - BSI (row 58)</t>
         </is>
       </c>
       <c r="E86" s="76" t="inlineStr">
         <is>
-          <t>"I approve.", Client Servicing Unit.</t>
+          <t>Senior Director of Operations returns the signed attestation, attachments: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Maria Teresa Del Cerro Hontanilla, Director of Operations, 08/19/2026) and the BCiC export (same file as E16b).</t>
         </is>
       </c>
       <c r="F86" s="76" t="inlineStr">
         <is>
-          <t>Approval evidence for 1 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026), samples 1937</t>
+          <t>Approval evidence for 6 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/19/2026), samples 3299, 1903, 1937</t>
         </is>
       </c>
       <c r="G86" s="77" t="inlineStr">
@@ -17076,26 +15896,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H86" s="68" t="n"/>
-      <c r="I86" s="68" t="n"/>
-      <c r="J86" s="68" t="n"/>
-      <c r="K86" s="68" t="n"/>
-      <c r="L86" s="68" t="n"/>
-      <c r="M86" s="68" t="n"/>
-      <c r="N86" s="68" t="n"/>
-      <c r="O86" s="68" t="n"/>
-      <c r="P86" s="68" t="n"/>
-      <c r="Q86" s="68" t="n"/>
-      <c r="R86" s="68" t="n"/>
-      <c r="S86" s="68" t="n"/>
-      <c r="T86" s="68" t="n"/>
-      <c r="U86" s="68" t="n"/>
-      <c r="V86" s="68" t="n"/>
-      <c r="W86" s="85" t="n"/>
-      <c r="X86" s="85" t="n"/>
-      <c r="Y86" s="85" t="n"/>
-      <c r="Z86" s="85" t="n"/>
-      <c r="AA86" s="85" t="n"/>
       <c r="AB86" s="85" t="n"/>
       <c r="AC86" s="85" t="n"/>
       <c r="AD86" s="85" t="n"/>
@@ -17121,61 +15921,41 @@
       <c r="AX86" s="85" t="n"/>
       <c r="AY86" s="85" t="n"/>
     </row>
-    <row r="87" ht="46" customHeight="1" s="50">
+    <row r="87" ht="52" customHeight="1" s="50">
       <c r="A87" s="76" t="inlineStr">
         <is>
-          <t>DMA13</t>
+          <t>DMA06</t>
         </is>
       </c>
       <c r="B87" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg")</f>
         <v/>
       </c>
       <c r="C87" s="76" t="inlineStr">
         <is>
-          <t>09/09/2026, Elizabeth Noda</t>
+          <t>08/18/2026, Ricardo Garcia-Marques</t>
         </is>
       </c>
       <c r="D87" s="76" t="inlineStr">
         <is>
-          <t>Cisco Call Manager: not one of the 10 tested applications</t>
+          <t>T24 (rows 3, 35, 36, 37, 38, 39, 40, 63)</t>
         </is>
       </c>
       <c r="E87" s="76" t="inlineStr">
         <is>
-          <t>"approve": Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications, retained for completeness only.</t>
+          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia), attachment: Data_Integrity_Attestation_Santander-BCiC_signed.pdf (e-signed MD, Head of Trading &amp; Capital Markets, 08/18/2026 11:45 AM EDT).</t>
         </is>
       </c>
       <c r="F87" s="76" t="inlineStr">
         <is>
-          <t>Out of scope: retained for completeness, samples: none</t>
-        </is>
-      </c>
-      <c r="G87" s="79" t="inlineStr">
-        <is>
-          <t>N/A (supplemental, not relied on)</t>
-        </is>
-      </c>
-      <c r="H87" s="68" t="n"/>
-      <c r="I87" s="68" t="n"/>
-      <c r="J87" s="68" t="n"/>
-      <c r="K87" s="68" t="n"/>
-      <c r="L87" s="68" t="n"/>
-      <c r="M87" s="68" t="n"/>
-      <c r="N87" s="68" t="n"/>
-      <c r="O87" s="68" t="n"/>
-      <c r="P87" s="68" t="n"/>
-      <c r="Q87" s="68" t="n"/>
-      <c r="R87" s="68" t="n"/>
-      <c r="S87" s="68" t="n"/>
-      <c r="T87" s="68" t="n"/>
-      <c r="U87" s="68" t="n"/>
-      <c r="V87" s="68" t="n"/>
-      <c r="W87" s="85" t="n"/>
-      <c r="X87" s="85" t="n"/>
-      <c r="Y87" s="85" t="n"/>
-      <c r="Z87" s="85" t="n"/>
-      <c r="AA87" s="85" t="n"/>
+          <t>Approval evidence for 8 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026), samples 1937</t>
+        </is>
+      </c>
+      <c r="G87" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB87" s="85" t="n"/>
       <c r="AC87" s="85" t="n"/>
       <c r="AD87" s="85" t="n"/>
@@ -17201,34 +15981,41 @@
       <c r="AX87" s="85" t="n"/>
       <c r="AY87" s="85" t="n"/>
     </row>
-    <row r="88">
-      <c r="A88" s="74" t="n"/>
-      <c r="B88" s="74" t="n"/>
-      <c r="C88" s="74" t="n"/>
-      <c r="D88" s="74" t="n"/>
-      <c r="E88" s="74" t="n"/>
-      <c r="F88" s="74" t="n"/>
-      <c r="G88" s="74" t="n"/>
-      <c r="H88" s="68" t="n"/>
-      <c r="I88" s="68" t="n"/>
-      <c r="J88" s="68" t="n"/>
-      <c r="K88" s="68" t="n"/>
-      <c r="L88" s="68" t="n"/>
-      <c r="M88" s="68" t="n"/>
-      <c r="N88" s="68" t="n"/>
-      <c r="O88" s="68" t="n"/>
-      <c r="P88" s="68" t="n"/>
-      <c r="Q88" s="68" t="n"/>
-      <c r="R88" s="68" t="n"/>
-      <c r="S88" s="68" t="n"/>
-      <c r="T88" s="68" t="n"/>
-      <c r="U88" s="68" t="n"/>
-      <c r="V88" s="68" t="n"/>
-      <c r="W88" s="85" t="n"/>
-      <c r="X88" s="85" t="n"/>
-      <c r="Y88" s="85" t="n"/>
-      <c r="Z88" s="85" t="n"/>
-      <c r="AA88" s="85" t="n"/>
+    <row r="88" ht="46" customHeight="1" s="50">
+      <c r="A88" s="76" t="inlineStr">
+        <is>
+          <t>DMA07</t>
+        </is>
+      </c>
+      <c r="B88" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C88" s="76" t="inlineStr">
+        <is>
+          <t>08/18/2026, Martha Sullivan</t>
+        </is>
+      </c>
+      <c r="D88" s="76" t="inlineStr">
+        <is>
+          <t>T24 (rows 41, 42, 43, 44, 45, 46)</t>
+        </is>
+      </c>
+      <c r="E88" s="76" t="inlineStr">
+        <is>
+          <t>Martha Sullivan returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Balance Sheet Manager, Treasury).</t>
+        </is>
+      </c>
+      <c r="F88" s="76" t="inlineStr">
+        <is>
+          <t>Approval evidence for 6 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026), samples 1937</t>
+        </is>
+      </c>
+      <c r="G88" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB88" s="85" t="n"/>
       <c r="AC88" s="85" t="n"/>
       <c r="AD88" s="85" t="n"/>
@@ -17254,38 +16041,41 @@
       <c r="AX88" s="85" t="n"/>
       <c r="AY88" s="85" t="n"/>
     </row>
-    <row r="89" ht="15.5" customHeight="1" s="50">
-      <c r="A89" s="71" t="inlineStr">
-        <is>
-          <t>Management Attestation / In-Scope Applications (folder 01) and Data Integrity &amp; Email Testing Evidence (folder 04), Review</t>
-        </is>
-      </c>
-      <c r="B89" s="97" t="n"/>
-      <c r="C89" s="97" t="n"/>
-      <c r="D89" s="97" t="n"/>
-      <c r="E89" s="97" t="n"/>
-      <c r="F89" s="97" t="n"/>
-      <c r="G89" s="98" t="n"/>
-      <c r="H89" s="68" t="n"/>
-      <c r="I89" s="68" t="n"/>
-      <c r="J89" s="68" t="n"/>
-      <c r="K89" s="68" t="n"/>
-      <c r="L89" s="68" t="n"/>
-      <c r="M89" s="68" t="n"/>
-      <c r="N89" s="68" t="n"/>
-      <c r="O89" s="68" t="n"/>
-      <c r="P89" s="68" t="n"/>
-      <c r="Q89" s="68" t="n"/>
-      <c r="R89" s="68" t="n"/>
-      <c r="S89" s="68" t="n"/>
-      <c r="T89" s="68" t="n"/>
-      <c r="U89" s="68" t="n"/>
-      <c r="V89" s="68" t="n"/>
-      <c r="W89" s="85" t="n"/>
-      <c r="X89" s="85" t="n"/>
-      <c r="Y89" s="85" t="n"/>
-      <c r="Z89" s="85" t="n"/>
-      <c r="AA89" s="85" t="n"/>
+    <row r="89" ht="46" customHeight="1" s="50">
+      <c r="A89" s="76" t="inlineStr">
+        <is>
+          <t>DMA08</t>
+        </is>
+      </c>
+      <c r="B89" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C89" s="76" t="inlineStr">
+        <is>
+          <t>08/18/2026, Ivan Caisapanta</t>
+        </is>
+      </c>
+      <c r="D89" s="76" t="inlineStr">
+        <is>
+          <t>T24 (rows 55, 56)</t>
+        </is>
+      </c>
+      <c r="E89" s="76" t="inlineStr">
+        <is>
+          <t>"Hi Elizabeth, You have my approval", Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
+        </is>
+      </c>
+      <c r="F89" s="76" t="inlineStr">
+        <is>
+          <t>Approval evidence for 2 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026), samples 1937</t>
+        </is>
+      </c>
+      <c r="G89" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB89" s="85" t="n"/>
       <c r="AC89" s="85" t="n"/>
       <c r="AD89" s="85" t="n"/>
@@ -17311,62 +16101,41 @@
       <c r="AX89" s="85" t="n"/>
       <c r="AY89" s="85" t="n"/>
     </row>
-    <row r="90" ht="26" customHeight="1" s="50">
-      <c r="A90" s="73" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B90" s="73" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C90" s="73" t="inlineStr">
-        <is>
-          <t>Date / owner</t>
-        </is>
-      </c>
-      <c r="D90" s="73" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E90" s="73" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F90" s="73" t="inlineStr">
-        <is>
-          <t>Samples / workpaper columns supported</t>
-        </is>
-      </c>
-      <c r="G90" s="73" t="inlineStr">
-        <is>
-          <t>Control Sample Assessment Result (Pass/Fail)</t>
-        </is>
-      </c>
-      <c r="H90" s="68" t="n"/>
-      <c r="I90" s="68" t="n"/>
-      <c r="J90" s="68" t="n"/>
-      <c r="K90" s="68" t="n"/>
-      <c r="L90" s="68" t="n"/>
-      <c r="M90" s="68" t="n"/>
-      <c r="N90" s="68" t="n"/>
-      <c r="O90" s="68" t="n"/>
-      <c r="P90" s="68" t="n"/>
-      <c r="Q90" s="68" t="n"/>
-      <c r="R90" s="68" t="n"/>
-      <c r="S90" s="68" t="n"/>
-      <c r="T90" s="68" t="n"/>
-      <c r="U90" s="68" t="n"/>
-      <c r="V90" s="68" t="n"/>
-      <c r="W90" s="85" t="n"/>
-      <c r="X90" s="85" t="n"/>
-      <c r="Y90" s="85" t="n"/>
-      <c r="Z90" s="85" t="n"/>
-      <c r="AA90" s="85" t="n"/>
+    <row r="90" ht="46" customHeight="1" s="50">
+      <c r="A90" s="76" t="inlineStr">
+        <is>
+          <t>DMA09</t>
+        </is>
+      </c>
+      <c r="B90" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg")</f>
+        <v/>
+      </c>
+      <c r="C90" s="76" t="inlineStr">
+        <is>
+          <t>08/18/2026, Clara G. De Castro</t>
+        </is>
+      </c>
+      <c r="D90" s="76" t="inlineStr">
+        <is>
+          <t>T24 (row 62)</t>
+        </is>
+      </c>
+      <c r="E90" s="76" t="inlineStr">
+        <is>
+          <t>Clara De Castro (Director, General Services &amp; Facilities) returns the signed attestation, attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Clara G. De Castro).</t>
+        </is>
+      </c>
+      <c r="F90" s="76" t="inlineStr">
+        <is>
+          <t>Approval evidence for 1 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026), samples 1937</t>
+        </is>
+      </c>
+      <c r="G90" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB90" s="85" t="n"/>
       <c r="AC90" s="85" t="n"/>
       <c r="AD90" s="85" t="n"/>
@@ -17392,34 +16161,34 @@
       <c r="AX90" s="85" t="n"/>
       <c r="AY90" s="85" t="n"/>
     </row>
-    <row r="91" ht="76" customHeight="1" s="50">
+    <row r="91" ht="46" customHeight="1" s="50">
       <c r="A91" s="76" t="inlineStr">
         <is>
-          <t>MA01</t>
+          <t>DMA10</t>
         </is>
       </c>
       <c r="B91" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml")</f>
         <v/>
       </c>
       <c r="C91" s="76" t="inlineStr">
         <is>
-          <t>09/23/2026, Cesar Vidal (BCiC walkthrough)</t>
+          <t>08/21/2026, Victoria Fernandez</t>
         </is>
       </c>
       <c r="D91" s="76" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>T24 (row 52)</t>
         </is>
       </c>
       <c r="E91" s="76" t="inlineStr">
         <is>
-          <t>BC in the Cloud 'Applications In Scope for DR Test BSI' view (filter Scope Entity = BSI; 43 items). The 10 tested applications are selected (1822, 1867, 1868, 1903, 1917, 1937, 1936, 3301, 3299, 4052) and each shows 2025 DR Test Scope = True, 2025 Backup/Restore Test Scope = True and 2025 Backup/Restore DIV Scope = True.</t>
+          <t>"Approved": Digital Wealth.</t>
         </is>
       </c>
       <c r="F91" s="76" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
+          <t>Approval evidence for 1 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 08/21/2026), samples 1937</t>
         </is>
       </c>
       <c r="G91" s="77" t="inlineStr">
@@ -17427,26 +16196,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H91" s="68" t="n"/>
-      <c r="I91" s="68" t="n"/>
-      <c r="J91" s="68" t="n"/>
-      <c r="K91" s="68" t="n"/>
-      <c r="L91" s="68" t="n"/>
-      <c r="M91" s="68" t="n"/>
-      <c r="N91" s="68" t="n"/>
-      <c r="O91" s="68" t="n"/>
-      <c r="P91" s="68" t="n"/>
-      <c r="Q91" s="68" t="n"/>
-      <c r="R91" s="68" t="n"/>
-      <c r="S91" s="68" t="n"/>
-      <c r="T91" s="68" t="n"/>
-      <c r="U91" s="68" t="n"/>
-      <c r="V91" s="68" t="n"/>
-      <c r="W91" s="85" t="n"/>
-      <c r="X91" s="85" t="n"/>
-      <c r="Y91" s="85" t="n"/>
-      <c r="Z91" s="85" t="n"/>
-      <c r="AA91" s="85" t="n"/>
       <c r="AB91" s="85" t="n"/>
       <c r="AC91" s="85" t="n"/>
       <c r="AD91" s="85" t="n"/>
@@ -17475,31 +16224,31 @@
     <row r="92" ht="46" customHeight="1" s="50">
       <c r="A92" s="76" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>DMA11</t>
         </is>
       </c>
       <c r="B92" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml")</f>
         <v/>
       </c>
       <c r="C92" s="76" t="inlineStr">
         <is>
-          <t>BCiC: Applications In Scope for DR Test BSI</t>
+          <t>09/09/2026, Miguel Orozco</t>
         </is>
       </c>
       <c r="D92" s="76" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>T24 (rows 15, 50); Imaging101 (row 51)</t>
         </is>
       </c>
       <c r="E92" s="76" t="inlineStr">
         <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
+          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
         </is>
       </c>
       <c r="F92" s="76" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, K, L, N</t>
+          <t>Approval evidence for 3 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026), samples 3299, 1937</t>
         </is>
       </c>
       <c r="G92" s="77" t="inlineStr">
@@ -17507,26 +16256,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H92" s="68" t="n"/>
-      <c r="I92" s="68" t="n"/>
-      <c r="J92" s="68" t="n"/>
-      <c r="K92" s="68" t="n"/>
-      <c r="L92" s="68" t="n"/>
-      <c r="M92" s="68" t="n"/>
-      <c r="N92" s="68" t="n"/>
-      <c r="O92" s="68" t="n"/>
-      <c r="P92" s="68" t="n"/>
-      <c r="Q92" s="68" t="n"/>
-      <c r="R92" s="68" t="n"/>
-      <c r="S92" s="68" t="n"/>
-      <c r="T92" s="68" t="n"/>
-      <c r="U92" s="68" t="n"/>
-      <c r="V92" s="68" t="n"/>
-      <c r="W92" s="85" t="n"/>
-      <c r="X92" s="85" t="n"/>
-      <c r="Y92" s="85" t="n"/>
-      <c r="Z92" s="85" t="n"/>
-      <c r="AA92" s="85" t="n"/>
       <c r="AB92" s="85" t="n"/>
       <c r="AC92" s="85" t="n"/>
       <c r="AD92" s="85" t="n"/>
@@ -17555,31 +16284,31 @@
     <row r="93" ht="46" customHeight="1" s="50">
       <c r="A93" s="76" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>DMA12</t>
         </is>
       </c>
       <c r="B93" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml")</f>
         <v/>
       </c>
       <c r="C93" s="76" t="inlineStr">
         <is>
-          <t>09/10/2026, Cesar Vidal</t>
+          <t>09/09/2026, Liliana Vizhnay</t>
         </is>
       </c>
       <c r="D93" s="76" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>T24 (row 49)</t>
         </is>
       </c>
       <c r="E93" s="76" t="inlineStr">
         <is>
-          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1 to 20 of 43 items).</t>
+          <t>"I approve.", Client Servicing Unit.</t>
         </is>
       </c>
       <c r="F93" s="76" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
+          <t>Approval evidence for 1 DIV records: approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026), samples 1937</t>
         </is>
       </c>
       <c r="G93" s="77" t="inlineStr">
@@ -17587,26 +16316,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H93" s="68" t="n"/>
-      <c r="I93" s="68" t="n"/>
-      <c r="J93" s="68" t="n"/>
-      <c r="K93" s="68" t="n"/>
-      <c r="L93" s="68" t="n"/>
-      <c r="M93" s="68" t="n"/>
-      <c r="N93" s="68" t="n"/>
-      <c r="O93" s="68" t="n"/>
-      <c r="P93" s="68" t="n"/>
-      <c r="Q93" s="68" t="n"/>
-      <c r="R93" s="68" t="n"/>
-      <c r="S93" s="68" t="n"/>
-      <c r="T93" s="68" t="n"/>
-      <c r="U93" s="68" t="n"/>
-      <c r="V93" s="68" t="n"/>
-      <c r="W93" s="85" t="n"/>
-      <c r="X93" s="85" t="n"/>
-      <c r="Y93" s="85" t="n"/>
-      <c r="Z93" s="85" t="n"/>
-      <c r="AA93" s="85" t="n"/>
       <c r="AB93" s="85" t="n"/>
       <c r="AC93" s="85" t="n"/>
       <c r="AD93" s="85" t="n"/>
@@ -17632,61 +16341,41 @@
       <c r="AX93" s="85" t="n"/>
       <c r="AY93" s="85" t="n"/>
     </row>
-    <row r="94" ht="52" customHeight="1" s="50">
+    <row r="94" ht="46" customHeight="1" s="50">
       <c r="A94" s="76" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>DMA13</t>
         </is>
       </c>
       <c r="B94" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml","\","/"),"03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml"),"BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml")</f>
         <v/>
       </c>
       <c r="C94" s="76" t="inlineStr">
         <is>
-          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
+          <t>09/09/2026, Elizabeth Noda</t>
         </is>
       </c>
       <c r="D94" s="76" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>Cisco Call Manager: not one of the 10 tested applications</t>
         </is>
       </c>
       <c r="E94" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>"approve": Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications, retained for completeness only.</t>
         </is>
       </c>
       <c r="F94" s="76" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, E, F, G, H, I, K, L, M, O, P</t>
-        </is>
-      </c>
-      <c r="G94" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H94" s="68" t="n"/>
-      <c r="I94" s="68" t="n"/>
-      <c r="J94" s="68" t="n"/>
-      <c r="K94" s="68" t="n"/>
-      <c r="L94" s="68" t="n"/>
-      <c r="M94" s="68" t="n"/>
-      <c r="N94" s="68" t="n"/>
-      <c r="O94" s="68" t="n"/>
-      <c r="P94" s="68" t="n"/>
-      <c r="Q94" s="68" t="n"/>
-      <c r="R94" s="68" t="n"/>
-      <c r="S94" s="68" t="n"/>
-      <c r="T94" s="68" t="n"/>
-      <c r="U94" s="68" t="n"/>
-      <c r="V94" s="68" t="n"/>
-      <c r="W94" s="85" t="n"/>
-      <c r="X94" s="85" t="n"/>
-      <c r="Y94" s="85" t="n"/>
-      <c r="Z94" s="85" t="n"/>
-      <c r="AA94" s="85" t="n"/>
+          <t>Out of scope: retained for completeness, samples: none</t>
+        </is>
+      </c>
+      <c r="G94" s="79" t="inlineStr">
+        <is>
+          <t>N/A (supplemental, not relied on)</t>
+        </is>
+      </c>
       <c r="AB94" s="85" t="n"/>
       <c r="AC94" s="85" t="n"/>
       <c r="AD94" s="85" t="n"/>
@@ -17712,61 +16401,14 @@
       <c r="AX94" s="85" t="n"/>
       <c r="AY94" s="85" t="n"/>
     </row>
-    <row r="95" ht="46" customHeight="1" s="50">
-      <c r="A95" s="76" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="B95" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
-        <v/>
-      </c>
-      <c r="C95" s="76" t="inlineStr">
-        <is>
-          <t>09/10/2026, Cesar Vidal</t>
-        </is>
-      </c>
-      <c r="D95" s="76" t="inlineStr">
-        <is>
-          <t>BCiC screenshot</t>
-        </is>
-      </c>
-      <c r="E95" s="76" t="inlineStr">
-        <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1 to 20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
-        </is>
-      </c>
-      <c r="F95" s="76" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, E, F, G, H, K, P</t>
-        </is>
-      </c>
-      <c r="G95" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H95" s="68" t="n"/>
-      <c r="I95" s="68" t="n"/>
-      <c r="J95" s="68" t="n"/>
-      <c r="K95" s="68" t="n"/>
-      <c r="L95" s="68" t="n"/>
-      <c r="M95" s="68" t="n"/>
-      <c r="N95" s="68" t="n"/>
-      <c r="O95" s="68" t="n"/>
-      <c r="P95" s="68" t="n"/>
-      <c r="Q95" s="68" t="n"/>
-      <c r="R95" s="68" t="n"/>
-      <c r="S95" s="68" t="n"/>
-      <c r="T95" s="68" t="n"/>
-      <c r="U95" s="68" t="n"/>
-      <c r="V95" s="68" t="n"/>
-      <c r="W95" s="85" t="n"/>
-      <c r="X95" s="85" t="n"/>
-      <c r="Y95" s="85" t="n"/>
-      <c r="Z95" s="85" t="n"/>
-      <c r="AA95" s="85" t="n"/>
+    <row r="95" s="50">
+      <c r="A95" s="74" t="n"/>
+      <c r="B95" s="74" t="n"/>
+      <c r="C95" s="74" t="n"/>
+      <c r="D95" s="74" t="n"/>
+      <c r="E95" s="74" t="n"/>
+      <c r="F95" s="74" t="n"/>
+      <c r="G95" s="74" t="n"/>
       <c r="AB95" s="85" t="n"/>
       <c r="AC95" s="85" t="n"/>
       <c r="AD95" s="85" t="n"/>
@@ -17792,61 +16434,18 @@
       <c r="AX95" s="85" t="n"/>
       <c r="AY95" s="85" t="n"/>
     </row>
-    <row r="96" ht="46" customHeight="1" s="50">
-      <c r="A96" s="76" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-      <c r="B96" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
-        <v/>
-      </c>
-      <c r="C96" s="76" t="inlineStr">
-        <is>
-          <t>09/15/2025, Elizabeth Noda</t>
-        </is>
-      </c>
-      <c r="D96" s="76" t="inlineStr">
-        <is>
-          <t>Meeting invite</t>
-        </is>
-      </c>
-      <c r="E96" s="76" t="inlineStr">
-        <is>
-          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025, duplicate E06 removed).</t>
-        </is>
-      </c>
-      <c r="F96" s="76" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
-        </is>
-      </c>
-      <c r="G96" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H96" s="68" t="n"/>
-      <c r="I96" s="68" t="n"/>
-      <c r="J96" s="68" t="n"/>
-      <c r="K96" s="68" t="n"/>
-      <c r="L96" s="68" t="n"/>
-      <c r="M96" s="68" t="n"/>
-      <c r="N96" s="68" t="n"/>
-      <c r="O96" s="68" t="n"/>
-      <c r="P96" s="68" t="n"/>
-      <c r="Q96" s="68" t="n"/>
-      <c r="R96" s="68" t="n"/>
-      <c r="S96" s="68" t="n"/>
-      <c r="T96" s="68" t="n"/>
-      <c r="U96" s="68" t="n"/>
-      <c r="V96" s="68" t="n"/>
-      <c r="W96" s="85" t="n"/>
-      <c r="X96" s="85" t="n"/>
-      <c r="Y96" s="85" t="n"/>
-      <c r="Z96" s="85" t="n"/>
-      <c r="AA96" s="85" t="n"/>
+    <row r="96" ht="15.5" customHeight="1" s="50">
+      <c r="A96" s="71" t="inlineStr">
+        <is>
+          <t>Management Attestation / In-Scope Applications (folder 01) and Data Integrity &amp; Email Testing Evidence (folder 04), Review</t>
+        </is>
+      </c>
+      <c r="B96" s="97" t="n"/>
+      <c r="C96" s="97" t="n"/>
+      <c r="D96" s="97" t="n"/>
+      <c r="E96" s="97" t="n"/>
+      <c r="F96" s="97" t="n"/>
+      <c r="G96" s="98" t="n"/>
       <c r="AB96" s="85" t="n"/>
       <c r="AC96" s="85" t="n"/>
       <c r="AD96" s="85" t="n"/>
@@ -17872,61 +16471,42 @@
       <c r="AX96" s="85" t="n"/>
       <c r="AY96" s="85" t="n"/>
     </row>
-    <row r="97" ht="148" customHeight="1" s="50">
-      <c r="A97" s="76" t="inlineStr">
-        <is>
-          <t>E07</t>
-        </is>
-      </c>
-      <c r="B97" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
-        <v/>
-      </c>
-      <c r="C97" s="76" t="inlineStr">
-        <is>
-          <t>11/15/2025, Frank Puentes</t>
-        </is>
-      </c>
-      <c r="D97" s="76" t="inlineStr">
-        <is>
-          <t>Email + report attachments</t>
-        </is>
-      </c>
-      <c r="E97" s="76" t="inlineStr">
-        <is>
-          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf; FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf; OFAC ACH 111425 0512PM.pdf; OFAC FED 111425 0511PM.pdf; OFAC SWIFT 111425 0511PM.pdf; OUTGOING FEDWIRE 111425 506PM.xls; OUTGOING SWIFT 111425 509PM.xls; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf; SWIFT INTERFACE MONITOR 111425 519PM.pdf; SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf.</t>
-        </is>
-      </c>
-      <c r="F97" s="76" t="inlineStr">
-        <is>
-          <t>Samples: 3301, 1903, 1936, 1937; columns: F</t>
-        </is>
-      </c>
-      <c r="G97" s="77" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H97" s="68" t="n"/>
-      <c r="I97" s="68" t="n"/>
-      <c r="J97" s="68" t="n"/>
-      <c r="K97" s="68" t="n"/>
-      <c r="L97" s="68" t="n"/>
-      <c r="M97" s="68" t="n"/>
-      <c r="N97" s="68" t="n"/>
-      <c r="O97" s="68" t="n"/>
-      <c r="P97" s="68" t="n"/>
-      <c r="Q97" s="68" t="n"/>
-      <c r="R97" s="68" t="n"/>
-      <c r="S97" s="68" t="n"/>
-      <c r="T97" s="68" t="n"/>
-      <c r="U97" s="68" t="n"/>
-      <c r="V97" s="68" t="n"/>
-      <c r="W97" s="85" t="n"/>
-      <c r="X97" s="85" t="n"/>
-      <c r="Y97" s="85" t="n"/>
-      <c r="Z97" s="85" t="n"/>
-      <c r="AA97" s="85" t="n"/>
+    <row r="97" ht="26" customHeight="1" s="50">
+      <c r="A97" s="73" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B97" s="73" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C97" s="73" t="inlineStr">
+        <is>
+          <t>Date / owner</t>
+        </is>
+      </c>
+      <c r="D97" s="73" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E97" s="73" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F97" s="73" t="inlineStr">
+        <is>
+          <t>Samples / workpaper columns supported</t>
+        </is>
+      </c>
+      <c r="G97" s="73" t="inlineStr">
+        <is>
+          <t>Control Sample Assessment Result (Pass/Fail)</t>
+        </is>
+      </c>
       <c r="AB97" s="85" t="n"/>
       <c r="AC97" s="85" t="n"/>
       <c r="AD97" s="85" t="n"/>
@@ -17952,34 +16532,34 @@
       <c r="AX97" s="85" t="n"/>
       <c r="AY97" s="85" t="n"/>
     </row>
-    <row r="98" ht="160" customHeight="1" s="50">
+    <row r="98" ht="76" customHeight="1" s="50">
       <c r="A98" s="76" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>MA01</t>
         </is>
       </c>
       <c r="B98" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png","\","/"),"01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png"),"BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png")</f>
         <v/>
       </c>
       <c r="C98" s="76" t="inlineStr">
         <is>
-          <t>11/15/2025, Frank Puentes</t>
+          <t>09/23/2026, Cesar Vidal (BCiC walkthrough)</t>
         </is>
       </c>
       <c r="D98" s="76" t="inlineStr">
         <is>
-          <t>Email + report attachments</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E98" s="76" t="inlineStr">
         <is>
-          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf; FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf; OFAC ACH 111425 - 11152025 1126AM.pdf; OFAC FED 111425 - 111525 1126AM.pdf; OFAC SWIFT 111425 - 111525 1128AM.pdf; OUTGOING FEDWIRE 111525 1025AM.xls; OUTGOING SWIFT 111525 1026AM.xls; PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf; PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf.</t>
+          <t>BC in the Cloud 'Applications In Scope for DR Test BSI' view (filter Scope Entity = BSI; 43 items). The 10 tested applications are selected (1822, 1867, 1868, 1903, 1917, 1937, 1936, 3301, 3299, 4052) and each shows 2025 DR Test Scope = True, 2025 Backup/Restore Test Scope = True and 2025 Backup/Restore DIV Scope = True.</t>
         </is>
       </c>
       <c r="F98" s="76" t="inlineStr">
         <is>
-          <t>Samples: 3301, 1903, 1936, 1937; columns: F, M</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, L</t>
         </is>
       </c>
       <c r="G98" s="77" t="inlineStr">
@@ -17987,26 +16567,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H98" s="68" t="n"/>
-      <c r="I98" s="68" t="n"/>
-      <c r="J98" s="68" t="n"/>
-      <c r="K98" s="68" t="n"/>
-      <c r="L98" s="68" t="n"/>
-      <c r="M98" s="68" t="n"/>
-      <c r="N98" s="68" t="n"/>
-      <c r="O98" s="68" t="n"/>
-      <c r="P98" s="68" t="n"/>
-      <c r="Q98" s="68" t="n"/>
-      <c r="R98" s="68" t="n"/>
-      <c r="S98" s="68" t="n"/>
-      <c r="T98" s="68" t="n"/>
-      <c r="U98" s="68" t="n"/>
-      <c r="V98" s="68" t="n"/>
-      <c r="W98" s="85" t="n"/>
-      <c r="X98" s="85" t="n"/>
-      <c r="Y98" s="85" t="n"/>
-      <c r="Z98" s="85" t="n"/>
-      <c r="AA98" s="85" t="n"/>
       <c r="AB98" s="85" t="n"/>
       <c r="AC98" s="85" t="n"/>
       <c r="AD98" s="85" t="n"/>
@@ -18032,34 +16592,34 @@
       <c r="AX98" s="85" t="n"/>
       <c r="AY98" s="85" t="n"/>
     </row>
-    <row r="99" ht="52" customHeight="1" s="50">
+    <row r="99" ht="46" customHeight="1" s="50">
       <c r="A99" s="76" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B99" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx")</f>
         <v/>
       </c>
       <c r="C99" s="76" t="inlineStr">
         <is>
-          <t>03/03/2026 to 05/05/2026: Claudia Romero</t>
+          <t>BCiC: Applications In Scope for DR Test BSI</t>
         </is>
       </c>
       <c r="D99" s="76" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="E99" s="76" t="inlineStr">
         <is>
-          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
         </is>
       </c>
       <c r="F99" s="76" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 1937; columns: E, G, H, J, M, N, O</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, E, L, M</t>
         </is>
       </c>
       <c r="G99" s="77" t="inlineStr">
@@ -18067,26 +16627,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H99" s="68" t="n"/>
-      <c r="I99" s="68" t="n"/>
-      <c r="J99" s="68" t="n"/>
-      <c r="K99" s="68" t="n"/>
-      <c r="L99" s="68" t="n"/>
-      <c r="M99" s="68" t="n"/>
-      <c r="N99" s="68" t="n"/>
-      <c r="O99" s="68" t="n"/>
-      <c r="P99" s="68" t="n"/>
-      <c r="Q99" s="68" t="n"/>
-      <c r="R99" s="68" t="n"/>
-      <c r="S99" s="68" t="n"/>
-      <c r="T99" s="68" t="n"/>
-      <c r="U99" s="68" t="n"/>
-      <c r="V99" s="68" t="n"/>
-      <c r="W99" s="85" t="n"/>
-      <c r="X99" s="85" t="n"/>
-      <c r="Y99" s="85" t="n"/>
-      <c r="Z99" s="85" t="n"/>
-      <c r="AA99" s="85" t="n"/>
       <c r="AB99" s="85" t="n"/>
       <c r="AC99" s="85" t="n"/>
       <c r="AD99" s="85" t="n"/>
@@ -18115,31 +16655,31 @@
     <row r="100" ht="46" customHeight="1" s="50">
       <c r="A100" s="76" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B100" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg")</f>
         <v/>
       </c>
       <c r="C100" s="76" t="inlineStr">
         <is>
-          <t>03/09/2026, Lina Acuna</t>
+          <t>09/10/2026, Cesar Vidal</t>
         </is>
       </c>
       <c r="D100" s="76" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E100" s="76" t="inlineStr">
         <is>
-          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
+          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1 to 20 of 43 items).</t>
         </is>
       </c>
       <c r="F100" s="76" t="inlineStr">
         <is>
-          <t>Samples: 1917, 1937; columns: M</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, L</t>
         </is>
       </c>
       <c r="G100" s="77" t="inlineStr">
@@ -18147,26 +16687,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H100" s="68" t="n"/>
-      <c r="I100" s="68" t="n"/>
-      <c r="J100" s="68" t="n"/>
-      <c r="K100" s="68" t="n"/>
-      <c r="L100" s="68" t="n"/>
-      <c r="M100" s="68" t="n"/>
-      <c r="N100" s="68" t="n"/>
-      <c r="O100" s="68" t="n"/>
-      <c r="P100" s="68" t="n"/>
-      <c r="Q100" s="68" t="n"/>
-      <c r="R100" s="68" t="n"/>
-      <c r="S100" s="68" t="n"/>
-      <c r="T100" s="68" t="n"/>
-      <c r="U100" s="68" t="n"/>
-      <c r="V100" s="68" t="n"/>
-      <c r="W100" s="85" t="n"/>
-      <c r="X100" s="85" t="n"/>
-      <c r="Y100" s="85" t="n"/>
-      <c r="Z100" s="85" t="n"/>
-      <c r="AA100" s="85" t="n"/>
       <c r="AB100" s="85" t="n"/>
       <c r="AC100" s="85" t="n"/>
       <c r="AD100" s="85" t="n"/>
@@ -18192,61 +16712,41 @@
       <c r="AX100" s="85" t="n"/>
       <c r="AY100" s="85" t="n"/>
     </row>
-    <row r="101" ht="46" customHeight="1" s="50">
+    <row r="101" ht="52" customHeight="1" s="50">
       <c r="A101" s="76" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B101" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls")</f>
         <v/>
       </c>
       <c r="C101" s="76" t="inlineStr">
         <is>
-          <t>11/13/2024, T24 backup user</t>
+          <t>BCiC: Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="D101" s="76" t="inlineStr">
         <is>
-          <t>System email</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="E101" s="76" t="inlineStr">
         <is>
-          <t>T24 environment refresh log: prior period (outside review period); supplemental only.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="F101" s="76" t="inlineStr">
         <is>
-          <t>Samples: ; columns: (supplemental)</t>
-        </is>
-      </c>
-      <c r="G101" s="79" t="inlineStr">
-        <is>
-          <t>N/A (supplemental, not relied on)</t>
-        </is>
-      </c>
-      <c r="H101" s="68" t="n"/>
-      <c r="I101" s="68" t="n"/>
-      <c r="J101" s="68" t="n"/>
-      <c r="K101" s="68" t="n"/>
-      <c r="L101" s="68" t="n"/>
-      <c r="M101" s="68" t="n"/>
-      <c r="N101" s="68" t="n"/>
-      <c r="O101" s="68" t="n"/>
-      <c r="P101" s="68" t="n"/>
-      <c r="Q101" s="68" t="n"/>
-      <c r="R101" s="68" t="n"/>
-      <c r="S101" s="68" t="n"/>
-      <c r="T101" s="68" t="n"/>
-      <c r="U101" s="68" t="n"/>
-      <c r="V101" s="68" t="n"/>
-      <c r="W101" s="85" t="n"/>
-      <c r="X101" s="85" t="n"/>
-      <c r="Y101" s="85" t="n"/>
-      <c r="Z101" s="85" t="n"/>
-      <c r="AA101" s="85" t="n"/>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, E, F, G, H, I, J, L, M, N, O, P</t>
+        </is>
+      </c>
+      <c r="G101" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="AB101" s="85" t="n"/>
       <c r="AC101" s="85" t="n"/>
       <c r="AD101" s="85" t="n"/>
@@ -18275,31 +16775,31 @@
     <row r="102" ht="46" customHeight="1" s="50">
       <c r="A102" s="76" t="inlineStr">
         <is>
-          <t>E16b</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B102" s="75">
-        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg")</f>
         <v/>
       </c>
       <c r="C102" s="76" t="inlineStr">
         <is>
-          <t>08/2026: BCiC export sent with attestation request</t>
+          <t>09/10/2026, Cesar Vidal</t>
         </is>
       </c>
       <c r="D102" s="76" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E102" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1 to 20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
         </is>
       </c>
       <c r="F102" s="76" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, E, F, I, K, P</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, F, G, H, I, L, P</t>
         </is>
       </c>
       <c r="G102" s="77" t="inlineStr">
@@ -18307,26 +16807,6 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="H102" s="68" t="n"/>
-      <c r="I102" s="68" t="n"/>
-      <c r="J102" s="68" t="n"/>
-      <c r="K102" s="68" t="n"/>
-      <c r="L102" s="68" t="n"/>
-      <c r="M102" s="68" t="n"/>
-      <c r="N102" s="68" t="n"/>
-      <c r="O102" s="68" t="n"/>
-      <c r="P102" s="68" t="n"/>
-      <c r="Q102" s="68" t="n"/>
-      <c r="R102" s="68" t="n"/>
-      <c r="S102" s="68" t="n"/>
-      <c r="T102" s="68" t="n"/>
-      <c r="U102" s="68" t="n"/>
-      <c r="V102" s="68" t="n"/>
-      <c r="W102" s="85" t="n"/>
-      <c r="X102" s="85" t="n"/>
-      <c r="Y102" s="85" t="n"/>
-      <c r="Z102" s="85" t="n"/>
-      <c r="AA102" s="85" t="n"/>
       <c r="AB102" s="85" t="n"/>
       <c r="AC102" s="85" t="n"/>
       <c r="AD102" s="85" t="n"/>
@@ -18352,61 +16832,318 @@
       <c r="AX102" s="85" t="n"/>
       <c r="AY102" s="85" t="n"/>
     </row>
+    <row r="103" ht="46" customHeight="1" s="50">
+      <c r="A103" s="76" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B103" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg")</f>
+        <v/>
+      </c>
+      <c r="C103" s="76" t="inlineStr">
+        <is>
+          <t>09/15/2025, Elizabeth Noda</t>
+        </is>
+      </c>
+      <c r="D103" s="76" t="inlineStr">
+        <is>
+          <t>Meeting invite</t>
+        </is>
+      </c>
+      <c r="E103" s="76" t="inlineStr">
+        <is>
+          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025, duplicate E06 removed).</t>
+        </is>
+      </c>
+      <c r="F103" s="76" t="inlineStr">
+        <is>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: C, N</t>
+        </is>
+      </c>
+      <c r="G103" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="148" customHeight="1" s="50">
+      <c r="A104" s="76" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B104" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg")</f>
+        <v/>
+      </c>
+      <c r="C104" s="76" t="inlineStr">
+        <is>
+          <t>11/15/2025, Frank Puentes</t>
+        </is>
+      </c>
+      <c r="D104" s="76" t="inlineStr">
+        <is>
+          <t>Email + report attachments</t>
+        </is>
+      </c>
+      <c r="E104" s="76" t="inlineStr">
+        <is>
+          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf; FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf; OFAC ACH 111425 0512PM.pdf; OFAC FED 111425 0511PM.pdf; OFAC SWIFT 111425 0511PM.pdf; OUTGOING FEDWIRE 111425 506PM.xls; OUTGOING SWIFT 111425 509PM.xls; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf; SWIFT INTERFACE MONITOR 111425 519PM.pdf; SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf.</t>
+        </is>
+      </c>
+      <c r="F104" s="76" t="inlineStr">
+        <is>
+          <t>Samples: 3301, 1903, 1936, 1937; columns: G</t>
+        </is>
+      </c>
+      <c r="G104" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="160" customHeight="1" s="50">
+      <c r="A105" s="76" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="B105" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg")</f>
+        <v/>
+      </c>
+      <c r="C105" s="76" t="inlineStr">
+        <is>
+          <t>11/15/2025, Frank Puentes</t>
+        </is>
+      </c>
+      <c r="D105" s="76" t="inlineStr">
+        <is>
+          <t>Email + report attachments</t>
+        </is>
+      </c>
+      <c r="E105" s="76" t="inlineStr">
+        <is>
+          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf; FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf; OFAC ACH 111425 - 11152025 1126AM.pdf; OFAC FED 111425 - 111525 1126AM.pdf; OFAC SWIFT 111425 - 111525 1128AM.pdf; OUTGOING FEDWIRE 111525 1025AM.xls; OUTGOING SWIFT 111525 1026AM.xls; PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf; PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf.</t>
+        </is>
+      </c>
+      <c r="F105" s="76" t="inlineStr">
+        <is>
+          <t>Samples: 3301, 1903, 1936, 1937; columns: G, N</t>
+        </is>
+      </c>
+      <c r="G105" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="52" customHeight="1" s="50">
+      <c r="A106" s="76" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="B106" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg")</f>
+        <v/>
+      </c>
+      <c r="C106" s="76" t="inlineStr">
+        <is>
+          <t>03/03/2026 to 05/05/2026: Claudia Romero</t>
+        </is>
+      </c>
+      <c r="D106" s="76" t="inlineStr">
+        <is>
+          <t>Email approval</t>
+        </is>
+      </c>
+      <c r="E106" s="76" t="inlineStr">
+        <is>
+          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
+        </is>
+      </c>
+      <c r="F106" s="76" t="inlineStr">
+        <is>
+          <t>Samples: 1822, 1867, 1868, 3299, 1937; columns: C, F, H, I, K, N, O</t>
+        </is>
+      </c>
+      <c r="G106" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="46" customHeight="1" s="50">
+      <c r="A107" s="76" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B107" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg")</f>
+        <v/>
+      </c>
+      <c r="C107" s="76" t="inlineStr">
+        <is>
+          <t>03/09/2026, Lina Acuna</t>
+        </is>
+      </c>
+      <c r="D107" s="76" t="inlineStr">
+        <is>
+          <t>Email approval</t>
+        </is>
+      </c>
+      <c r="E107" s="76" t="inlineStr">
+        <is>
+          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
+        </is>
+      </c>
+      <c r="F107" s="76" t="inlineStr">
+        <is>
+          <t>Samples: 1917, 1937; columns: N</t>
+        </is>
+      </c>
+      <c r="G107" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="46" customHeight="1" s="50">
+      <c r="A108" s="76" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="B108" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg")</f>
+        <v/>
+      </c>
+      <c r="C108" s="76" t="inlineStr">
+        <is>
+          <t>11/13/2024, T24 backup user</t>
+        </is>
+      </c>
+      <c r="D108" s="76" t="inlineStr">
+        <is>
+          <t>System email</t>
+        </is>
+      </c>
+      <c r="E108" s="76" t="inlineStr">
+        <is>
+          <t>T24 environment refresh log: prior period (outside review period); supplemental only.</t>
+        </is>
+      </c>
+      <c r="F108" s="76" t="inlineStr">
+        <is>
+          <t>Samples: ; columns: (supplemental)</t>
+        </is>
+      </c>
+      <c r="G108" s="79" t="inlineStr">
+        <is>
+          <t>N/A (supplemental, not relied on)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="46" customHeight="1" s="50">
+      <c r="A109" s="76" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
+      <c r="B109" s="75">
+        <f>HYPERLINK(EvidenceRoot&amp;IF(LEFT(EvidenceRoot,4)="http",SUBSTITUTE("04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx","\","/"),"04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx"),"BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx")</f>
+        <v/>
+      </c>
+      <c r="C109" s="76" t="inlineStr">
+        <is>
+          <t>08/2026: BCiC export sent with attestation request</t>
+        </is>
+      </c>
+      <c r="D109" s="76" t="inlineStr">
+        <is>
+          <t>BCiC export</t>
+        </is>
+      </c>
+      <c r="E109" s="76" t="inlineStr">
+        <is>
+          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
+        </is>
+      </c>
+      <c r="F109" s="76" t="inlineStr">
+        <is>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, F, G, J, L, P</t>
+        </is>
+      </c>
+      <c r="G109" s="77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="H29:N29"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="H13:P13"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="H49:R49"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="H45:O45"/>
-    <mergeCell ref="H8:P8"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="H25:W25"/>
-    <mergeCell ref="H53:M53"/>
+  <mergeCells count="18">
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A96:G96"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="H57:AA57"/>
-    <mergeCell ref="H21:W21"/>
-    <mergeCell ref="A89:G89"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="A3:G3"/>
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="H17:Q17"/>
-    <mergeCell ref="H33:U33"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A5" location="'Application Attribute Testing'!A98"/>
-    <hyperlink ref="A9" location="'Application Attribute Testing'!A99"/>
-    <hyperlink ref="A14" location="'Application Attribute Testing'!A101"/>
-    <hyperlink ref="A18" location="'Application Attribute Testing'!A101"/>
-    <hyperlink ref="A22" location="'Application Attribute Testing'!A101"/>
-    <hyperlink ref="A26" location="'Application Attribute Testing'!A101"/>
-    <hyperlink ref="A30" location="'Application Attribute Testing'!A101"/>
-    <hyperlink ref="A34" location="'Application Attribute Testing'!A78"/>
-    <hyperlink ref="A35" location="'Application Attribute Testing'!A82"/>
-    <hyperlink ref="A36" location="'Application Attribute Testing'!A83"/>
-    <hyperlink ref="A37" location="'Application Attribute Testing'!A84"/>
-    <hyperlink ref="A38" location="'Application Attribute Testing'!A85"/>
-    <hyperlink ref="A42" location="'Application Attribute Testing'!A101"/>
-    <hyperlink ref="A46" location="'Application Attribute Testing'!A99"/>
-    <hyperlink ref="A50" location="'Application Attribute Testing'!A103"/>
-    <hyperlink ref="A54" location="'Application Attribute Testing'!A98"/>
-    <hyperlink ref="A58" location="'Application Attribute Testing'!A78"/>
-    <hyperlink ref="A59" location="'Application Attribute Testing'!A82"/>
-    <hyperlink ref="A60" location="'Application Attribute Testing'!A83"/>
-    <hyperlink ref="A61" location="'Application Attribute Testing'!A84"/>
-    <hyperlink ref="A62" location="'Application Attribute Testing'!A85"/>
+    <hyperlink ref="A3" location="'Application Attribute Testing-1'!B2" tooltip="Back to column B on Application Attribute Testing-1"/>
+    <hyperlink ref="A5" location="'Testing Attributes Testing -2'!A98" tooltip="Go to MA01 evidence review"/>
+    <hyperlink ref="A7" location="'Application Attribute Testing-1'!C2" tooltip="Back to column C on Application Attribute Testing-1"/>
+    <hyperlink ref="A9" location="'Testing Attributes Testing -2'!A98" tooltip="Go to MA01 evidence review"/>
+    <hyperlink ref="A11" location="'Application Attribute Testing-1'!D2" tooltip="Back to column D on Application Attribute Testing-1"/>
+    <hyperlink ref="A13" location="'Testing Attributes Testing -2'!A99" tooltip="Go to E01 evidence review"/>
+    <hyperlink ref="A15" location="'Application Attribute Testing-1'!E2" tooltip="Back to column E on Application Attribute Testing-1"/>
+    <hyperlink ref="A17" location="'Testing Attributes Testing -2'!A99" tooltip="Go to E01 evidence review"/>
+    <hyperlink ref="A19" location="'Application Attribute Testing-1'!F2" tooltip="Back to column F on Application Attribute Testing-1"/>
+    <hyperlink ref="A21" location="'Testing Attributes Testing -2'!A101" tooltip="Go to E03 evidence review"/>
+    <hyperlink ref="A23" location="'Application Attribute Testing-1'!G2" tooltip="Back to column G on Application Attribute Testing-1"/>
+    <hyperlink ref="A25" location="'Testing Attributes Testing -2'!A101" tooltip="Go to E03 evidence review"/>
+    <hyperlink ref="A27" location="'Application Attribute Testing-1'!H2" tooltip="Back to column H on Application Attribute Testing-1"/>
+    <hyperlink ref="A29" location="'Testing Attributes Testing -2'!A101" tooltip="Go to E03 evidence review"/>
+    <hyperlink ref="A31" location="'Application Attribute Testing-1'!I2" tooltip="Back to column I on Application Attribute Testing-1"/>
+    <hyperlink ref="A33" location="'Testing Attributes Testing -2'!A101" tooltip="Go to E03 evidence review"/>
+    <hyperlink ref="A35" location="'Application Attribute Testing-1'!J2" tooltip="Back to column J on Application Attribute Testing-1"/>
+    <hyperlink ref="A37" location="'Testing Attributes Testing -2'!A101" tooltip="Go to E03 evidence review"/>
+    <hyperlink ref="A39" location="'Application Attribute Testing-1'!K2" tooltip="Back to column K on Application Attribute Testing-1"/>
+    <hyperlink ref="A41" location="'Testing Attributes Testing -2'!A78" tooltip="Go to BLA06 evidence review"/>
+    <hyperlink ref="A42" location="'Testing Attributes Testing -2'!A82" tooltip="Go to DMA01 evidence review"/>
+    <hyperlink ref="A43" location="'Testing Attributes Testing -2'!A83" tooltip="Go to DMA02 evidence review"/>
+    <hyperlink ref="A44" location="'Testing Attributes Testing -2'!A84" tooltip="Go to DMA03 evidence review"/>
+    <hyperlink ref="A45" location="'Testing Attributes Testing -2'!A85" tooltip="Go to DMA04 evidence review"/>
+    <hyperlink ref="A47" location="'Application Attribute Testing-1'!L2" tooltip="Back to column L on Application Attribute Testing-1"/>
+    <hyperlink ref="A49" location="'Testing Attributes Testing -2'!A101" tooltip="Go to E03 evidence review"/>
+    <hyperlink ref="A51" location="'Application Attribute Testing-1'!M2" tooltip="Back to column M on Application Attribute Testing-1"/>
+    <hyperlink ref="A53" location="'Testing Attributes Testing -2'!A99" tooltip="Go to E01 evidence review"/>
+    <hyperlink ref="A55" location="'Application Attribute Testing-1'!N2" tooltip="Back to column N on Application Attribute Testing-1"/>
+    <hyperlink ref="A57" location="'Testing Attributes Testing -2'!A103" tooltip="Go to E05 evidence review"/>
+    <hyperlink ref="A59" location="'Application Attribute Testing-1'!O2" tooltip="Back to column O on Application Attribute Testing-1"/>
+    <hyperlink ref="A61" location="'Testing Attributes Testing -2'!A78" tooltip="Go to BLA06 evidence review"/>
+    <hyperlink ref="A62" location="'Testing Attributes Testing -2'!A82" tooltip="Go to DMA01 evidence review"/>
+    <hyperlink ref="A63" location="'Testing Attributes Testing -2'!A83" tooltip="Go to DMA02 evidence review"/>
+    <hyperlink ref="A64" location="'Testing Attributes Testing -2'!A84" tooltip="Go to DMA03 evidence review"/>
+    <hyperlink ref="A65" location="'Testing Attributes Testing -2'!A85" tooltip="Go to DMA04 evidence review"/>
+    <hyperlink ref="A67" location="'Application Attribute Testing-1'!P2" tooltip="Back to column P on Application Attribute Testing-1"/>
+    <hyperlink ref="A69" location="'Testing Attributes Testing -2'!A101" tooltip="Go to E03 evidence review"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_13_1.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_13_1.xlsx
@@ -1352,11 +1352,17 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>BSI.IT.6.C7.3</author>
+    <author>Control Testing</author>
   </authors>
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
         <t>Click an evidence file path to open the file. The evidence folder location is set on tab 'WP Summary' (yellow cell, row 27): blank = folder 'BSI.IT.6.C7.3-Evidences' next to this workbook.</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="1" shapeId="0">
+      <text>
+        <t>Annual execution: 2025 cycle, BSI IT DR Exercise 11/15/2025 (DIV validated 11/15/2025), within the review period 08/01/2025 to 06/01/2026. 2024 cycle, Full DR Test (Virginia) 10/19/2024, see tab 'DR 2024 Testing Results'. One DR / DIV exercise per annual cycle; 392 days between exercises.</t>
       </text>
     </comment>
   </commentList>
@@ -1367,11 +1373,17 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>BSI.IT.6.C7.3</author>
+    <author>Control Testing</author>
   </authors>
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
         <t>Click an evidence file path to open the file. The evidence folder location is set on tab 'WP Summary' (yellow cell, row 27): blank = folder 'BSI.IT.6.C7.3-Evidences' next to this workbook.</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="1" shapeId="0">
+      <text>
+        <t>Annual execution: 2025 cycle, BSI IT DR Exercise 11/15/2025 (DIV validated 11/15/2025), within the review period 08/01/2025 to 06/01/2026. 2024 cycle, Full DR Test (Virginia) 10/19/2024, see tab 'DR 2024 Testing Results'. One DR / DIV exercise per annual cycle; 392 days between exercises.</t>
       </text>
     </comment>
   </commentList>
@@ -5256,7 +5268,7 @@
       </c>
       <c r="S3" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5304,7 @@
       </c>
       <c r="G4" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 1 of 1 record; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 1 of 1 record; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H4" s="42" t="inlineStr">
@@ -5368,7 +5380,7 @@
       </c>
       <c r="S4" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5416,7 @@
       </c>
       <c r="G5" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 1 of 1 record; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 1 of 1 record; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H5" s="42" t="inlineStr">
@@ -5480,7 +5492,7 @@
       </c>
       <c r="S5" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5533,7 @@
       </c>
       <c r="G6" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 6 of 6 records; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 6 of 6 records; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H6" s="42" t="inlineStr">
@@ -5614,7 +5626,7 @@
       </c>
       <c r="S6" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Claudia Romero, Miguel Orozco, Maria del Cerro Hontanilla).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Claudia Romero, Miguel Orozco, Maria del Cerro Hontanilla).</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5662,7 @@
       </c>
       <c r="G7" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 1 of 1 record; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 1 of 1 record; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H7" s="42" t="inlineStr">
@@ -5725,7 +5737,7 @@
       </c>
       <c r="S7" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Michelle Oropesa).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Michelle Oropesa).</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5773,7 @@
       </c>
       <c r="G8" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 2 of 2 records; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 2 of 2 records; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H8" s="42" t="inlineStr">
@@ -5839,7 +5851,7 @@
       </c>
       <c r="S8" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Franklin Puentes).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Franklin Puentes).</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5889,7 @@
       </c>
       <c r="G9" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 5 of 5 records; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 5 of 5 records; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H9" s="42" t="inlineStr">
@@ -5966,7 +5978,7 @@
       </c>
       <c r="S9" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Franklin Puentes, Maria del Cerro Hontanilla).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Franklin Puentes, Maria del Cerro Hontanilla).</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6014,7 @@
       </c>
       <c r="G10" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 1 of 1 record; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 1 of 1 record; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H10" s="42" t="inlineStr">
@@ -6078,7 +6090,7 @@
       </c>
       <c r="S10" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Sadis Alvarenga Hernandez).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Sadis Alvarenga Hernandez).</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6127,7 @@
       </c>
       <c r="G11" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 2 of 2 records; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 2 of 2 records; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H11" s="45" t="inlineStr">
@@ -6197,7 +6209,7 @@
       </c>
       <c r="S11" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Michelle Oropesa).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Michelle Oropesa).</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6261,7 @@
       </c>
       <c r="G12" s="42" t="inlineStr">
         <is>
-          <t>11/15/2025, data validated during the DR exercise; Format / Headers / Content = Y / Y / Y for 36 of 36 records; no data integrity exceptions.</t>
+          <t>11/15/2025, data validated during the DR exercise; Format, Headers and Content validated for 36 of 36 records; no data integrity exceptions.</t>
         </is>
       </c>
       <c r="H12" s="42" t="inlineStr">
@@ -6386,7 +6398,7 @@
       </c>
       <c r="S12" s="44" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Ricardo Garcia, David Marquez, Claudia Romero, Miguel Orozco, Sadis Alvarenga Hernandez, Maria del Cerro Hontanilla, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez, Xavier Caisapanta, Clara De Castro).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Ricardo Garcia, David Marquez, Claudia Romero, Miguel Orozco, Sadis Alvarenga Hernandez, Maria del Cerro Hontanilla, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez, Xavier Caisapanta, Clara De Castro).</t>
         </is>
       </c>
     </row>
@@ -6967,7 +6979,7 @@
       </c>
       <c r="H16" s="67" t="n"/>
     </row>
-    <row r="17" ht="126" customHeight="1" s="50">
+    <row r="17" ht="190" customHeight="1" s="50">
       <c r="A17" s="78" t="inlineStr">
         <is>
           <t>E01</t>
@@ -7002,9 +7014,7 @@
 Checked for IT DR exercise name, was the exercise annually executed?
 Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-2025 cycle: BSI IT DR Exercise 11/15/2025 (within the review period 08/01/2025 to 06/01/2026).
-2024 cycle: 2024 Full 2024 DR Test (Virginia) 10/19/2024, see tab 'DR 2024 Testing Results'.
-Interval 10/19/2024 to 11/15/2025 = 392 days; one DR / DIV exercise in each annual cycle.</t>
+Note: Annual execution: 2025 cycle, BSI IT DR Exercise 11/15/2025 (DIV validated 11/15/2025), within the review period 08/01/2025 to 06/01/2026. 2024 cycle, Full DR Test (Virginia) 10/19/2024, see tab 'DR 2024 Testing Results'. One DR / DIV exercise per annual cycle; 392 days between exercises.</t>
         </is>
       </c>
       <c r="F17" s="76" t="inlineStr">
@@ -7137,7 +7147,7 @@
       </c>
       <c r="E21" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Business Tester:
 'Business Tester(s)' column</t>
         </is>
@@ -7273,9 +7283,9 @@
       </c>
       <c r="E25" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Business Data validation:
-Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y</t>
+Business Data Validation Date 11/15/2025; Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="F25" s="76" t="inlineStr">
@@ -7410,7 +7420,7 @@
       </c>
       <c r="E29" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Business line manager name:
 'Department Manager' column</t>
         </is>
@@ -7553,7 +7563,7 @@
       </c>
       <c r="E33" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Business line manager approval dates:
 'Department Manager Approval Date' and 'Attestation Date' columns</t>
         </is>
@@ -7696,7 +7706,7 @@
       </c>
       <c r="E37" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for DIV Test procedures listed within the Test results document:
 'Data Integrity Validation Procedures' column</t>
         </is>
@@ -7919,7 +7929,7 @@
       </c>
       <c r="E43" s="76" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all validated; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
 Checked for Emails showing Business line manager approval of DIV testing results:
 Application / record agreed to the evidence.</t>
         </is>
@@ -8126,9 +8136,9 @@
       </c>
       <c r="E49" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for All evidence of Data Integrity DR test in BCIC:
-BCiC DIV export (tester, dates, manager, Y/N results, attestation)</t>
+BCiC DIV export (tester, dates, manager, validation results, attestation)</t>
         </is>
       </c>
       <c r="F49" s="76" t="inlineStr">
@@ -8628,7 +8638,7 @@
       </c>
       <c r="E63" s="76" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all validated; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
 Checked for Business Line Approval of Results:
 Application / record agreed to the evidence.</t>
         </is>
@@ -8835,7 +8845,7 @@
       </c>
       <c r="E69" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Results Documented in BCMS:
 DIV results, business tester, validation date, manager approval and attestation fields recorded in BCMS (BC in the Cloud) for each application</t>
         </is>
@@ -8938,7 +8948,7 @@
       </c>
       <c r="E73" s="76" t="inlineStr">
         <is>
-          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y, "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
+          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format, Headers and Content validated, "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
         </is>
       </c>
       <c r="F73" s="76" t="inlineStr">
@@ -9249,7 +9259,7 @@
       </c>
       <c r="E83" s="76" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all validated; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="F83" s="76" t="inlineStr">
@@ -9848,7 +9858,7 @@
       </c>
       <c r="E101" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="F101" s="76" t="inlineStr">
@@ -9884,7 +9894,7 @@
       </c>
       <c r="E102" s="76" t="inlineStr">
         <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1 to 20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1 to 20 of 66 items) showing tester, validation date, manager, approval date, validation results and attestation fields.</t>
         </is>
       </c>
       <c r="F102" s="76" t="inlineStr">
@@ -10272,7 +10282,7 @@
       </c>
       <c r="F115" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
         </is>
       </c>
       <c r="G115" s="77" t="inlineStr">
@@ -10334,7 +10344,7 @@
       </c>
       <c r="F116" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
         </is>
       </c>
       <c r="G116" s="77" t="inlineStr">
@@ -10396,7 +10406,7 @@
       </c>
       <c r="F117" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
         </is>
       </c>
       <c r="G117" s="77" t="inlineStr">
@@ -10461,7 +10471,7 @@
       </c>
       <c r="F118" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Claudia Romero, Miguel Orozco, Maria del Cerro Hontanilla).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Claudia Romero, Miguel Orozco, Maria del Cerro Hontanilla).</t>
         </is>
       </c>
       <c r="G118" s="77" t="inlineStr">
@@ -10522,7 +10532,7 @@
       </c>
       <c r="F119" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Michelle Oropesa).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Michelle Oropesa).</t>
         </is>
       </c>
       <c r="G119" s="77" t="inlineStr">
@@ -10585,7 +10595,7 @@
       </c>
       <c r="F120" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Franklin Puentes).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Franklin Puentes).</t>
         </is>
       </c>
       <c r="G120" s="77" t="inlineStr">
@@ -10650,7 +10660,7 @@
       </c>
       <c r="F121" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Franklin Puentes, Maria del Cerro Hontanilla).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Franklin Puentes, Maria del Cerro Hontanilla).</t>
         </is>
       </c>
       <c r="G121" s="77" t="inlineStr">
@@ -10712,7 +10722,7 @@
       </c>
       <c r="F122" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Sadis Alvarenga Hernandez).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Sadis Alvarenga Hernandez).</t>
         </is>
       </c>
       <c r="G122" s="77" t="inlineStr">
@@ -10776,7 +10786,7 @@
       </c>
       <c r="F123" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Michelle Oropesa).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Michelle Oropesa).</t>
         </is>
       </c>
       <c r="G123" s="77" t="inlineStr">
@@ -10856,7 +10866,7 @@
       </c>
       <c r="F124" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Ricardo Garcia, David Marquez, Claudia Romero, Miguel Orozco, Sadis Alvarenga Hernandez, Maria del Cerro Hontanilla, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez, Xavier Caisapanta, Clara De Castro).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Ricardo Garcia, David Marquez, Claudia Romero, Miguel Orozco, Sadis Alvarenga Hernandez, Maria del Cerro Hontanilla, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez, Xavier Caisapanta, Clara De Castro).</t>
         </is>
       </c>
       <c r="G124" s="77" t="inlineStr">
@@ -11837,7 +11847,7 @@
       <c r="AX16" s="85" t="n"/>
       <c r="AY16" s="85" t="n"/>
     </row>
-    <row r="17" ht="126" customHeight="1" s="50">
+    <row r="17" ht="190" customHeight="1" s="50">
       <c r="A17" s="78" t="inlineStr">
         <is>
           <t>E01</t>
@@ -11872,9 +11882,7 @@
 Checked for IT DR exercise name, was the exercise annually executed?
 Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-2025 cycle: BSI IT DR Exercise 11/15/2025 (within the review period 08/01/2025 to 06/01/2026).
-2024 cycle: 2024 Full 2024 DR Test (Virginia) 10/19/2024, see tab 'DR 2024 Testing Results'.
-Interval 10/19/2024 to 11/15/2025 = 392 days; one DR / DIV exercise in each annual cycle.</t>
+Note: Annual execution: 2025 cycle, BSI IT DR Exercise 11/15/2025 (DIV validated 11/15/2025), within the review period 08/01/2025 to 06/01/2026. 2024 cycle, Full DR Test (Virginia) 10/19/2024, see tab 'DR 2024 Testing Results'. One DR / DIV exercise per annual cycle; 392 days between exercises.</t>
         </is>
       </c>
       <c r="F17" s="76" t="inlineStr">
@@ -12103,7 +12111,7 @@
       </c>
       <c r="E21" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Business Tester:
 'Business Tester(s)' column</t>
         </is>
@@ -12335,9 +12343,9 @@
       </c>
       <c r="E25" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Business Data validation:
-Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y</t>
+Business Data Validation Date 11/15/2025; Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="F25" s="76" t="inlineStr">
@@ -12568,7 +12576,7 @@
       </c>
       <c r="E29" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Business line manager name:
 'Department Manager' column</t>
         </is>
@@ -12807,7 +12815,7 @@
       </c>
       <c r="E33" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Business line manager approval dates:
 'Department Manager Approval Date' and 'Attestation Date' columns</t>
         </is>
@@ -13046,7 +13054,7 @@
       </c>
       <c r="E37" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for DIV Test procedures listed within the Test results document:
 'Data Integrity Validation Procedures' column</t>
         </is>
@@ -13413,7 +13421,7 @@
       </c>
       <c r="E43" s="76" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all validated; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
 Checked for Emails showing Business line manager approval of DIV testing results:
 Application / record agreed to the evidence.</t>
         </is>
@@ -13764,9 +13772,9 @@
       </c>
       <c r="E49" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for All evidence of Data Integrity DR test in BCIC:
-BCiC DIV export (tester, dates, manager, Y/N results, attestation)</t>
+BCiC DIV export (tester, dates, manager, validation results, attestation)</t>
         </is>
       </c>
       <c r="F49" s="76" t="inlineStr">
@@ -14602,7 +14610,7 @@
       </c>
       <c r="E63" s="76" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all validated; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.
 Checked for Business Line Approval of Results:
 Application / record agreed to the evidence.</t>
         </is>
@@ -14953,7 +14961,7 @@
       </c>
       <c r="E69" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.
 Checked for Results Documented in BCMS:
 DIV results, business tester, validation date, manager approval and attestation fields recorded in BCMS (BC in the Cloud) for each application</t>
         </is>
@@ -15152,7 +15160,7 @@
       </c>
       <c r="E73" s="76" t="inlineStr">
         <is>
-          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y, "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
+          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format, Headers and Content validated, "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
         </is>
       </c>
       <c r="F73" s="76" t="inlineStr">
@@ -15703,7 +15711,7 @@
       </c>
       <c r="E83" s="76" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all validated; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="F83" s="76" t="inlineStr">
@@ -16734,7 +16742,7 @@
       </c>
       <c r="E101" s="76" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="F101" s="76" t="inlineStr">
@@ -16794,7 +16802,7 @@
       </c>
       <c r="E102" s="76" t="inlineStr">
         <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1 to 20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1 to 20 of 66 items) showing tester, validation date, manager, approval date, validation results and attestation fields.</t>
         </is>
       </c>
       <c r="F102" s="76" t="inlineStr">
@@ -17086,22 +17094,22 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A35:G35"/>
     <mergeCell ref="A96:G96"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A71:G71"/>
     <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A71:G71"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
@@ -17562,7 +17570,7 @@
       </c>
       <c r="F5" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Claudia Romero).</t>
         </is>
       </c>
       <c r="G5" s="77" t="inlineStr">
@@ -17670,7 +17678,7 @@
       </c>
       <c r="F6" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Claudia Romero, Miguel Orozco, Maria del Cerro Hontanilla).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Claudia Romero, Miguel Orozco, Maria del Cerro Hontanilla).</t>
         </is>
       </c>
       <c r="G6" s="77" t="inlineStr">
@@ -17774,7 +17782,7 @@
       </c>
       <c r="F7" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Michelle Oropesa).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Michelle Oropesa).</t>
         </is>
       </c>
       <c r="G7" s="77" t="inlineStr">
@@ -17880,7 +17888,7 @@
       </c>
       <c r="F8" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Franklin Puentes).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Franklin Puentes).</t>
         </is>
       </c>
       <c r="G8" s="77" t="inlineStr">
@@ -17988,7 +17996,7 @@
       </c>
       <c r="F9" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Franklin Puentes, Maria del Cerro Hontanilla).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Franklin Puentes, Maria del Cerro Hontanilla).</t>
         </is>
       </c>
       <c r="G9" s="77" t="inlineStr">
@@ -18093,7 +18101,7 @@
       </c>
       <c r="F10" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Sadis Alvarenga Hernandez).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Sadis Alvarenga Hernandez).</t>
         </is>
       </c>
       <c r="G10" s="77" t="inlineStr">
@@ -18200,7 +18208,7 @@
       </c>
       <c r="F11" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Michelle Oropesa).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (David Marquez, Michelle Oropesa).</t>
         </is>
       </c>
       <c r="G11" s="77" t="inlineStr">
@@ -18323,7 +18331,7 @@
       </c>
       <c r="F12" s="76" t="inlineStr">
         <is>
-          <t>PASS. DIV executed and validated (Y/Y/Y) during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Ricardo Garcia, David Marquez, Claudia Romero, Miguel Orozco, Sadis Alvarenga Hernandez, Maria del Cerro Hontanilla, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez, Xavier Caisapanta, Clara De Castro).</t>
+          <t>PASS. DIV executed and validated during the 11/15/2025 annual DR exercise, application in scope (MA01), results documented in BCiC/BCMS and approved by business line management (Ricardo Garcia, David Marquez, Claudia Romero, Miguel Orozco, Sadis Alvarenga Hernandez, Maria del Cerro Hontanilla, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez, Xavier Caisapanta, Clara De Castro).</t>
         </is>
       </c>
       <c r="G12" s="77" t="inlineStr">
@@ -21331,9 +21339,9 @@
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48 to 11/15/2025; Y / Y / Y
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format / Headers / Content = Y, "No data discrepancy found"); pp.2-14 screenshots</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48 to 11/15/2025; Format, Headers and Content validated
+BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
         </is>
       </c>
       <c r="F5" s="25" t="inlineStr">
@@ -21365,7 +21373,7 @@
       </c>
       <c r="J5" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 48, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 3
@@ -21387,7 +21395,7 @@
 DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
 BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 47, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
@@ -21475,10 +21483,10 @@
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9 to 11/15/2025; Y / Y / Y
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and Y/N columns
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format / Headers / Content = Y, "No data discrepancy found"); pp.2-14 screenshots</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
+BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
         </is>
       </c>
       <c r="F6" s="25" t="inlineStr">
@@ -21512,7 +21520,7 @@
       </c>
       <c r="J6" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 9, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 19
@@ -21534,7 +21542,7 @@
 DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
 BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 9, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M6" s="25" t="inlineStr">
@@ -21622,10 +21630,10 @@
       </c>
       <c r="E7" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10 to 11/15/2025; Y / Y / Y
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and Y/N columns
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format / Headers / Content = Y, "No data discrepancy found"); pp.2-14 screenshots</t>
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
+BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots</t>
         </is>
       </c>
       <c r="F7" s="25" t="inlineStr">
@@ -21659,7 +21667,7 @@
       </c>
       <c r="J7" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 10, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 20
@@ -21681,7 +21689,7 @@
 DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
 BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 10, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M7" s="25" t="inlineStr">
@@ -21771,10 +21779,10 @@
       </c>
       <c r="E8" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58 to 11/15/2025; Y / Y / Y
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and Y/N columns
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format / Headers / Content = Y, "No data discrepancy found"); pp.2-14 screenshots
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
+BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots
 BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots</t>
         </is>
       </c>
@@ -21819,7 +21827,7 @@
       </c>
       <c r="J8" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 5, 11, 13, 52, 54, 58, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 24
@@ -21843,7 +21851,7 @@
 BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 E09: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg, IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 5, 11, 13, 51, 53, 57, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M8" s="25" t="inlineStr">
@@ -21936,8 +21944,8 @@
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62 to 11/15/2025; Y / Y / Y
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62 to 11/15/2025; Format, Headers and Content validated
 BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)</t>
         </is>
       </c>
@@ -21967,7 +21975,7 @@
       </c>
       <c r="J9" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 62, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 25
@@ -21988,7 +21996,7 @@
           <t>E05: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg, IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
 DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
 BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, IT DR test script completed by the business-line tester
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 61, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M9" s="25" t="inlineStr">
@@ -22071,8 +22079,8 @@
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29 to 11/15/2025; Y / Y / Y
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29 to 11/15/2025; Format, Headers and Content validated
 BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
 E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
 E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, DR test-day 11/15/2025 comparison reports</t>
@@ -22104,7 +22112,7 @@
       </c>
       <c r="J10" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 25, 29, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 31
@@ -22126,7 +22134,7 @@
 DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
 BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 25, 29, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M10" s="25" t="inlineStr">
@@ -22214,9 +22222,9 @@
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59 to 11/15/2025; Y / Y / Y
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and Y/N columns
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
 BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots
 BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
 E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
@@ -22258,7 +22266,7 @@
       </c>
       <c r="J11" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 6, 26, 30, 34, 59, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 34
@@ -22282,7 +22290,7 @@
 BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 6, 26, 30, 34, 58, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M11" s="25" t="inlineStr">
@@ -22372,8 +22380,8 @@
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17 to 11/15/2025; Y / Y / Y
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17 to 11/15/2025; Format, Headers and Content validated
 BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Yes / Yes / Yes, no discrepancies); pp.2-9 reconciliation reports 11/13 versus 11/15</t>
         </is>
       </c>
@@ -22403,7 +22411,7 @@
       </c>
       <c r="J12" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, row 17, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, BCiC report screen (record on a later page of the 66-item report)
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 36
@@ -22425,7 +22433,7 @@
 DMA02: BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg, attached signed attestation section 1-2, IT DR team facilitates DIV performed by business line testers during actual DR testing
 BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 E10: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg, IT DR (Elizabeth Noda) Finance DIV chart and approval request
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, row 17, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M12" s="25" t="inlineStr">
@@ -22512,9 +22520,9 @@
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61 to 11/15/2025; Y / Y / Y
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and Y/N columns
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
 BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
 BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)
 E07: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg, pre-DR source reports 11/14/2025 (Payment Monitor, OFAC, SWIFT Interface Monitor)
@@ -22553,7 +22561,7 @@
       </c>
       <c r="J13" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 7, 61, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 42
@@ -22577,7 +22585,7 @@
 BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, IT DR test script completed by the business-line tester
 E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 7, 60, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M13" s="25" t="inlineStr">
@@ -22674,10 +22682,10 @@
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Business Data Validation Date 11/15/2025; Y/N Format / Headers / Content = Y
-E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64 to 11/15/2025; Y / Y / Y
-E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and Y/N columns
-BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format / Headers / Content = Y, "No data discrepancy found"); pp.2-14 screenshots
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Business Data Validation Date 11/15/2025; Format, Headers and Content validated
+E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64 to 11/15/2025; Format, Headers and Content validated
+E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, Business Data Validation Date and validation result columns
+BLA01: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf, p.1 DIV section (Format, Headers and Content validated, "No data discrepancy found"); pp.2-14 screenshots
 BLA02: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf, p.1 DIV procedure &amp; in-scope apps; pp.2-14 production-day 11/14 versus test-day 11/15 screenshots
 BLA03: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf, pp.1-2 DIV section (Format / Headers / Content = yes; 11/14 Fed &amp; SWIFT data reconciled)
 BLA04: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx, DIV table (Format / Headers / Content = Yes; MT300 &amp; FX S reports matched 11/14 versus 11/15)
@@ -22757,7 +22765,7 @@
       </c>
       <c r="J14" s="25" t="inlineStr">
         <is>
-          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+          <t>E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, BCiC DIV export (tester, dates, manager, validation results, attestation)
 E16b: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64, BCiC DIV export 2025-26 reviewed with the attestation
 E04: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg, records visible on screen
 E01: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx, row 43
@@ -22788,7 +22796,7 @@
 BLA05: BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf, IT DR test script completed by the business-line tester
 E08: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg, business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
 E10: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg, IT DR (Elizabeth Noda) Finance DIV chart and approval request
-E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Y/N Format, Headers, Content = Y</t>
+E03: BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls, rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63, Format, Headers and Content validated</t>
         </is>
       </c>
       <c r="M14" s="25" t="inlineStr">
@@ -23142,7 +23150,7 @@
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y, "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
+          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format, Headers and Content validated, "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
         </is>
       </c>
       <c r="I4" s="35" t="inlineStr">
@@ -23506,7 +23514,7 @@
       </c>
       <c r="H11" s="35" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all Y/Y/Y; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf, signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation section 1: IT DR team facilitates DIV annually; section 2: 63 entries / 13 applications, all validated; section 3.5: retained in BCMS/BCiC; section 3.6: contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="I11" s="35" t="inlineStr">
@@ -24230,7 +24238,7 @@
       </c>
       <c r="H25" s="35" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Format/Headers/Content validation results, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="I25" s="35" t="inlineStr">
@@ -24282,7 +24290,7 @@
       </c>
       <c r="H26" s="35" t="inlineStr">
         <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1 to 20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1 to 20 of 66 items) showing tester, validation date, manager, approval date, validation results and attestation fields.</t>
         </is>
       </c>
       <c r="I26" s="35" t="inlineStr">

--- a/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_13_1.xlsx
+++ b/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_13_1.xlsx
@@ -1386,6 +1386,11 @@
         <t>Annual execution: 2025 cycle, BSI IT DR Exercise 11/15/2025 (DIV validated 11/15/2025), within the review period 08/01/2025 to 06/01/2026. 2024 cycle, Full DR Test (Virginia) 10/19/2024, see tab 'DR 2024 Testing Results'. One DR / DIV exercise per annual cycle; 392 days between exercises.</t>
       </text>
     </comment>
+    <comment ref="A51" authorId="1" shapeId="0">
+      <text>
+        <t>Yes, annually executed. 2025 cycle: BSI IT DR Exercise 11/15/2025 (DIV validated 11/15/2025), within the review period 08/01/2025 to 06/01/2026. 2024 cycle: 2024 Full 2024 DR Test (Virginia) on 10/19/2024, see tab 'DR 2024 Testing Results' (application not listed individually on that extract). One DR / DIV exercise executed in each annual DR cycle; interval 10/19/2024 to 11/15/2025 = 392 days.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -13970,7 +13975,7 @@
       <c r="AX52" s="85" t="n"/>
       <c r="AY52" s="85" t="n"/>
     </row>
-    <row r="53" ht="126" customHeight="1" s="50">
+    <row r="53" ht="200" customHeight="1" s="50">
       <c r="A53" s="78" t="inlineStr">
         <is>
           <t>E01</t>
@@ -14004,7 +14009,8 @@
           <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.
 Checked for Annual Testing Executed:
 Exercise Date 12/11/2025 / 2025 DR Test Scope = True
-Exercise Date 11/15/2025 / 2025 DR Test Scope = True</t>
+Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+Note: Yes, annually executed. 2025 cycle: BSI IT DR Exercise 11/15/2025 (DIV validated 11/15/2025), within the review period 08/01/2025 to 06/01/2026. 2024 cycle: 2024 Full 2024 DR Test (Virginia) on 10/19/2024, see tab 'DR 2024 Testing Results' (application not listed individually on that extract). One DR / DIV exercise executed in each annual DR cycle; interval 10/19/2024 to 11/15/2025 = 392 days.</t>
         </is>
       </c>
       <c r="F53" s="76" t="inlineStr">
